--- a/Comentarios Campaña.xlsx
+++ b/Comentarios Campaña.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P127"/>
+  <dimension ref="A1:Q127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,15 +491,20 @@
       </c>
       <c r="N1" t="inlineStr">
         <is>
+          <t>parent_comment_id</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
           <t>author_url</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>extraction_status</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>created_time_raw</t>
         </is>
@@ -551,13 +556,14 @@
       <c r="M2" t="b">
         <v>0</v>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr">
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr">
         <is>
           <t xml:space="preserve">{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7600955886223232277', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSannqcDU/', 'input': 'https://vt.tiktok.com/ZSannqcDU/', 'cid': '7603543574210986772', 'createTime': 1770338207, 'createTimeISO': '2026-02-06T00:36:47.000Z', 'text': 'solo tu gabyy no te vallassss😭😭😭😭😭😭😭😭😭😭😭', 'diggCount': 1, 'likedByAuthor': False, 'repliesToId': '7600981628773204757', 'replyCommentTotal': None, 'uid': '7467024639018468360', 'uniqueId': 'leidy.yulieth22', </t>
         </is>
@@ -609,13 +615,14 @@
       <c r="M3" t="b">
         <v>0</v>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7600955886223232277', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSannqcDU/', 'input': 'https://vt.tiktok.com/ZSannqcDU/', 'cid': '7603543320425923349', 'createTime': 1770338105, 'createTimeISO': '2026-02-06T00:35:05.000Z', 'text': 'gaby no quiero que te vallas😭yo quiero que sigas haciendo videitos de alpinaa😭😭😭😭😭😭😭😭😭😭💙💖', 'diggCount': 1, 'likedByAuthor': False, 'repliesToId': '7600981628773204757', 'replyCommentTotal': None, 'uid': '7467</t>
         </is>
@@ -667,13 +674,14 @@
       <c r="M4" t="b">
         <v>0</v>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr">
         <is>
           <t xml:space="preserve">{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7600955886223232277', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSannqcDU/', 'input': 'https://vt.tiktok.com/ZSannqcDU/', 'cid': '7603542496237093653', 'createTime': 1770337969, 'createTimeISO': '2026-02-06T00:32:49.000Z', 'text': 'jaja🤭si, las recetas se ven muy ricas 💙✨', 'diggCount': 1, 'likedByAuthor': False, 'repliesToId': '7600981628773204757', 'replyCommentTotal': None, 'uid': '7467024639018468360', 'uniqueId': 'leidy.yulieth22', </t>
         </is>
@@ -725,13 +733,14 @@
       <c r="M5" t="b">
         <v>0</v>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7600955886223232277', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSannqcDU/', 'input': 'https://vt.tiktok.com/ZSannqcDU/', 'cid': '7603484564858192660', 'createTime': 1770324221, 'createTimeISO': '2026-02-05T20:43:41.000Z', 'text': 'Haz un video y nos etiquetas!!🤩', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': '7601033369098896136', 'replyCommentTotal': None, 'uid': '7104365507802039302', 'uniqueId': 'al</t>
         </is>
@@ -783,13 +792,14 @@
       <c r="M6" t="b">
         <v>0</v>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7600955886223232277', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSannqcDU/', 'input': 'https://vt.tiktok.com/ZSannqcDU/', 'cid': '7603484464274785045', 'createTime': 1770324202, 'createTimeISO': '2026-02-05T20:43:22.000Z', 'text': 'Cierto???🤩 no es porque yo sea de alpina🤭😉', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': '7600981628773204757', 'replyCommentTotal': None, 'uid': '7104365507802039302', 'uni</t>
         </is>
@@ -841,13 +851,14 @@
       <c r="M7" t="b">
         <v>0</v>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7600955886223232277', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSannqcDU/', 'input': 'https://vt.tiktok.com/ZSannqcDU/', 'cid': '7603484333210682132', 'createTime': 1770324167, 'createTimeISO': '2026-02-05T20:42:47.000Z', 'text': 'Amamoss💙', 'diggCount': 0, 'likedByAuthor': False, 'repliesToId': '7601667808368165639', 'replyCommentTotal': None, 'uid': '7104365507802039302', 'uniqueId': 'alpinacol', 'avatarThumbnail': 'https://p16-common</t>
         </is>
@@ -899,13 +910,14 @@
       <c r="M8" t="b">
         <v>0</v>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7600955886223232277', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSannqcDU/', 'input': 'https://vt.tiktok.com/ZSannqcDU/', 'cid': '7602279642737066760', 'createTime': 1770043671, 'createTimeISO': '2026-02-02T14:47:51.000Z', 'text': 'si, Gabi todavía no he podido conseguir los aqua Mochis😔💙💙', 'diggCount': 0, 'likedByAuthor': False, 'repliesToId': '7600957864790197000', 'replyCommentTotal': None, 'uid': '7505793601163674642', 'uniqueId': '</t>
         </is>
@@ -957,13 +969,14 @@
       <c r="M9" t="b">
         <v>0</v>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7600955886223232277', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSannqcDU/', 'input': 'https://vt.tiktok.com/ZSannqcDU/', 'cid': '7602263847853064980', 'createTime': 1770039996, 'createTimeISO': '2026-02-02T13:46:36.000Z', 'text': 'Ya casiii🤭', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': '7601100678766134023', 'replyCommentTotal': None, 'uid': '7104365507802039302', 'uniqueId': 'alpinacol', 'avatarThum</t>
         </is>
@@ -1015,13 +1028,14 @@
       <c r="M10" t="b">
         <v>0</v>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7600955886223232277', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSannqcDU/', 'input': 'https://vt.tiktok.com/ZSannqcDU/', 'cid': '7602263706861667093', 'createTime': 1770039966, 'createTimeISO': '2026-02-02T13:46:06.000Z', 'text': 'Es deliciosoo!!🤩', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': '7600957864790197000', 'replyCommentTotal': None, 'uid': '7104365507802039302', 'uniqueId': 'alpinacol', 'avat</t>
         </is>
@@ -1073,13 +1087,14 @@
       <c r="M11" t="b">
         <v>0</v>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr">
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7600955886223232277', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSannqcDU/', 'input': 'https://vt.tiktok.com/ZSannqcDU/', 'cid': '7601898749665395464', 'createTime': 1769954987, 'createTimeISO': '2026-02-01T14:09:47.000Z', 'text': 'Busca en Youtube, escribe aqua mochis y te aparece', 'diggCount': 0, 'likedByAuthor': False, 'repliesToId': '7601130474090464007', 'replyCommentTotal': None, 'uid': '7462023650225783816', 'uniqueId': 'salome_.</t>
         </is>
@@ -1131,13 +1146,14 @@
       <c r="M12" t="b">
         <v>0</v>
       </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr">
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7600955886223232277', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSannqcDU/', 'input': 'https://vt.tiktok.com/ZSannqcDU/', 'cid': '7601678572046107413', 'createTime': 1769903894, 'createTimeISO': '2026-01-31T23:58:14.000Z', 'text': 'ya estan en yogo premio', 'diggCount': 1, 'likedByAuthor': False, 'repliesToId': '7601340708133749522', 'replyCommentTotal': None, 'uid': '7467024639018468360', 'uniqueId': 'leidy.yulieth22', 'avatarThumbnail'</t>
         </is>
@@ -1192,13 +1208,14 @@
       <c r="M13" t="b">
         <v>0</v>
       </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr">
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7600955886223232277', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSannqcDU/', 'input': 'https://vt.tiktok.com/ZSannqcDU/', 'cid': '7601667808368165639', 'createTime': 1769901230, 'createTimeISO': '2026-01-31T23:13:50.000Z', 'text': 'Es uno de los más vendidos en nuestros carulla,\nalpinista de corazón💜❤.', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '6962671684969169</t>
         </is>
@@ -1252,13 +1269,14 @@
       <c r="M14" t="b">
         <v>0</v>
       </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr">
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7600955886223232277', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSannqcDU/', 'input': 'https://vt.tiktok.com/ZSannqcDU/', 'cid': '7601648158657413895', 'createTime': 1769896653, 'createTimeISO': '2026-01-31T21:57:33.000Z', 'text': 'Gaby cuando ban a salir los acua mochis', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7587675420830565394', 'uniqueId': 'mathias.castil</t>
         </is>
@@ -1310,13 +1328,14 @@
       <c r="M15" t="b">
         <v>0</v>
       </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7600955886223232277', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSannqcDU/', 'input': 'https://vt.tiktok.com/ZSannqcDU/', 'cid': '7601615764496007937', 'createTime': 1769889101, 'createTimeISO': '2026-01-31T19:51:41.000Z', 'text': 'Como lo buscooo', 'diggCount': 1, 'likedByAuthor': False, 'repliesToId': '7601130474090464007', 'replyCommentTotal': None, 'uid': '7494424850569364481', 'uniqueId': 'maryangel.castrop', 'avatarThumbnail': 'htt</t>
         </is>
@@ -1368,13 +1387,14 @@
       <c r="M16" t="b">
         <v>0</v>
       </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr">
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7600955886223232277', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSannqcDU/', 'input': 'https://vt.tiktok.com/ZSannqcDU/', 'cid': '7601615659219469072', 'createTime': 1769889081, 'createTimeISO': '2026-01-31T19:51:21.000Z', 'text': 'Como lo', 'diggCount': 1, 'likedByAuthor': False, 'repliesToId': '7601130474090464007', 'replyCommentTotal': None, 'uid': '7494424850569364481', 'uniqueId': 'maryangel.castrop', 'avatarThumbnail': 'https://p16</t>
         </is>
@@ -1426,13 +1446,14 @@
       <c r="M17" t="b">
         <v>0</v>
       </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr">
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7600955886223232277', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSannqcDU/', 'input': 'https://vt.tiktok.com/ZSannqcDU/', 'cid': '7601591880967619344', 'createTime': 1769883539, 'createTimeISO': '2026-01-31T18:18:59.000Z', 'text': 'Ya la están sacando se llama ACUA MOCHIS', 'diggCount': 1, 'likedByAuthor': False, 'repliesToId': '7601340708133749522', 'replyCommentTotal': None, 'uid': '7593101177660195856', 'uniqueId': 'andrs.camilo2275',</t>
         </is>
@@ -1486,13 +1507,14 @@
       <c r="M18" t="b">
         <v>0</v>
       </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr">
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7600955886223232277', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSannqcDU/', 'input': 'https://vt.tiktok.com/ZSannqcDU/', 'cid': '7601340708133749522', 'createTime': 1769825063, 'createTimeISO': '2026-01-31T02:04:23.000Z', 'text': 'por que no sacas una nueva colección de mochis', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 2, 'uid': '7368218740909212678', 'uniqueId': 'meowl49</t>
         </is>
@@ -1546,13 +1568,14 @@
       <c r="M19" t="b">
         <v>0</v>
       </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr">
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7600955886223232277', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSannqcDU/', 'input': 'https://vt.tiktok.com/ZSannqcDU/', 'cid': '7601336152705352456', 'createTime': 1769824009, 'createTimeISO': '2026-01-31T01:46:49.000Z', 'text': 'se tu secreto alpinaaaaaa', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7465180798346675201', 'uniqueId': 'mafesita502', 'avatarThumbna</t>
         </is>
@@ -1606,13 +1629,14 @@
       <c r="M20" t="b">
         <v>0</v>
       </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr">
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7600955886223232277', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSannqcDU/', 'input': 'https://vt.tiktok.com/ZSannqcDU/', 'cid': '7601332782338245394', 'createTime': 1769823221, 'createTimeISO': '2026-01-31T01:33:41.000Z', 'text': 'y los nuevos mochis?', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6961098909117907974', 'uniqueId': 'clara0_7', 'avatarThumbnail': 'ht</t>
         </is>
@@ -1666,13 +1690,14 @@
       <c r="M21" t="b">
         <v>0</v>
       </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr">
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7600955886223232277', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSannqcDU/', 'input': 'https://vt.tiktok.com/ZSannqcDU/', 'cid': '7601304306054611732', 'createTime': 1769816597, 'createTimeISO': '2026-01-30T23:43:17.000Z', 'text': 'Alpina los mochisssss', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7571611773297132556', 'uniqueId': 'ronquisaurio.y.re', 'avatarThumb</t>
         </is>
@@ -1726,13 +1751,14 @@
       <c r="M22" t="b">
         <v>0</v>
       </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr">
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7600955886223232277', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSannqcDU/', 'input': 'https://vt.tiktok.com/ZSannqcDU/', 'cid': '7601288389082530580', 'createTime': 1769812897, 'createTimeISO': '2026-01-30T22:41:37.000Z', 'text': 'Pa cuando el bon yourt de blessd', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7280635663249867782', 'uniqueId': 'sxnti_oyl', 'avatarTh</t>
         </is>
@@ -1784,13 +1810,14 @@
       <c r="M23" t="b">
         <v>0</v>
       </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr">
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7600955886223232277', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSannqcDU/', 'input': 'https://vt.tiktok.com/ZSannqcDU/', 'cid': '7601256810984932113', 'createTime': 1769805526, 'createTimeISO': '2026-01-30T20:38:46.000Z', 'text': 've Ami canal te invito porque se nota que estás re perdido', 'diggCount': 0, 'likedByAuthor': False, 'repliesToId': '7600955758550123282', 'replyCommentTotal': None, 'uid': '7581350641369891848', 'uniqueId': '</t>
         </is>
@@ -1844,13 +1871,14 @@
       <c r="M24" t="b">
         <v>0</v>
       </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr">
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7600955886223232277', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSannqcDU/', 'input': 'https://vt.tiktok.com/ZSannqcDU/', 'cid': '7601211223090266898', 'createTime': 1769794908, 'createTimeISO': '2026-01-30T17:41:48.000Z', 'text': 'muy buena y saludable receta, graxiax', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7428447431131857925', 'uniqueId': 'dario.bermudez.m</t>
         </is>
@@ -1904,13 +1932,14 @@
       <c r="M25" t="b">
         <v>0</v>
       </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr">
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7600955886223232277', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSannqcDU/', 'input': 'https://vt.tiktok.com/ZSannqcDU/', 'cid': '7601208873487926036', 'createTime': 1769794365, 'createTimeISO': '2026-01-30T17:32:45.000Z', 'text': '😭😭😭😭😭 @Alpina el miércoles me salieron elfina y pinardo pero de otro color', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '73211360028600</t>
         </is>
@@ -1964,13 +1993,14 @@
       <c r="M26" t="b">
         <v>0</v>
       </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr">
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7600955886223232277', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSannqcDU/', 'input': 'https://vt.tiktok.com/ZSannqcDU/', 'cid': '7601181962170630930', 'createTime': 1769788096, 'createTimeISO': '2026-01-30T15:48:16.000Z', 'text': 'Ya que Gaby me ignoró el mensaje, vengo a preguntarle acá si el Applause se sigue vendiendo? 🤔', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'u</t>
         </is>
@@ -2022,13 +2052,14 @@
       <c r="M27" t="b">
         <v>0</v>
       </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr">
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7600955886223232277', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSannqcDU/', 'input': 'https://vt.tiktok.com/ZSannqcDU/', 'cid': '7601148384763151122', 'createTime': 1769780282, 'createTimeISO': '2026-01-30T13:38:02.000Z', 'text': 'Hola, es que ella había dicho que haría una dinamica, pero no pasa nada si te equivocaste 😄', 'diggCount': 1, 'likedByAuthor': False, 'repliesToId': '7601130474090464007', 'replyCommentTotal': None, 'uid': '74</t>
         </is>
@@ -2080,13 +2111,14 @@
       <c r="M28" t="b">
         <v>0</v>
       </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr">
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7600955886223232277', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSannqcDU/', 'input': 'https://vt.tiktok.com/ZSannqcDU/', 'cid': '7601141061986370325', 'createTime': 1769778733, 'createTimeISO': '2026-01-30T13:12:13.000Z', 'text': 'la nueva colección se llama AQUA MOCHIS busca en YouTube y veras', 'diggCount': 2, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': '7601130474090464007', 'replyCommentTotal': None, 'uid': '7467</t>
         </is>
@@ -2140,13 +2172,14 @@
       <c r="M29" t="b">
         <v>0</v>
       </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr">
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7600955886223232277', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSannqcDU/', 'input': 'https://vt.tiktok.com/ZSannqcDU/', 'cid': '7601130474090464007', 'createTime': 1769776110, 'createTimeISO': '2026-01-30T12:28:30.000Z', 'text': 'Dame 2 pistas de la dinamica plis 🥹', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 5, 'uid': '7462023650225783816', 'uniqueId': 'salome_.art', 'ava</t>
         </is>
@@ -2200,13 +2233,14 @@
       <c r="M30" t="b">
         <v>0</v>
       </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr">
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7600955886223232277', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSannqcDU/', 'input': 'https://vt.tiktok.com/ZSannqcDU/', 'cid': '7601100678766134023', 'createTime': 1769769175, 'createTimeISO': '2026-01-30T10:32:55.000Z', 'text': 'gabyyyy los mochisss están de morados', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '7502913145976767509', 'uniqueId': 'rudy.alvarez024'</t>
         </is>
@@ -2260,13 +2294,14 @@
       <c r="M31" t="b">
         <v>0</v>
       </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr">
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr">
         <is>
           <t xml:space="preserve">{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7600955886223232277', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSannqcDU/', 'input': 'https://vt.tiktok.com/ZSannqcDU/', 'cid': '7601033369098896136', 'createTime': 1769753502, 'createTimeISO': '2026-01-30T06:11:42.000Z', 'text': 'Gabiiiii que deli tu receta la copiare ame el yogur Griego casero de @Alpina 🐮 de otro planeta 🥰', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, </t>
         </is>
@@ -2320,13 +2355,14 @@
       <c r="M32" t="b">
         <v>0</v>
       </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr">
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7600955886223232277', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSannqcDU/', 'input': 'https://vt.tiktok.com/ZSannqcDU/', 'cid': '7600981628773204757', 'createTime': 1769741632, 'createTimeISO': '2026-01-30T02:53:52.000Z', 'text': 'todo lo de alpina y las recetas estan🤤😋💙✨', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 4, 'uid': '7467024639018468360', 'uniqueId': 'leidy.yuliet</t>
         </is>
@@ -2380,13 +2416,14 @@
       <c r="M33" t="b">
         <v>0</v>
       </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr">
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7600955886223232277', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSannqcDU/', 'input': 'https://vt.tiktok.com/ZSannqcDU/', 'cid': '7600979599431025429', 'createTime': 1769741198, 'createTimeISO': '2026-01-30T02:46:38.000Z', 'text': '😋🥰💙', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7467024639018468360', 'uniqueId': 'leidy.yulieth22', 'avatarThumbnail': 'https://p16-</t>
         </is>
@@ -2440,13 +2477,14 @@
       <c r="M34" t="b">
         <v>0</v>
       </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr">
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7600955886223232277', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSannqcDU/', 'input': 'https://vt.tiktok.com/ZSannqcDU/', 'cid': '7600979263550817045', 'createTime': 1769741086, 'createTimeISO': '2026-01-30T02:44:46.000Z', 'text': 'gaby es cierto que mañana ya podemos conseguir los aqua mochis en tiendas y supermercados????????', 'diggCount': 2, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0,</t>
         </is>
@@ -2500,13 +2538,14 @@
       <c r="M35" t="b">
         <v>0</v>
       </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr">
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7600955886223232277', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSannqcDU/', 'input': 'https://vt.tiktok.com/ZSannqcDU/', 'cid': '7600977406539612948', 'createTime': 1769740681, 'createTimeISO': '2026-01-30T02:38:01.000Z', 'text': 'gabyyy y los AQUA MOCHIS?????? quiero que los anunciessss yaaa por faaaaaaaaaaa🥺😭💙', 'diggCount': 2, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '746702</t>
         </is>
@@ -2560,13 +2599,14 @@
       <c r="M36" t="b">
         <v>0</v>
       </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr">
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7600955886223232277', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSannqcDU/', 'input': 'https://vt.tiktok.com/ZSannqcDU/', 'cid': '7600963433807495956', 'createTime': 1769737232, 'createTimeISO': '2026-01-30T01:40:32.000Z', 'text': 'alpinaaaa los mochisssss porfisssss🙏🏻🙏🏻🙏🏻🙏🏻💗💗💗💗', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7545202271677924359', 'uniqueId': 'sofia.</t>
         </is>
@@ -2620,13 +2660,14 @@
       <c r="M37" t="b">
         <v>0</v>
       </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr">
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7600955886223232277', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSannqcDU/', 'input': 'https://vt.tiktok.com/ZSannqcDU/', 'cid': '7600962044775301908', 'createTime': 1769736910, 'createTimeISO': '2026-01-30T01:35:10.000Z', 'text': 'Alpina por favor los mochisssss 🥹🥹', 'diggCount': 2, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7438960899258598455', 'uniqueId': 'ospinajimena2', 'av</t>
         </is>
@@ -2680,13 +2721,14 @@
       <c r="M38" t="b">
         <v>0</v>
       </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr">
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7600955886223232277', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSannqcDU/', 'input': 'https://vt.tiktok.com/ZSannqcDU/', 'cid': '7600957864790197000', 'createTime': 1769735927, 'createTimeISO': '2026-01-30T01:18:47.000Z', 'text': 'siento y se ve que es delicioso🤤😯', 'diggCount': 2, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 2, 'uid': '7505793601163674642', 'uniqueId': 'mariangel6169', 'ava</t>
         </is>
@@ -2740,13 +2782,14 @@
       <c r="M39" t="b">
         <v>0</v>
       </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr">
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7600955886223232277', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSannqcDU/', 'input': 'https://vt.tiktok.com/ZSannqcDU/', 'cid': '7600955753084863239', 'createTime': 1769735757, 'createTimeISO': '2026-01-30T01:15:57.000Z', 'text': 'gaby los mochissss ☺️🤣', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7587684360884077576', 'uniqueId': 'miguelcardona998', 'avatarThumb</t>
         </is>
@@ -2800,13 +2843,14 @@
       <c r="M40" t="b">
         <v>0</v>
       </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr">
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7600955886223232277', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSannqcDU/', 'input': 'https://vt.tiktok.com/ZSannqcDU/', 'cid': '7600955758550123282', 'createTime': 1769735729, 'createTimeISO': '2026-01-30T01:15:29.000Z', 'text': 'Gaby son aqua Mochis ?☺️☺️yo creo q si', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '7587684360884077576', 'uniqueId': 'miguelcardona99</t>
         </is>
@@ -2860,13 +2904,14 @@
       <c r="M41" t="b">
         <v>0</v>
       </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr">
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr">
         <is>
           <t xml:space="preserve">{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7600955886223232277', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSannqcDU/', 'input': 'https://vt.tiktok.com/ZSannqcDU/', 'cid': '7600955752375370504', 'createTime': 1769735699, 'createTimeISO': '2026-01-30T01:14:59.000Z', 'text': 'Gaby pensé q el próximo video anunsiabas los siguientes mochis 😅☺️', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7587684360884077576', </t>
         </is>
@@ -2920,13 +2965,14 @@
       <c r="M42" t="b">
         <v>0</v>
       </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr">
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7600955886223232277', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSannqcDU/', 'input': 'https://vt.tiktok.com/ZSannqcDU/', 'cid': '7600956815049229076', 'createTime': 1769735694, 'createTimeISO': '2026-01-30T01:14:54.000Z', 'text': '🥰🥰🥰', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7511416596604437522', 'uniqueId': 'jeronimosanmiguel4', 'avatarThumbnail': 'https://p</t>
         </is>
@@ -2980,13 +3026,14 @@
       <c r="M43" t="b">
         <v>0</v>
       </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr">
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7600955886223232277', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSannqcDU/', 'input': 'https://vt.tiktok.com/ZSannqcDU/', 'cid': '7600956719275000592', 'createTime': 1769735658, 'createTimeISO': '2026-01-30T01:14:18.000Z', 'text': 'wow qué rico', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7568684553474360321', 'uniqueId': 'samuel.florez500', 'avatarThumbnail': 'ht</t>
         </is>
@@ -3027,12 +3074,13 @@
         <v>0</v>
       </c>
       <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr">
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
         <is>
           <t>FAILED</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -3069,12 +3117,13 @@
         <v>0</v>
       </c>
       <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr">
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
         <is>
           <t>FAILED</t>
         </is>
       </c>
-      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -3124,13 +3173,14 @@
       <c r="M46" t="b">
         <v>0</v>
       </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr">
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7607261475942220545', 'createTime': 1771203612, 'createTimeISO': '2026-02-16T01:00:12.000Z', 'text': 'yo tengo todos los q a salido pq mi mm me los tare ya q trabaja en alpina', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '695597863502037</t>
         </is>
@@ -3184,13 +3234,14 @@
       <c r="M47" t="b">
         <v>0</v>
       </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr">
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7607210527748162311', 'createTime': 1771191742, 'createTimeISO': '2026-02-15T21:42:22.000Z', 'text': 'sos', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7593056634043204615', 'uniqueId': 'la.bubu8556', 'avatarThumbnail': 'https://p16-comm</t>
         </is>
@@ -3244,13 +3295,14 @@
       <c r="M48" t="b">
         <v>0</v>
       </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr">
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7607177720812339975', 'createTime': 1771184098, 'createTimeISO': '2026-02-15T19:34:58.000Z', 'text': 'Hola alpina te amo', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7587775700880606225', 'uniqueId': 'christopher.castr002', 'avatarThumb</t>
         </is>
@@ -3304,13 +3356,14 @@
       <c r="M49" t="b">
         <v>0</v>
       </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr">
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7607175055629435665', 'createTime': 1771183482, 'createTimeISO': '2026-02-15T19:24:42.000Z', 'text': 'una pío pío rojo agua Mochis 🥳🥳🥳', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7597509511503299601', 'uniqueId': 'daniel.zabala476', 'a</t>
         </is>
@@ -3364,13 +3417,14 @@
       <c r="M50" t="b">
         <v>0</v>
       </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr">
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7607172648293171969', 'createTime': 1771182931, 'createTimeISO': '2026-02-15T19:15:31.000Z', 'text': ' [sticker]', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7498893686404875319', 'uniqueId': 'amypalacioserrera', 'avatarThumbnail': 'htt</t>
         </is>
@@ -3424,13 +3478,14 @@
       <c r="M51" t="b">
         <v>0</v>
       </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr">
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7607160512694174482', 'createTime': 1771180086, 'createTimeISO': '2026-02-15T18:28:06.000Z', 'text': 'tengo dos dinosaurios, tres de Navidad y dos del mar. ya estoy obsesionada', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '73319522321483</t>
         </is>
@@ -3484,13 +3539,14 @@
       <c r="M52" t="b">
         <v>0</v>
       </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr">
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7607149095819445012', 'createTime': 1771177428, 'createTimeISO': '2026-02-15T17:43:48.000Z', 'text': 'Pueden ver la lista oficial en mi perfil 🥰', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6942672037790041094', 'uniqueId': 'hola.soy.an</t>
         </is>
@@ -3544,13 +3600,14 @@
       <c r="M53" t="b">
         <v>0</v>
       </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr">
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7607146486328984338', 'createTime': 1771176819, 'createTimeISO': '2026-02-15T17:33:39.000Z', 'text': 'Muy caro', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6957546666179200005', 'uniqueId': 'amarillo987', 'avatarThumbnail': 'https://p16</t>
         </is>
@@ -3605,13 +3662,14 @@
       <c r="M54" t="b">
         <v>0</v>
       </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr">
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7607145092734976776', 'createTime': 1771176500, 'createTimeISO': '2026-02-15T17:28:20.000Z', 'text': 'Ami seme derritieron todos 😭💔\n(nose por que)', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7471458807811327031', 'uniqueId': 'robloxia</t>
         </is>
@@ -3665,13 +3723,14 @@
       <c r="M55" t="b">
         <v>0</v>
       </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr">
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7607131662543192852', 'createTime': 1771173370, 'createTimeISO': '2026-02-15T16:36:10.000Z', 'text': 'porque ahora solo asen Mochis', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7582793117721527304', 'uniqueId': 'joangamer19904', 'avatar</t>
         </is>
@@ -3725,13 +3784,14 @@
       <c r="M56" t="b">
         <v>0</v>
       </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr">
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7607131081683649300', 'createTime': 1771173239, 'createTimeISO': '2026-02-15T16:33:59.000Z', 'text': 'Nooo otra vez nooo', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6806838285697106950', 'uniqueId': 'monicacifuentes4', 'avatarThumbnail</t>
         </is>
@@ -3785,13 +3845,14 @@
       <c r="M57" t="b">
         <v>0</v>
       </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O57" t="inlineStr"/>
-      <c r="P57" t="inlineStr">
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7607123785518777109', 'createTime': 1771171536, 'createTimeISO': '2026-02-15T16:05:36.000Z', 'text': 'alpina hay mantarraya???', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7298821580599329797', 'uniqueId': 'davidcardenas09', 'avatarThum</t>
         </is>
@@ -3845,13 +3906,14 @@
       <c r="M58" t="b">
         <v>0</v>
       </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O58" t="inlineStr"/>
-      <c r="P58" t="inlineStr">
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7607115112029930248', 'createTime': 1771169516, 'createTimeISO': '2026-02-15T15:31:56.000Z', 'text': 'perfecto para mi pecera 😁', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7398844929906623493', 'uniqueId': 'danilo.alvarez_', 'avatarThu</t>
         </is>
@@ -3905,13 +3967,14 @@
       <c r="M59" t="b">
         <v>0</v>
       </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O59" t="inlineStr"/>
-      <c r="P59" t="inlineStr">
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7607110027069768455', 'createTime': 1771168333, 'createTimeISO': '2026-02-15T15:12:13.000Z', 'text': 'alpina regaleme los mochis', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7449505731574760453', 'uniqueId': 'bassielol10', 'avatarThumbn</t>
         </is>
@@ -3965,13 +4028,14 @@
       <c r="M60" t="b">
         <v>0</v>
       </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O60" t="inlineStr"/>
-      <c r="P60" t="inlineStr">
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr">
         <is>
           <t xml:space="preserve">{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7607102555449737991', 'createTime': 1771166591, 'createTimeISO': '2026-02-15T14:43:11.000Z', 'text': 'se pueden meter en el agua o se dañan?', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6843576266509108229', 'uniqueId': 'edwinperilla', </t>
         </is>
@@ -4025,13 +4089,14 @@
       <c r="M61" t="b">
         <v>0</v>
       </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr">
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606968952678417159', 'createTime': 1771135495, 'createTimeISO': '2026-02-15T06:04:55.000Z', 'text': 'amo los Mochis [sticker]', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7358029087606588422', 'uniqueId': 'gabis_ortis', 'avatarThumbnai</t>
         </is>
@@ -4085,13 +4150,14 @@
       <c r="M62" t="b">
         <v>0</v>
       </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O62" t="inlineStr"/>
-      <c r="P62" t="inlineStr">
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606947532074091271', 'createTime': 1771130506, 'createTimeISO': '2026-02-15T04:41:46.000Z', 'text': 'Metan lo muñequitos que hacían antes [sticker]', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7452207058546181126', 'uniqueId': 'miguela</t>
         </is>
@@ -4145,13 +4211,14 @@
       <c r="M63" t="b">
         <v>0</v>
       </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O63" t="inlineStr"/>
-      <c r="P63" t="inlineStr">
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606918182959694613', 'createTime': 1771123668, 'createTimeISO': '2026-02-15T02:47:48.000Z', 'text': 'yo ya tengo uno👺 [sticker]', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7578869395050775570', 'uniqueId': 'sharik_rodriguez2', 'avatar</t>
         </is>
@@ -4205,13 +4272,14 @@
       <c r="M64" t="b">
         <v>0</v>
       </c>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O64" t="inlineStr"/>
-      <c r="P64" t="inlineStr">
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606902021753586452', 'createTime': 1771119916, 'createTimeISO': '2026-02-15T01:45:16.000Z', 'text': 'y muchas piedras', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7219811811126117382', 'uniqueId': 'maricel.1921', 'avatarThumbnail': 'ht</t>
         </is>
@@ -4265,13 +4333,14 @@
       <c r="M65" t="b">
         <v>0</v>
       </c>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O65" t="inlineStr"/>
-      <c r="P65" t="inlineStr">
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606896084937540373', 'createTime': 1771118528, 'createTimeISO': '2026-02-15T01:22:08.000Z', 'text': '@𝘀𝗸𝗶𝗯𝗶𝗱𝗶𝘀𝗼𝗳 mochis del aguaaaaaaaaaaaaa', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7319063244818859014', 'uniqueId': 'zapynushin', '</t>
         </is>
@@ -4325,13 +4394,14 @@
       <c r="M66" t="b">
         <v>0</v>
       </c>
-      <c r="N66" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O66" t="inlineStr"/>
-      <c r="P66" t="inlineStr">
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606860679941702421', 'createTime': 1771110301, 'createTimeISO': '2026-02-14T23:05:01.000Z', 'text': 'TODOS A LAS CALLES 17 DE FEBRERO POR UNA VIDA DIGNA, NO A LA BAJA DEL SALARIO MINIMO VITAL', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid':</t>
         </is>
@@ -4385,13 +4455,14 @@
       <c r="M67" t="b">
         <v>0</v>
       </c>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O67" t="inlineStr"/>
-      <c r="P67" t="inlineStr">
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606842411357422354', 'createTime': 1771106038, 'createTimeISO': '2026-02-14T21:53:58.000Z', 'text': 'los amoooo, déjenlo mucho tiempo por favor 🥰🥰', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7151105819618362374', 'uniqueId': 'pau15838</t>
         </is>
@@ -4445,13 +4516,14 @@
       <c r="M68" t="b">
         <v>0</v>
       </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O68" t="inlineStr"/>
-      <c r="P68" t="inlineStr">
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606830870297330453', 'createTime': 1771103349, 'createTimeISO': '2026-02-14T21:09:09.000Z', 'text': 'Alpina te ama🌟 y te piensa mucho', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7090696448391873542', 'uniqueId': 'twice_tofu', 'avatarT</t>
         </is>
@@ -4505,13 +4577,14 @@
       <c r="M69" t="b">
         <v>0</v>
       </c>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O69" t="inlineStr"/>
-      <c r="P69" t="inlineStr">
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606830782704157460', 'createTime': 1771103337, 'createTimeISO': '2026-02-14T21:08:57.000Z', 'text': 'esto es arteeee', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7090696448391873542', 'uniqueId': 'twice_tofu', 'avatarThumbnail': 'https</t>
         </is>
@@ -4565,13 +4638,14 @@
       <c r="M70" t="b">
         <v>0</v>
       </c>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O70" t="inlineStr"/>
-      <c r="P70" t="inlineStr">
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606830779751138069', 'createTime': 1771103331, 'createTimeISO': '2026-02-14T21:08:51.000Z', 'text': 'arteeee', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7090696448391873542', 'uniqueId': 'twice_tofu', 'avatarThumbnail': 'https://p16-c</t>
         </is>
@@ -4625,13 +4699,14 @@
       <c r="M71" t="b">
         <v>0</v>
       </c>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O71" t="inlineStr"/>
-      <c r="P71" t="inlineStr">
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr"/>
+      <c r="Q71" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606816669142385424', 'createTime': 1771100040, 'createTimeISO': '2026-02-14T20:14:00.000Z', 'text': 'hay en el ara?', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6888066902696018950', 'uniqueId': 'alguienramdon78', 'avatarThumbnail': 'h</t>
         </is>
@@ -4685,13 +4760,14 @@
       <c r="M72" t="b">
         <v>0</v>
       </c>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O72" t="inlineStr"/>
-      <c r="P72" t="inlineStr">
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr"/>
+      <c r="Q72" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606790296471421716', 'createTime': 1771093895, 'createTimeISO': '2026-02-14T18:31:35.000Z', 'text': 'oye alpina hay mantarraya??', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7298821580599329797', 'uniqueId': 'davidcardenas09', 'avatarT</t>
         </is>
@@ -4745,13 +4821,14 @@
       <c r="M73" t="b">
         <v>0</v>
       </c>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O73" t="inlineStr"/>
-      <c r="P73" t="inlineStr">
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr"/>
+      <c r="Q73" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606790208725730068', 'createTime': 1771093871, 'createTimeISO': '2026-02-14T18:31:11.000Z', 'text': 'oye alpina hay mantarraya???', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7298821580599329797', 'uniqueId': 'davidcardenas09', 'avatar</t>
         </is>
@@ -4805,13 +4882,14 @@
       <c r="M74" t="b">
         <v>0</v>
       </c>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O74" t="inlineStr"/>
-      <c r="P74" t="inlineStr">
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606788244819215122', 'createTime': 1771093416, 'createTimeISO': '2026-02-14T18:23:36.000Z', 'text': ' [sticker]', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7138274941577937925', 'uniqueId': 'unknown_user_g404', 'avatarThumbnail': 'htt</t>
         </is>
@@ -4865,13 +4943,14 @@
       <c r="M75" t="b">
         <v>0</v>
       </c>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O75" t="inlineStr"/>
-      <c r="P75" t="inlineStr">
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr"/>
+      <c r="Q75" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606782063303508737', 'createTime': 1771091971, 'createTimeISO': '2026-02-14T17:59:31.000Z', 'text': '2025', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7419337733036999685', 'uniqueId': 'saka019283', 'avatarThumbnail': 'https://p16-sign</t>
         </is>
@@ -4925,13 +5004,14 @@
       <c r="M76" t="b">
         <v>0</v>
       </c>
-      <c r="N76" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O76" t="inlineStr"/>
-      <c r="P76" t="inlineStr">
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606764253924967176', 'createTime': 1771087831, 'createTimeISO': '2026-02-14T16:50:31.000Z', 'text': 'y como saben si no se puede ver?', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6847655935771558917', 'uniqueId': 'hancel....la...h', 'a</t>
         </is>
@@ -4985,13 +5065,14 @@
       <c r="M77" t="b">
         <v>0</v>
       </c>
-      <c r="N77" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O77" t="inlineStr"/>
-      <c r="P77" t="inlineStr">
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606758103325426439', 'createTime': 1771086393, 'createTimeISO': '2026-02-14T16:26:33.000Z', 'text': 'ellos están sobre explotando porque la primera vez que hicieron eso le salió re bien', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7488</t>
         </is>
@@ -5045,13 +5126,14 @@
       <c r="M78" t="b">
         <v>0</v>
       </c>
-      <c r="N78" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O78" t="inlineStr"/>
-      <c r="P78" t="inlineStr">
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr"/>
+      <c r="Q78" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606753762271019796', 'createTime': 1771085382, 'createTimeISO': '2026-02-14T16:09:42.000Z', 'text': 'Quiero!!! 🥰', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7412745403223163909', 'uniqueId': 'tdboreas', 'avatarThumbnail': 'https://p19</t>
         </is>
@@ -5105,13 +5187,14 @@
       <c r="M79" t="b">
         <v>0</v>
       </c>
-      <c r="N79" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O79" t="inlineStr"/>
-      <c r="P79" t="inlineStr">
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606748746374120212', 'createTime': 1771084215, 'createTimeISO': '2026-02-14T15:50:15.000Z', 'text': 'amor', 'diggCount': 2, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7024651547277100037', 'uniqueId': 'maicolcepaa0520', 'avatarThumbnail': 'https://p16</t>
         </is>
@@ -5165,13 +5248,14 @@
       <c r="M80" t="b">
         <v>0</v>
       </c>
-      <c r="N80" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O80" t="inlineStr"/>
-      <c r="P80" t="inlineStr">
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606727932404417298', 'createTime': 1771079367, 'createTimeISO': '2026-02-14T14:29:27.000Z', 'text': 'Una pregunta cuántas focas hay en la nueva colección de aquamochis?', 'diggCount': 2, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7443532287475598391',</t>
         </is>
@@ -5225,13 +5309,14 @@
       <c r="M81" t="b">
         <v>0</v>
       </c>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O81" t="inlineStr"/>
-      <c r="P81" t="inlineStr">
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606727884686476050', 'createTime': 1771079356, 'createTimeISO': '2026-02-14T14:29:16.000Z', 'text': 'juguetes que terminaran en lo más profundo del océano...', 'diggCount': 8, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6786307716072866822', 'uniqueId'</t>
         </is>
@@ -5285,13 +5370,14 @@
       <c r="M82" t="b">
         <v>0</v>
       </c>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O82" t="inlineStr"/>
-      <c r="P82" t="inlineStr">
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr"/>
+      <c r="Q82" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606672707526771464', 'createTime': 1771066510, 'createTimeISO': '2026-02-14T10:55:10.000Z', 'text': '∞', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7545226599298352144', 'uniqueId': 'antocc13', 'avatarThumbnail': 'https://p16-common-si</t>
         </is>
@@ -5345,13 +5431,14 @@
       <c r="M83" t="b">
         <v>0</v>
       </c>
-      <c r="N83" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O83" t="inlineStr"/>
-      <c r="P83" t="inlineStr">
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr"/>
+      <c r="Q83" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606598502535774994', 'createTime': 1771049239, 'createTimeISO': '2026-02-14T06:07:19.000Z', 'text': 'tengo 143', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7569266375668794386', 'uniqueId': 'cata.rojas743', 'avatarThumbnail': 'https://</t>
         </is>
@@ -5405,13 +5492,14 @@
       <c r="M84" t="b">
         <v>0</v>
       </c>
-      <c r="N84" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O84" t="inlineStr"/>
-      <c r="P84" t="inlineStr">
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr"/>
+      <c r="Q84" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606575506917638913', 'createTime': 1771043890, 'createTimeISO': '2026-02-14T04:38:10.000Z', 'text': '@Alpina 🐮 que vuelvan los muñequitos de antes de series o algo así como los guerreros', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '665</t>
         </is>
@@ -5465,13 +5553,14 @@
       <c r="M85" t="b">
         <v>0</v>
       </c>
-      <c r="N85" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O85" t="inlineStr"/>
-      <c r="P85" t="inlineStr">
+      <c r="N85" t="inlineStr"/>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr"/>
+      <c r="Q85" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606523638166913812', 'createTime': 1771031816, 'createTimeISO': '2026-02-14T01:16:56.000Z', 'text': 'yo tengo 5.😁', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7427283654273844229', 'uniqueId': 'pedro.nemoga6', 'avatarThumbnail': 'https</t>
         </is>
@@ -5525,13 +5614,14 @@
       <c r="M86" t="b">
         <v>0</v>
       </c>
-      <c r="N86" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O86" t="inlineStr"/>
-      <c r="P86" t="inlineStr">
+      <c r="N86" t="inlineStr"/>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr"/>
+      <c r="Q86" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606439786600989461', 'createTime': 1771012282, 'createTimeISO': '2026-02-13T19:51:22.000Z', 'text': 'Ya tengo todos', 'diggCount': 3, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7131053865117533190', 'uniqueId': 'maria.teresa.card87', 'avatarThumbnail'</t>
         </is>
@@ -5585,13 +5675,14 @@
       <c r="M87" t="b">
         <v>0</v>
       </c>
-      <c r="N87" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O87" t="inlineStr"/>
-      <c r="P87" t="inlineStr">
+      <c r="N87" t="inlineStr"/>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr"/>
+      <c r="Q87" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606439434900865813', 'createTime': 1771012205, 'createTimeISO': '2026-02-13T19:50:05.000Z', 'text': 'hola regalame todos plis🙏', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7576484586520216584', 'uniqueId': 'osita1941', 'avatarThumbnail</t>
         </is>
@@ -5645,13 +5736,14 @@
       <c r="M88" t="b">
         <v>0</v>
       </c>
-      <c r="N88" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O88" t="inlineStr"/>
-      <c r="P88" t="inlineStr">
+      <c r="N88" t="inlineStr"/>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr"/>
+      <c r="Q88" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606405974844293908', 'createTime': 1771004406, 'createTimeISO': '2026-02-13T17:40:06.000Z', 'text': 'Isaporahi eres tu ? el.que entendió entendió', 'diggCount': 2, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6843103869150741509', 'uniqueId': 'provocavi</t>
         </is>
@@ -5705,13 +5797,14 @@
       <c r="M89" t="b">
         <v>0</v>
       </c>
-      <c r="N89" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O89" t="inlineStr"/>
-      <c r="P89" t="inlineStr">
+      <c r="N89" t="inlineStr"/>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr"/>
+      <c r="Q89" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606387993427985170', 'createTime': 1771000219, 'createTimeISO': '2026-02-13T16:30:19.000Z', 'text': 'saque los ya yo esperé el de navidad y no llego [sticker]', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '7582376729450349588', 'uniqueId</t>
         </is>
@@ -5765,13 +5858,14 @@
       <c r="M90" t="b">
         <v>0</v>
       </c>
-      <c r="N90" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O90" t="inlineStr"/>
-      <c r="P90" t="inlineStr">
+      <c r="N90" t="inlineStr"/>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr"/>
+      <c r="Q90" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606351356999615240', 'createTime': 1770991689, 'createTimeISO': '2026-02-13T14:08:09.000Z', 'text': 'no esta la foca a mi hijo le dalio la foco es preciosa 🥺 le compro solo porque a mi tambien me gusta el las olvida y yo las colecciono pero🤫', 'diggCount': 2, 'likedByAuthor': False, 'pinnedByAuthor': False, '</t>
         </is>
@@ -5825,13 +5919,14 @@
       <c r="M91" t="b">
         <v>0</v>
       </c>
-      <c r="N91" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O91" t="inlineStr"/>
-      <c r="P91" t="inlineStr">
+      <c r="N91" t="inlineStr"/>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr"/>
+      <c r="Q91" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606331029511602965', 'createTime': 1770986962, 'createTimeISO': '2026-02-13T12:49:22.000Z', 'text': '😏😏😏', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6856804310517842950', 'uniqueId': 'sanpaparu75', 'avatarThumbnail': 'https://p16-comm</t>
         </is>
@@ -5885,13 +5980,14 @@
       <c r="M92" t="b">
         <v>0</v>
       </c>
-      <c r="N92" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O92" t="inlineStr"/>
-      <c r="P92" t="inlineStr">
+      <c r="N92" t="inlineStr"/>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr"/>
+      <c r="Q92" t="inlineStr">
         <is>
           <t xml:space="preserve">{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606319986450678546', 'createTime': 1770984390, 'createTimeISO': '2026-02-13T12:06:30.000Z', 'text': 'Hola alpina tengo un pequeño negocio en crecimiento gracias a Dios donde puedo comprar los productos de alpina para venderlos?', 'diggCount': 5, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': </t>
         </is>
@@ -5945,13 +6041,14 @@
       <c r="M93" t="b">
         <v>0</v>
       </c>
-      <c r="N93" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O93" t="inlineStr"/>
-      <c r="P93" t="inlineStr">
+      <c r="N93" t="inlineStr"/>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr"/>
+      <c r="Q93" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606234181786485521', 'createTime': 1770964423, 'createTimeISO': '2026-02-13T06:33:43.000Z', 'text': '🙄\U0001faea', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7577226738905596946', 'uniqueId': 'tingui913', 'avatarThumbnail': 'https://p1</t>
         </is>
@@ -6005,13 +6102,14 @@
       <c r="M94" t="b">
         <v>0</v>
       </c>
-      <c r="N94" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O94" t="inlineStr"/>
-      <c r="P94" t="inlineStr">
+      <c r="N94" t="inlineStr"/>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr"/>
+      <c r="Q94" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606178321075831560', 'createTime': 1770951402, 'createTimeISO': '2026-02-13T02:56:42.000Z', 'text': 'De lo mejor', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7238758478402094086', 'uniqueId': 'user1622760006000', 'avatarThumbnail': 'ht</t>
         </is>
@@ -6065,13 +6163,14 @@
       <c r="M95" t="b">
         <v>0</v>
       </c>
-      <c r="N95" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O95" t="inlineStr"/>
-      <c r="P95" t="inlineStr">
+      <c r="N95" t="inlineStr"/>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr"/>
+      <c r="Q95" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606166729261990664', 'createTime': 1770948712, 'createTimeISO': '2026-02-13T02:11:52.000Z', 'text': 'Extraño a mi ex', 'diggCount': 5, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7512221394000872456', 'uniqueId': 'papas.con.arroz35', 'avatarThumbnail':</t>
         </is>
@@ -6125,13 +6224,14 @@
       <c r="M96" t="b">
         <v>0</v>
       </c>
-      <c r="N96" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O96" t="inlineStr"/>
-      <c r="P96" t="inlineStr">
+      <c r="N96" t="inlineStr"/>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr"/>
+      <c r="Q96" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606154497101988624', 'createTime': 1770945870, 'createTimeISO': '2026-02-13T01:24:30.000Z', 'text': 'Yo escuché al principio Elon musk.', 'diggCount': 2, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7531452720693675014', 'uniqueId': 'jamifyapp', 'avatar</t>
         </is>
@@ -6185,13 +6285,14 @@
       <c r="M97" t="b">
         <v>0</v>
       </c>
-      <c r="N97" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O97" t="inlineStr"/>
-      <c r="P97" t="inlineStr">
+      <c r="N97" t="inlineStr"/>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr"/>
+      <c r="Q97" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606141431102784277', 'createTime': 1770942820, 'createTimeISO': '2026-02-13T00:33:40.000Z', 'text': 'lo más hermoso que he visto hoy', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7242097318991037445', 'uniqueId': 'noreidismaria', 'avata</t>
         </is>
@@ -6245,13 +6346,14 @@
       <c r="M98" t="b">
         <v>0</v>
       </c>
-      <c r="N98" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O98" t="inlineStr"/>
-      <c r="P98" t="inlineStr">
+      <c r="N98" t="inlineStr"/>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr"/>
+      <c r="Q98" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606128082316460808', 'createTime': 1770939724, 'createTimeISO': '2026-02-12T23:42:04.000Z', 'text': '@𝐸𝑠𝑝𝑖𝑛𝑜𝑠𝑎 @Andres Alzate', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7183578757004854277', 'uniqueId': 'castro_01010', 'avatarThumbna</t>
         </is>
@@ -6305,13 +6407,14 @@
       <c r="M99" t="b">
         <v>0</v>
       </c>
-      <c r="N99" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O99" t="inlineStr"/>
-      <c r="P99" t="inlineStr">
+      <c r="N99" t="inlineStr"/>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr"/>
+      <c r="Q99" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606118835406340885', 'createTime': 1770937571, 'createTimeISO': '2026-02-12T23:06:11.000Z', 'text': '🥰🥰🥰🥰', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7511416596604437522', 'uniqueId': 'jeronimosanmiguel4', 'avatarThumbnail': 'https://</t>
         </is>
@@ -6365,13 +6468,14 @@
       <c r="M100" t="b">
         <v>0</v>
       </c>
-      <c r="N100" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O100" t="inlineStr"/>
-      <c r="P100" t="inlineStr">
+      <c r="N100" t="inlineStr"/>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr"/>
+      <c r="Q100" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606101748613169928', 'createTime': 1770933583, 'createTimeISO': '2026-02-12T21:59:43.000Z', 'text': 'quiero el noctopi w', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7449448478445814790', 'uniqueId': 'daren.calderon3', 'avatarThumbnail</t>
         </is>
@@ -6425,13 +6529,14 @@
       <c r="M101" t="b">
         <v>0</v>
       </c>
-      <c r="N101" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O101" t="inlineStr"/>
-      <c r="P101" t="inlineStr">
+      <c r="N101" t="inlineStr"/>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr"/>
+      <c r="Q101" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606088482087600904', 'createTime': 1770930491, 'createTimeISO': '2026-02-12T21:08:11.000Z', 'text': 'pov mochis se quedan sin ideas o ya se un mochi de agua', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7554069625988105223', 'uniqueId':</t>
         </is>
@@ -6485,13 +6590,14 @@
       <c r="M102" t="b">
         <v>0</v>
       </c>
-      <c r="N102" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O102" t="inlineStr"/>
-      <c r="P102" t="inlineStr">
+      <c r="N102" t="inlineStr"/>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr"/>
+      <c r="Q102" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606079011882943250', 'createTime': 1770928296, 'createTimeISO': '2026-02-12T20:31:36.000Z', 'text': 'noooooo otra vez son 40 😭', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7578335295364924434', 'uniqueId': 'santiagodiaz3487', 'avatarTh</t>
         </is>
@@ -6545,13 +6651,14 @@
       <c r="M103" t="b">
         <v>0</v>
       </c>
-      <c r="N103" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O103" t="inlineStr"/>
-      <c r="P103" t="inlineStr">
+      <c r="N103" t="inlineStr"/>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr"/>
+      <c r="Q103" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606063681915749141', 'createTime': 1770924722, 'createTimeISO': '2026-02-12T19:32:02.000Z', 'text': 'YA PAREEEEEN', 'diggCount': 24, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 4, 'uid': '7483155009288733717', 'uniqueId': 'limoncito3333', 'avatarThumbnail': 'http</t>
         </is>
@@ -6605,13 +6712,14 @@
       <c r="M104" t="b">
         <v>0</v>
       </c>
-      <c r="N104" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O104" t="inlineStr"/>
-      <c r="P104" t="inlineStr">
+      <c r="N104" t="inlineStr"/>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr"/>
+      <c r="Q104" t="inlineStr">
         <is>
           <t xml:space="preserve">{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606049388909953810', 'createTime': 1770921388, 'createTimeISO': '2026-02-12T18:36:28.000Z', 'text': 'Alpina ayuda yo estoy emocionada por que estoy acá desde los Mochis , ilumi Mochis, mini Mochis, los Mochis para la maleta, dino Mochis, jojo Mochis, y ahora los aqua Mochis no te miento no los pude conseguir </t>
         </is>
@@ -6665,13 +6773,14 @@
       <c r="M105" t="b">
         <v>0</v>
       </c>
-      <c r="N105" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O105" t="inlineStr"/>
-      <c r="P105" t="inlineStr">
+      <c r="N105" t="inlineStr"/>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr"/>
+      <c r="Q105" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606044275377652501', 'createTime': 1770920196, 'createTimeISO': '2026-02-12T18:16:36.000Z', 'text': 'Yo tengo 6🫧', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7321136002860008454', 'uniqueId': 'gatobias.y.titosaurio', 'avatarThumbnail':</t>
         </is>
@@ -6725,13 +6834,14 @@
       <c r="M106" t="b">
         <v>0</v>
       </c>
-      <c r="N106" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O106" t="inlineStr"/>
-      <c r="P106" t="inlineStr">
+      <c r="N106" t="inlineStr"/>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr"/>
+      <c r="Q106" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606031806882939669', 'createTime': 1770917296, 'createTimeISO': '2026-02-12T17:28:16.000Z', 'text': 'SOLO ALQUERIA🤪🤪🤪', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7590083135682200597', 'uniqueId': 'andresito0777', 'avatarThumbnail': 'h</t>
         </is>
@@ -6785,13 +6895,14 @@
       <c r="M107" t="b">
         <v>0</v>
       </c>
-      <c r="N107" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O107" t="inlineStr"/>
-      <c r="P107" t="inlineStr">
+      <c r="N107" t="inlineStr"/>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr"/>
+      <c r="Q107" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606021231103673105', 'createTime': 1770914825, 'createTimeISO': '2026-02-12T16:47:05.000Z', 'text': 'hermosa mil bendiciones', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6964522060413436933', 'uniqueId': 'antoniocarlosdomi3', 'avatarTh</t>
         </is>
@@ -6845,13 +6956,14 @@
       <c r="M108" t="b">
         <v>0</v>
       </c>
-      <c r="N108" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O108" t="inlineStr"/>
-      <c r="P108" t="inlineStr">
+      <c r="N108" t="inlineStr"/>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P108" t="inlineStr"/>
+      <c r="Q108" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606018071988634369', 'createTime': 1770914092, 'createTimeISO': '2026-02-12T16:34:52.000Z', 'text': 'sii que hermoso ya los quiero', 'diggCount': 3, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7139507407827567621', 'uniqueId': 'xux400', 'avatarThumbnai</t>
         </is>
@@ -6905,13 +7017,14 @@
       <c r="M109" t="b">
         <v>0</v>
       </c>
-      <c r="N109" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O109" t="inlineStr"/>
-      <c r="P109" t="inlineStr">
+      <c r="N109" t="inlineStr"/>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr"/>
+      <c r="Q109" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606010431609963285', 'createTime': 1770912313, 'createTimeISO': '2026-02-12T16:05:13.000Z', 'text': 'jajaja ya tienen muy quemados los mochos', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6517432558840452111', 'uniqueId': '223345fabio',</t>
         </is>
@@ -6965,13 +7078,14 @@
       <c r="M110" t="b">
         <v>0</v>
       </c>
-      <c r="N110" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O110" t="inlineStr"/>
-      <c r="P110" t="inlineStr">
+      <c r="N110" t="inlineStr"/>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr"/>
+      <c r="Q110" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606008795130921748', 'createTime': 1770911933, 'createTimeISO': '2026-02-12T15:58:53.000Z', 'text': 'dioss mio mi hija tiene todos los dinosaurios, los de navidad jajajaa y ahora salen estos jajajaj', 'diggCount': 10, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 2</t>
         </is>
@@ -7025,13 +7139,14 @@
       <c r="M111" t="b">
         <v>0</v>
       </c>
-      <c r="N111" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O111" t="inlineStr"/>
-      <c r="P111" t="inlineStr">
+      <c r="N111" t="inlineStr"/>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr"/>
+      <c r="Q111" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7605921005799211797', 'createTime': 1770891501, 'createTimeISO': '2026-02-12T10:18:21.000Z', 'text': 'a Mochis amo los Mochis', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7577169276382807048', 'uniqueId': 'sofia18597', 'avatarThumbnail'</t>
         </is>
@@ -7085,13 +7200,14 @@
       <c r="M112" t="b">
         <v>0</v>
       </c>
-      <c r="N112" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O112" t="inlineStr"/>
-      <c r="P112" t="inlineStr">
+      <c r="N112" t="inlineStr"/>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P112" t="inlineStr"/>
+      <c r="Q112" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7605919710110106388', 'createTime': 1770891189, 'createTimeISO': '2026-02-12T10:13:09.000Z', 'text': 'yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo</t>
         </is>
@@ -7145,13 +7261,14 @@
       <c r="M113" t="b">
         <v>0</v>
       </c>
-      <c r="N113" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O113" t="inlineStr"/>
-      <c r="P113" t="inlineStr">
+      <c r="N113" t="inlineStr"/>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr"/>
+      <c r="Q113" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7605916734050026248', 'createTime': 1770890495, 'createTimeISO': '2026-02-12T10:01:35.000Z', 'text': 'mi hija me hizo comprar todos los de dinosaurios, navidad ,y ahora sacan sus favoritos 🥴🥴 animales marinos 🥴🤣🤣🤣', 'diggCount': 14, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCo</t>
         </is>
@@ -7205,13 +7322,14 @@
       <c r="M114" t="b">
         <v>0</v>
       </c>
-      <c r="N114" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O114" t="inlineStr"/>
-      <c r="P114" t="inlineStr">
+      <c r="N114" t="inlineStr"/>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P114" t="inlineStr"/>
+      <c r="Q114" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7605912711730856705', 'createTime': 1770889565, 'createTimeISO': '2026-02-12T09:46:05.000Z', 'text': 'yo quiero', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7336195362929787910', 'uniqueId': 'melany.noriega30', 'avatarThumbnail': 'https</t>
         </is>
@@ -7265,13 +7383,14 @@
       <c r="M115" t="b">
         <v>0</v>
       </c>
-      <c r="N115" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="O115" t="inlineStr"/>
-      <c r="P115" t="inlineStr">
+      <c r="N115" t="inlineStr"/>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P115" t="inlineStr"/>
+      <c r="Q115" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7605890624642024212', 'createTime': 1770884424, 'createTimeISO': '2026-02-12T08:20:24.000Z', 'text': 'Yo quirooooo 🥺', 'diggCount': 2, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6573387218701811717', 'uniqueId': 'papita_0401', 'avatarThumbnail': 'https</t>
         </is>
@@ -7331,13 +7450,14 @@
       <c r="M116" t="b">
         <v>0</v>
       </c>
-      <c r="N116" t="inlineStr">
+      <c r="N116" t="inlineStr"/>
+      <c r="O116" t="inlineStr">
         <is>
           <t>https://instagram.com/mm.____.3x</t>
         </is>
       </c>
-      <c r="O116" t="inlineStr"/>
-      <c r="P116" t="inlineStr">
+      <c r="P116" t="inlineStr"/>
+      <c r="Q116" t="inlineStr">
         <is>
           <t>{'postUrl': 'https://www.instagram.com/p/DQZl34lDDef/', 'commentUrl': 'https://www.instagram.com/p/DQZl34lDDef/c/17878999155332166', 'id': '17878999155332166', 'text': 'Y esa cosa negra en la pared🤨🤨🤨', 'ownerUsername': 'mm.____.3x', 'ownerProfilePicUrl': 'https://scontent-lga3-3.cdninstagram.com/v/t51.82787-19/621156172_17872637967510128_1309047705098992380_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=104&amp;ig_cache_key=GEwXBiVwqkDNEX8-APw6d8DzqyoSbmNDAQAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=e</t>
         </is>
@@ -7397,13 +7517,14 @@
       <c r="M117" t="b">
         <v>0</v>
       </c>
-      <c r="N117" t="inlineStr">
+      <c r="N117" t="inlineStr"/>
+      <c r="O117" t="inlineStr">
         <is>
           <t>https://instagram.com/luis_dacop</t>
         </is>
       </c>
-      <c r="O117" t="inlineStr"/>
-      <c r="P117" t="inlineStr">
+      <c r="P117" t="inlineStr"/>
+      <c r="Q117" t="inlineStr">
         <is>
           <t>{'postUrl': 'https://www.instagram.com/p/DQZl34lDDef/', 'commentUrl': 'https://www.instagram.com/p/DQZl34lDDef/c/17980855841926100', 'id': '17980855841926100', 'text': 'Dejame negociar el riñón que me sobra 🙄', 'ownerUsername': 'luis_dacop', 'ownerProfilePicUrl': 'https://scontent-lga3-2.cdninstagram.com/v/t51.82787-19/625230176_18095921168313175_2177686544448637796_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=107&amp;ig_cache_key=GGBBRCVX6x75JEpAAGRLAtJfsjgebmNDAQAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=6694</t>
         </is>
@@ -7463,13 +7584,14 @@
       <c r="M118" t="b">
         <v>0</v>
       </c>
-      <c r="N118" t="inlineStr">
+      <c r="N118" t="inlineStr"/>
+      <c r="O118" t="inlineStr">
         <is>
           <t>https://instagram.com/solo.roberto</t>
         </is>
       </c>
-      <c r="O118" t="inlineStr"/>
-      <c r="P118" t="inlineStr">
+      <c r="P118" t="inlineStr"/>
+      <c r="Q118" t="inlineStr">
         <is>
           <t>{'postUrl': 'https://www.instagram.com/p/DQZl34lDDef/', 'commentUrl': 'https://www.instagram.com/p/DQZl34lDDef/c/17869377699399109', 'id': '17869377699399109', 'text': 'No gracias alpina está muy cara !', 'ownerUsername': 'solo.roberto', 'ownerProfilePicUrl': 'https://scontent-lga3-3.cdninstagram.com/v/t51.75761-19/497451179_18462727648079276_6370863006333456058_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=104&amp;ig_cache_key=GKuAph2sbQzDwJdBALrOLmUm2mlYbvEnAQAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;e</t>
         </is>
@@ -7529,13 +7651,14 @@
       <c r="M119" t="b">
         <v>0</v>
       </c>
-      <c r="N119" t="inlineStr">
+      <c r="N119" t="inlineStr"/>
+      <c r="O119" t="inlineStr">
         <is>
           <t>https://instagram.com/jeanb_555</t>
         </is>
       </c>
-      <c r="O119" t="inlineStr"/>
-      <c r="P119" t="inlineStr">
+      <c r="P119" t="inlineStr"/>
+      <c r="Q119" t="inlineStr">
         <is>
           <t>{'postUrl': 'https://www.instagram.com/p/DQZl34lDDef/', 'commentUrl': 'https://www.instagram.com/p/DQZl34lDDef/c/18327825274240575', 'id': '18327825274240575', 'text': 'HaaaaAAA!', 'ownerUsername': 'jeanb_555', 'ownerProfilePicUrl': 'https://scontent-lga3-1.cdninstagram.com/v/t51.82787-19/619082747_17977100765977609_5485987972083477950_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=108&amp;ig_cache_key=GPtz5iQJXD-xE94-AL7tGZ7_JCJMbmNDAQAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InBy</t>
         </is>
@@ -7593,7 +7716,8 @@
       </c>
       <c r="N120" t="inlineStr"/>
       <c r="O120" t="inlineStr"/>
-      <c r="P120" t="inlineStr">
+      <c r="P120" t="inlineStr"/>
+      <c r="Q120" t="inlineStr">
         <is>
           <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/1318637550308481/', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02Ach9AC61BKpdSmgSrgBZzHgfRycCH8earVjLAxMVuaCN4T41xVwKCfGdpD1q7JiCl?comment_id=1123930883027156', 'id': 'Y29tbWVudDoxMzE4NjM4MDUwMzA4NDMxXzExMjM5MzA4ODMwMjcxNTY=', 'feedbackId': 'ZmVlZGJhY2s6MTMxODYzODA1MDMwODQzMV8xMTIzOTMwODgzMDI3MTU2', 'date': '2026-01-18T21:45:53.000Z', 'text': 'Holavivianapaternia', 'profileUrl': 'https://www.facebook.com/people/Juli-X</t>
         </is>
@@ -7651,7 +7775,8 @@
       </c>
       <c r="N121" t="inlineStr"/>
       <c r="O121" t="inlineStr"/>
-      <c r="P121" t="inlineStr">
+      <c r="P121" t="inlineStr"/>
+      <c r="Q121" t="inlineStr">
         <is>
           <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/1318637550308481/', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02Ach9AC61BKpdSmgSrgBZzHgfRycCH8earVjLAxMVuaCN4T41xVwKCfGdpD1q7JiCl?comment_id=1412783150373933', 'id': 'Y29tbWVudDoxMzE4NjM4MDUwMzA4NDMxXzE0MTI3ODMxNTAzNzM5MzM=', 'feedbackId': 'ZmVlZGJhY2s6MTMxODYzODA1MDMwODQzMV8xNDEyNzgzMTUwMzczOTMz', 'date': '2026-01-14T23:51:57.000Z', 'text': 'Salome', 'profileUrl': 'https://www.facebook.com/yhonjairo.mirandaascanio',</t>
         </is>
@@ -7710,7 +7835,8 @@
       </c>
       <c r="N122" t="inlineStr"/>
       <c r="O122" t="inlineStr"/>
-      <c r="P122" t="inlineStr">
+      <c r="P122" t="inlineStr"/>
+      <c r="Q122" t="inlineStr">
         <is>
           <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/1318637550308481/', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02Ach9AC61BKpdSmgSrgBZzHgfRycCH8earVjLAxMVuaCN4T41xVwKCfGdpD1q7JiCl?comment_id=1185407276613695', 'id': 'Y29tbWVudDoxMzE4NjM4MDUwMzA4NDMxXzExODU0MDcyNzY2MTM2OTU=', 'feedbackId': 'ZmVlZGJhY2s6MTMxODYzODA1MDMwODQzMV8xMTg1NDA3Mjc2NjEzNjk1', 'date': '2026-01-11T20:48:42.000Z', 'text': 'Ñ\nÑñ', 'profileUrl': 'https://www.facebook.com/miller.torres.929614', 'pro</t>
         </is>
@@ -7768,7 +7894,8 @@
       </c>
       <c r="N123" t="inlineStr"/>
       <c r="O123" t="inlineStr"/>
-      <c r="P123" t="inlineStr">
+      <c r="P123" t="inlineStr"/>
+      <c r="Q123" t="inlineStr">
         <is>
           <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/1318637550308481/', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02Ach9AC61BKpdSmgSrgBZzHgfRycCH8earVjLAxMVuaCN4T41xVwKCfGdpD1q7JiCl?comment_id=893455673202688', 'id': 'Y29tbWVudDoxMzE4NjM4MDUwMzA4NDMxXzg5MzQ1NTY3MzIwMjY4OA==', 'feedbackId': 'ZmVlZGJhY2s6MTMxODYzODA1MDMwODQzMV84OTM0NTU2NzMyMDI2ODg=', 'date': '2026-01-10T22:35:04.000Z', 'text': 'Bueno', 'profileUrl': 'https://www.facebook.com/nacira.bolanoospino', 'profi</t>
         </is>
@@ -7826,7 +7953,8 @@
       </c>
       <c r="N124" t="inlineStr"/>
       <c r="O124" t="inlineStr"/>
-      <c r="P124" t="inlineStr">
+      <c r="P124" t="inlineStr"/>
+      <c r="Q124" t="inlineStr">
         <is>
           <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/1318637550308481/', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02Ach9AC61BKpdSmgSrgBZzHgfRycCH8earVjLAxMVuaCN4T41xVwKCfGdpD1q7JiCl?comment_id=754375667135961', 'id': 'Y29tbWVudDoxMzE4NjM4MDUwMzA4NDMxXzc1NDM3NTY2NzEzNTk2MQ==', 'feedbackId': 'ZmVlZGJhY2s6MTMxODYzODA1MDMwODQzMV83NTQzNzU2NjcxMzU5NjE=', 'date': '2026-01-10T00:41:55.000Z', 'text': 'Soy onerto', 'profileUrl': 'https://www.facebook.com/manuel.antonio.martinez</t>
         </is>
@@ -7884,7 +8012,8 @@
       </c>
       <c r="N125" t="inlineStr"/>
       <c r="O125" t="inlineStr"/>
-      <c r="P125" t="inlineStr">
+      <c r="P125" t="inlineStr"/>
+      <c r="Q125" t="inlineStr">
         <is>
           <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/1318637550308481/', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02Ach9AC61BKpdSmgSrgBZzHgfRycCH8earVjLAxMVuaCN4T41xVwKCfGdpD1q7JiCl?comment_id=1689542495353193', 'id': 'Y29tbWVudDoxMzE4NjM4MDUwMzA4NDMxXzE2ODk1NDI0OTUzNTMxOTM=', 'feedbackId': 'ZmVlZGJhY2s6MTMxODYzODA1MDMwODQzMV8xNjg5NTQyNDk1MzUzMTkz', 'date': '2026-01-09T22:09:01.000Z', 'text': 'Muy cierto. Lo recomiendo x experiencia propia.', 'profilePicture': 'https:</t>
         </is>
@@ -7942,7 +8071,8 @@
       </c>
       <c r="N126" t="inlineStr"/>
       <c r="O126" t="inlineStr"/>
-      <c r="P126" t="inlineStr">
+      <c r="P126" t="inlineStr"/>
+      <c r="Q126" t="inlineStr">
         <is>
           <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/1318637550308481/', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02Ach9AC61BKpdSmgSrgBZzHgfRycCH8earVjLAxMVuaCN4T41xVwKCfGdpD1q7JiCl?comment_id=1565057301442891', 'id': 'Y29tbWVudDoxMzE4NjM4MDUwMzA4NDMxXzE1NjUwNTczMDE0NDI4OTE=', 'feedbackId': 'ZmVlZGJhY2s6MTMxODYzODA1MDMwODQzMV8xNTY1MDU3MzAxNDQyODkx', 'date': '2026-01-09T20:26:53.000Z', 'text': 'Ya no venden nada deslactosado y sin azúcar.', 'profilePicture': 'https://s</t>
         </is>
@@ -8000,7 +8130,8 @@
       </c>
       <c r="N127" t="inlineStr"/>
       <c r="O127" t="inlineStr"/>
-      <c r="P127" t="inlineStr">
+      <c r="P127" t="inlineStr"/>
+      <c r="Q127" t="inlineStr">
         <is>
           <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/1318637550308481/', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid02Ach9AC61BKpdSmgSrgBZzHgfRycCH8earVjLAxMVuaCN4T41xVwKCfGdpD1q7JiCl?comment_id=1206257714984269', 'id': 'Y29tbWVudDoxMzE4NjM4MDUwMzA4NDMxXzEyMDYyNTc3MTQ5ODQyNjk=', 'feedbackId': 'ZmVlZGJhY2s6MTMxODYzODA1MDMwODQzMV8xMjA2MjU3NzE0OTg0MjY5', 'date': '2026-01-09T01:15:23.000Z', 'text': 'Quien y donde dice q el azúcar ayuda a fortalecer el sistema inmune ?', 'pr</t>
         </is>

--- a/Comentarios Campaña.xlsx
+++ b/Comentarios Campaña.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P82"/>
+  <dimension ref="A1:Q83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -504,6 +504,11 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>extraction_status</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>created_time_raw</t>
         </is>
       </c>
@@ -539,7 +544,7 @@
       <c r="H2" s="1" t="n">
         <v>46069.04180555556</v>
       </c>
-      <c r="I2" s="2" t="n">
+      <c r="I2" s="1" t="n">
         <v>46069</v>
       </c>
       <c r="J2" t="inlineStr">
@@ -562,7 +567,8 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7607261475942220545', 'createTime': 1771203612, 'createTimeISO': '2026-02-16T01:00:12.000Z', 'text': 'yo tengo todos los q a salido pq mi mm me los tare ya q trabaja en alpina', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '695597863502037</t>
         </is>
@@ -599,7 +605,7 @@
       <c r="H3" s="1" t="n">
         <v>46068.9044212963</v>
       </c>
-      <c r="I3" s="2" t="n">
+      <c r="I3" s="1" t="n">
         <v>46068</v>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,7 +628,8 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7607210527748162311', 'createTime': 1771191742, 'createTimeISO': '2026-02-15T21:42:22.000Z', 'text': 'sos', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7593056634043204615', 'uniqueId': 'la.bubu8556', 'avatarThumbnail': 'https://p16-comm</t>
         </is>
@@ -659,7 +666,7 @@
       <c r="H4" s="1" t="n">
         <v>46068.81594907407</v>
       </c>
-      <c r="I4" s="2" t="n">
+      <c r="I4" s="1" t="n">
         <v>46068</v>
       </c>
       <c r="J4" t="inlineStr">
@@ -682,7 +689,8 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7607177720812339975', 'createTime': 1771184098, 'createTimeISO': '2026-02-15T19:34:58.000Z', 'text': 'Hola alpina te amo', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7587775700880606225', 'uniqueId': 'christopher.castr002', 'avatarThumb</t>
         </is>
@@ -719,7 +727,7 @@
       <c r="H5" s="1" t="n">
         <v>46068.80881944444</v>
       </c>
-      <c r="I5" s="2" t="n">
+      <c r="I5" s="1" t="n">
         <v>46068</v>
       </c>
       <c r="J5" t="inlineStr">
@@ -742,7 +750,8 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7607175055629435665', 'createTime': 1771183482, 'createTimeISO': '2026-02-15T19:24:42.000Z', 'text': 'una pío pío rojo agua Mochis 🥳🥳🥳', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7597509511503299601', 'uniqueId': 'familiapeluches2026',</t>
         </is>
@@ -779,7 +788,7 @@
       <c r="H6" s="1" t="n">
         <v>46068.80244212963</v>
       </c>
-      <c r="I6" s="2" t="n">
+      <c r="I6" s="1" t="n">
         <v>46068</v>
       </c>
       <c r="J6" t="inlineStr">
@@ -802,7 +811,8 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7607172648293171969', 'createTime': 1771182931, 'createTimeISO': '2026-02-15T19:15:31.000Z', 'text': ' [sticker]', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7498893686404875319', 'uniqueId': 'amypalacioserrera', 'avatarThumbnail': 'htt</t>
         </is>
@@ -839,7 +849,7 @@
       <c r="H7" s="1" t="n">
         <v>46068.76951388889</v>
       </c>
-      <c r="I7" s="2" t="n">
+      <c r="I7" s="1" t="n">
         <v>46068</v>
       </c>
       <c r="J7" t="inlineStr">
@@ -862,7 +872,8 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7607160512694174482', 'createTime': 1771180086, 'createTimeISO': '2026-02-15T18:28:06.000Z', 'text': 'tengo dos dinosaurios, tres de Navidad y dos del mar. ya estoy obsesionada', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '73319522321483</t>
         </is>
@@ -890,21 +901,21 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Muy caro</t>
+          <t>Pueden ver la lista oficial en mi perfil 🥰</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1771176819</v>
+        <v>1771177428</v>
       </c>
       <c r="H8" s="1" t="n">
-        <v>46068.73170138889</v>
+        <v>46068.73875</v>
       </c>
       <c r="I8" s="2" t="n">
         <v>46068</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>17:33:39</t>
+          <t>17:43:48</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -922,9 +933,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7607146486328984338', 'createTime': 1771176819, 'createTimeISO': '2026-02-15T17:33:39.000Z', 'text': 'Muy caro', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6957546666179200005', 'uniqueId': 'amarillo987', 'avatarThumbnail': 'https://p16</t>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7607149095819445012', 'createTime': 1771177428, 'createTimeISO': '2026-02-15T17:43:48.000Z', 'text': 'Pueden ver la lista oficial en mi perfil 🥰', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6942672037790041094', 'uniqueId': 'hola.soy.an</t>
         </is>
       </c>
     </row>
@@ -950,82 +962,83 @@
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
+          <t>Muy caro</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>1771176819</v>
+      </c>
+      <c r="H9" s="1" t="n">
+        <v>46068.73170138889</v>
+      </c>
+      <c r="I9" s="1" t="n">
+        <v>46068</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>17:33:39</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="b">
+        <v>0</v>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7607146486328984338', 'createTime': 1771176819, 'createTimeISO': '2026-02-15T17:33:39.000Z', 'text': 'Muy caro', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6957546666179200005', 'uniqueId': 'amarillo987', 'avatarThumbnail': 'https://p16</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://vt.tiktok.com/ZSmCS4nn2/</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://vt.tiktok.com/ZSmCS4nn2/</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>Ami seme derritieron todos 😭💔
 (nose por que)</t>
         </is>
       </c>
-      <c r="G9" t="n">
+      <c r="G10" t="n">
         <v>1771176500</v>
       </c>
-      <c r="H9" s="1" t="n">
+      <c r="H10" s="1" t="n">
         <v>46068.72800925926</v>
       </c>
-      <c r="I9" s="2" t="n">
+      <c r="I10" s="1" t="n">
         <v>46068</v>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>17:28:20</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="b">
-        <v>0</v>
-      </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>https://www.tiktok.com/@</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7607145092734976776', 'createTime': 1771176500, 'createTimeISO': '2026-02-15T17:28:20.000Z', 'text': 'Ami seme derritieron todos 😭💔\n(nose por que)', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7471458807811327031', 'uniqueId': 'robloxia</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>1</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>TikTok</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>https://vt.tiktok.com/ZSmCS4nn2/</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>https://vt.tiktok.com/ZSmCS4nn2/</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>porque ahora solo asen Mochis</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>1771173370</v>
-      </c>
-      <c r="H10" s="1" t="n">
-        <v>46068.6917824074</v>
-      </c>
-      <c r="I10" s="2" t="n">
-        <v>46068</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>16:36:10</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1043,9 +1056,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7607131662543192852', 'createTime': 1771173370, 'createTimeISO': '2026-02-15T16:36:10.000Z', 'text': 'porque ahora solo asen Mochis', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7582793117721527304', 'uniqueId': 'joangamer19904', 'avatar</t>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7607145092734976776', 'createTime': 1771176500, 'createTimeISO': '2026-02-15T17:28:20.000Z', 'text': 'Ami seme derritieron todos 😭💔\n(nose por que)', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7471458807811327031', 'uniqueId': 'robloxia</t>
         </is>
       </c>
     </row>
@@ -1071,21 +1085,21 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nooo otra vez nooo</t>
+          <t>porque ahora solo asen Mochis</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1771173239</v>
+        <v>1771173370</v>
       </c>
       <c r="H11" s="1" t="n">
-        <v>46068.6902662037</v>
-      </c>
-      <c r="I11" s="2" t="n">
+        <v>46068.6917824074</v>
+      </c>
+      <c r="I11" s="1" t="n">
         <v>46068</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>16:33:59</t>
+          <t>16:36:10</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1103,9 +1117,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7607131081683649300', 'createTime': 1771173239, 'createTimeISO': '2026-02-15T16:33:59.000Z', 'text': 'Nooo otra vez nooo', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6806838285697106950', 'uniqueId': 'monicacifuentes4', 'avatarThumbnail</t>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7607131662543192852', 'createTime': 1771173370, 'createTimeISO': '2026-02-15T16:36:10.000Z', 'text': 'porque ahora solo asen Mochis', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7582793117721527304', 'uniqueId': 'joangamer19904', 'avatar</t>
         </is>
       </c>
     </row>
@@ -1131,21 +1146,21 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>alpina hay mantarraya???</t>
+          <t>Nooo otra vez nooo</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1771171536</v>
+        <v>1771173239</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>46068.67055555555</v>
-      </c>
-      <c r="I12" s="2" t="n">
+        <v>46068.6902662037</v>
+      </c>
+      <c r="I12" s="1" t="n">
         <v>46068</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>16:05:36</t>
+          <t>16:33:59</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1163,9 +1178,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7607123785518777109', 'createTime': 1771171536, 'createTimeISO': '2026-02-15T16:05:36.000Z', 'text': 'alpina hay mantarraya???', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7298821580599329797', 'uniqueId': 'davidcardenas09', 'avatarThum</t>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7607131081683649300', 'createTime': 1771173239, 'createTimeISO': '2026-02-15T16:33:59.000Z', 'text': 'Nooo otra vez nooo', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6806838285697106950', 'uniqueId': 'monicacifuentes4', 'avatarThumbnail</t>
         </is>
       </c>
     </row>
@@ -1191,21 +1207,21 @@
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>perfecto para mi pecera 😁</t>
+          <t>alpina hay mantarraya???</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1771169516</v>
+        <v>1771171536</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>46068.64717592593</v>
-      </c>
-      <c r="I13" s="2" t="n">
+        <v>46068.67055555555</v>
+      </c>
+      <c r="I13" s="1" t="n">
         <v>46068</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>15:31:56</t>
+          <t>16:05:36</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1223,9 +1239,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7607115112029930248', 'createTime': 1771169516, 'createTimeISO': '2026-02-15T15:31:56.000Z', 'text': 'perfecto para mi pecera 😁', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7398844929906623493', 'uniqueId': 'danilo.alvarez_', 'avatarThu</t>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7607123785518777109', 'createTime': 1771171536, 'createTimeISO': '2026-02-15T16:05:36.000Z', 'text': 'alpina hay mantarraya???', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7298821580599329797', 'uniqueId': 'davidcardenas09', 'avatarThum</t>
         </is>
       </c>
     </row>
@@ -1251,21 +1268,21 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>alpina regaleme los mochis</t>
+          <t>perfecto para mi pecera 😁</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1771168333</v>
+        <v>1771169516</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>46068.63348379629</v>
-      </c>
-      <c r="I14" s="2" t="n">
+        <v>46068.64717592593</v>
+      </c>
+      <c r="I14" s="1" t="n">
         <v>46068</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>15:12:13</t>
+          <t>15:31:56</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1283,9 +1300,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7607110027069768455', 'createTime': 1771168333, 'createTimeISO': '2026-02-15T15:12:13.000Z', 'text': 'alpina regaleme los mochis', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7449505731574760453', 'uniqueId': 'bassielol10', 'avatarThumbn</t>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7607115112029930248', 'createTime': 1771169516, 'createTimeISO': '2026-02-15T15:31:56.000Z', 'text': 'perfecto para mi pecera 😁', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7398844929906623493', 'uniqueId': 'danilo.alvarez_', 'avatarThu</t>
         </is>
       </c>
     </row>
@@ -1311,21 +1329,21 @@
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>se pueden meter en el agua o se dañan?</t>
+          <t>alpina regaleme los mochis</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1771166591</v>
+        <v>1771168333</v>
       </c>
       <c r="H15" s="1" t="n">
-        <v>46068.61332175926</v>
-      </c>
-      <c r="I15" s="2" t="n">
+        <v>46068.63348379629</v>
+      </c>
+      <c r="I15" s="1" t="n">
         <v>46068</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>14:43:11</t>
+          <t>15:12:13</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1343,9 +1361,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7607102555449737991', 'createTime': 1771166591, 'createTimeISO': '2026-02-15T14:43:11.000Z', 'text': 'se pueden meter en el agua o se dañan?', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6843576266509108229', 'uniqueId': 'edwinperilla', </t>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7607110027069768455', 'createTime': 1771168333, 'createTimeISO': '2026-02-15T15:12:13.000Z', 'text': 'alpina regaleme los mochis', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7449505731574760453', 'uniqueId': 'bassielol10', 'avatarThumbn</t>
         </is>
       </c>
     </row>
@@ -1371,21 +1390,21 @@
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>amo los Mochis [sticker]</t>
+          <t>se pueden meter en el agua o se dañan?</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1771135495</v>
+        <v>1771166591</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>46068.25341435185</v>
-      </c>
-      <c r="I16" s="2" t="n">
+        <v>46068.61332175926</v>
+      </c>
+      <c r="I16" s="1" t="n">
         <v>46068</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>06:04:55</t>
+          <t>14:43:11</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1403,9 +1422,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606968952678417159', 'createTime': 1771135495, 'createTimeISO': '2026-02-15T06:04:55.000Z', 'text': 'amo los Mochis [sticker]', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7358029087606588422', 'uniqueId': 'gabis_ortis', 'avatarThumbnai</t>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7607102555449737991', 'createTime': 1771166591, 'createTimeISO': '2026-02-15T14:43:11.000Z', 'text': 'se pueden meter en el agua o se dañan?', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6843576266509108229', 'uniqueId': 'edwinperilla', </t>
         </is>
       </c>
     </row>
@@ -1431,21 +1451,21 @@
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Metan lo muñequitos que hacían antes [sticker]</t>
+          <t>amo los Mochis [sticker]</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1771130506</v>
+        <v>1771135495</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>46068.19567129629</v>
-      </c>
-      <c r="I17" s="2" t="n">
+        <v>46068.25341435185</v>
+      </c>
+      <c r="I17" s="1" t="n">
         <v>46068</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>04:41:46</t>
+          <t>06:04:55</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1463,9 +1483,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606947532074091271', 'createTime': 1771130506, 'createTimeISO': '2026-02-15T04:41:46.000Z', 'text': 'Metan lo muñequitos que hacían antes [sticker]', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7452207058546181126', 'uniqueId': 'miguela</t>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606968952678417159', 'createTime': 1771135495, 'createTimeISO': '2026-02-15T06:04:55.000Z', 'text': 'amo los Mochis [sticker]', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7358029087606588422', 'uniqueId': 'gabis_ortis', 'avatarThumbnai</t>
         </is>
       </c>
     </row>
@@ -1491,25 +1512,25 @@
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>yo ya tengo uno👺 [sticker]</t>
+          <t>Metan lo muñequitos que hacían antes [sticker]</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1771123668</v>
+        <v>1771130506</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>46068.11652777778</v>
-      </c>
-      <c r="I18" s="2" t="n">
+        <v>46068.19567129629</v>
+      </c>
+      <c r="I18" s="1" t="n">
         <v>46068</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>02:47:48</t>
+          <t>04:41:46</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -1523,9 +1544,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606918182959694613', 'createTime': 1771123668, 'createTimeISO': '2026-02-15T02:47:48.000Z', 'text': 'yo ya tengo uno👺 [sticker]', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7578869395050775570', 'uniqueId': 'sharik_rodriguez2', 'avatar</t>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606947532074091271', 'createTime': 1771130506, 'createTimeISO': '2026-02-15T04:41:46.000Z', 'text': 'Metan lo muñequitos que hacían antes [sticker]', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7452207058546181126', 'uniqueId': 'miguela</t>
         </is>
       </c>
     </row>
@@ -1551,25 +1573,25 @@
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>y muchas piedras</t>
+          <t>yo ya tengo uno👺 [sticker]</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>1771119916</v>
+        <v>1771123668</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>46068.07310185185</v>
-      </c>
-      <c r="I19" s="2" t="n">
+        <v>46068.11652777778</v>
+      </c>
+      <c r="I19" s="1" t="n">
         <v>46068</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>01:45:16</t>
+          <t>02:47:48</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -1583,9 +1605,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606902021753586452', 'createTime': 1771119916, 'createTimeISO': '2026-02-15T01:45:16.000Z', 'text': 'y muchas piedras', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7219811811126117382', 'uniqueId': 'maricel.1921', 'avatarThumbnail': 'ht</t>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606918182959694613', 'createTime': 1771123668, 'createTimeISO': '2026-02-15T02:47:48.000Z', 'text': 'yo ya tengo uno👺 [sticker]', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7578869395050775570', 'uniqueId': 'sharik_rodriguez2', 'avatar</t>
         </is>
       </c>
     </row>
@@ -1611,25 +1634,25 @@
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>@skibidisof mochis del aguaaaaaaaaaaaaa</t>
+          <t>y muchas piedras</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1771118528</v>
+        <v>1771119916</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>46068.05703703704</v>
-      </c>
-      <c r="I20" s="2" t="n">
+        <v>46068.07310185185</v>
+      </c>
+      <c r="I20" s="1" t="n">
         <v>46068</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>01:22:08</t>
+          <t>01:45:16</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -1643,9 +1666,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606896084937540373', 'createTime': 1771118528, 'createTimeISO': '2026-02-15T01:22:08.000Z', 'text': '@𝘀𝗸𝗶𝗯𝗶𝗱𝗶𝘀𝗼𝗳 mochis del aguaaaaaaaaaaaaa', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7319063244818859014', 'uniqueId': 'zapynushin', '</t>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606902021753586452', 'createTime': 1771119916, 'createTimeISO': '2026-02-15T01:45:16.000Z', 'text': 'y muchas piedras', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7219811811126117382', 'uniqueId': 'maricel.1921', 'avatarThumbnail': 'ht</t>
         </is>
       </c>
     </row>
@@ -1671,25 +1695,25 @@
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>TODOS A LAS CALLES 17 DE FEBRERO POR UNA VIDA DIGNA, NO A LA BAJA DEL SALARIO MINIMO VITAL</t>
+          <t>@skibidisof mochis del aguaaaaaaaaaaaaa</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>1771110301</v>
+        <v>1771118528</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>46067.96181712963</v>
-      </c>
-      <c r="I21" s="2" t="n">
-        <v>46067</v>
+        <v>46068.05703703704</v>
+      </c>
+      <c r="I21" s="1" t="n">
+        <v>46068</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>23:05:01</t>
+          <t>01:22:08</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -1703,9 +1727,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606860679941702421', 'createTime': 1771110301, 'createTimeISO': '2026-02-14T23:05:01.000Z', 'text': 'TODOS A LAS CALLES 17 DE FEBRERO POR UNA VIDA DIGNA, NO A LA BAJA DEL SALARIO MINIMO VITAL', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid':</t>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606896084937540373', 'createTime': 1771118528, 'createTimeISO': '2026-02-15T01:22:08.000Z', 'text': '@𝘀𝗸𝗶𝗯𝗶𝗱𝗶𝘀𝗼𝗳 mochis del aguaaaaaaaaaaaaa', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7319063244818859014', 'uniqueId': 'zapynushin', '</t>
         </is>
       </c>
     </row>
@@ -1731,21 +1756,21 @@
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>los amoooo, déjenlo mucho tiempo por favor 🥰🥰</t>
+          <t>TODOS A LAS CALLES 17 DE FEBRERO POR UNA VIDA DIGNA, NO A LA BAJA DEL SALARIO MINIMO VITAL</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>1771106038</v>
+        <v>1771110301</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>46067.91247685185</v>
-      </c>
-      <c r="I22" s="2" t="n">
+        <v>46067.96181712963</v>
+      </c>
+      <c r="I22" s="1" t="n">
         <v>46067</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>21:53:58</t>
+          <t>23:05:01</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -1763,9 +1788,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606842411357422354', 'createTime': 1771106038, 'createTimeISO': '2026-02-14T21:53:58.000Z', 'text': 'los amoooo, déjenlo mucho tiempo por favor 🥰🥰', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7151105819618362374', 'uniqueId': 'pau15838</t>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606860679941702421', 'createTime': 1771110301, 'createTimeISO': '2026-02-14T23:05:01.000Z', 'text': 'TODOS A LAS CALLES 17 DE FEBRERO POR UNA VIDA DIGNA, NO A LA BAJA DEL SALARIO MINIMO VITAL', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid':</t>
         </is>
       </c>
     </row>
@@ -1791,21 +1817,21 @@
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Alpina te ama🌟 y te piensa mucho</t>
+          <t>los amoooo, déjenlo mucho tiempo por favor 🥰🥰</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>1771103349</v>
+        <v>1771106038</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>46067.88135416667</v>
-      </c>
-      <c r="I23" s="2" t="n">
+        <v>46067.91247685185</v>
+      </c>
+      <c r="I23" s="1" t="n">
         <v>46067</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>21:09:09</t>
+          <t>21:53:58</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -1823,9 +1849,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606830870297330453', 'createTime': 1771103349, 'createTimeISO': '2026-02-14T21:09:09.000Z', 'text': 'Alpina te ama🌟 y te piensa mucho', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7090696448391873542', 'uniqueId': 'twice_tofu', 'avatarT</t>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606842411357422354', 'createTime': 1771106038, 'createTimeISO': '2026-02-14T21:53:58.000Z', 'text': 'los amoooo, déjenlo mucho tiempo por favor 🥰🥰', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7151105819618362374', 'uniqueId': 'pau15838</t>
         </is>
       </c>
     </row>
@@ -1851,21 +1878,21 @@
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>esto es arteeee</t>
+          <t>Alpina te ama🌟 y te piensa mucho</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>1771103337</v>
+        <v>1771103349</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>46067.88121527778</v>
-      </c>
-      <c r="I24" s="2" t="n">
+        <v>46067.88135416667</v>
+      </c>
+      <c r="I24" s="1" t="n">
         <v>46067</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>21:08:57</t>
+          <t>21:09:09</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -1883,9 +1910,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606830782704157460', 'createTime': 1771103337, 'createTimeISO': '2026-02-14T21:08:57.000Z', 'text': 'esto es arteeee', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7090696448391873542', 'uniqueId': 'twice_tofu', 'avatarThumbnail': 'https</t>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606830870297330453', 'createTime': 1771103349, 'createTimeISO': '2026-02-14T21:09:09.000Z', 'text': 'Alpina te ama🌟 y te piensa mucho', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7090696448391873542', 'uniqueId': 'twice_tofu', 'avatarT</t>
         </is>
       </c>
     </row>
@@ -1911,21 +1939,21 @@
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>arteeee</t>
+          <t>esto es arteeee</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>1771103331</v>
+        <v>1771103337</v>
       </c>
       <c r="H25" s="1" t="n">
-        <v>46067.88114583334</v>
-      </c>
-      <c r="I25" s="2" t="n">
+        <v>46067.88121527778</v>
+      </c>
+      <c r="I25" s="1" t="n">
         <v>46067</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>21:08:51</t>
+          <t>21:08:57</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -1943,9 +1971,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606830779751138069', 'createTime': 1771103331, 'createTimeISO': '2026-02-14T21:08:51.000Z', 'text': 'arteeee', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7090696448391873542', 'uniqueId': 'twice_tofu', 'avatarThumbnail': 'https://p77-s</t>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606830782704157460', 'createTime': 1771103337, 'createTimeISO': '2026-02-14T21:08:57.000Z', 'text': 'esto es arteeee', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7090696448391873542', 'uniqueId': 'twice_tofu', 'avatarThumbnail': 'https</t>
         </is>
       </c>
     </row>
@@ -1971,25 +2000,25 @@
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>hay en el ara?</t>
+          <t>arteeee</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>1771100040</v>
+        <v>1771103331</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>46067.84305555555</v>
-      </c>
-      <c r="I26" s="2" t="n">
+        <v>46067.88114583334</v>
+      </c>
+      <c r="I26" s="1" t="n">
         <v>46067</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>20:14:00</t>
+          <t>21:08:51</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -2003,9 +2032,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606816669142385424', 'createTime': 1771100040, 'createTimeISO': '2026-02-14T20:14:00.000Z', 'text': 'hay en el ara?', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6888066902696018950', 'uniqueId': 'alguienramdon78', 'avatarThumbnail': 'h</t>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606830779751138069', 'createTime': 1771103331, 'createTimeISO': '2026-02-14T21:08:51.000Z', 'text': 'arteeee', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7090696448391873542', 'uniqueId': 'twice_tofu', 'avatarThumbnail': 'https://p77-s</t>
         </is>
       </c>
     </row>
@@ -2031,25 +2061,25 @@
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>oye alpina hay mantarraya??</t>
+          <t>hay en el ara?</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>1771093895</v>
+        <v>1771100040</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>46067.77193287037</v>
-      </c>
-      <c r="I27" s="2" t="n">
+        <v>46067.84305555555</v>
+      </c>
+      <c r="I27" s="1" t="n">
         <v>46067</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>18:31:35</t>
+          <t>20:14:00</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -2063,9 +2093,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606790296471421716', 'createTime': 1771093895, 'createTimeISO': '2026-02-14T18:31:35.000Z', 'text': 'oye alpina hay mantarraya??', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7298821580599329797', 'uniqueId': 'davidcardenas09', 'avatarT</t>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606816669142385424', 'createTime': 1771100040, 'createTimeISO': '2026-02-14T20:14:00.000Z', 'text': 'hay en el ara?', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6888066902696018950', 'uniqueId': 'alguienramdon78', 'avatarThumbnail': 'h</t>
         </is>
       </c>
     </row>
@@ -2091,21 +2122,21 @@
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>oye alpina hay mantarraya???</t>
+          <t>oye alpina hay mantarraya??</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>1771093871</v>
+        <v>1771093895</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>46067.77165509259</v>
-      </c>
-      <c r="I28" s="2" t="n">
+        <v>46067.77193287037</v>
+      </c>
+      <c r="I28" s="1" t="n">
         <v>46067</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>18:31:11</t>
+          <t>18:31:35</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -2123,9 +2154,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606790208725730068', 'createTime': 1771093871, 'createTimeISO': '2026-02-14T18:31:11.000Z', 'text': 'oye alpina hay mantarraya???', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7298821580599329797', 'uniqueId': 'davidcardenas09', 'avatar</t>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606790296471421716', 'createTime': 1771093895, 'createTimeISO': '2026-02-14T18:31:35.000Z', 'text': 'oye alpina hay mantarraya??', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7298821580599329797', 'uniqueId': 'davidcardenas09', 'avatarT</t>
         </is>
       </c>
     </row>
@@ -2151,21 +2183,21 @@
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>[sticker]</t>
+          <t>oye alpina hay mantarraya???</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>1771093416</v>
+        <v>1771093871</v>
       </c>
       <c r="H29" s="1" t="n">
-        <v>46067.76638888889</v>
-      </c>
-      <c r="I29" s="2" t="n">
+        <v>46067.77165509259</v>
+      </c>
+      <c r="I29" s="1" t="n">
         <v>46067</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>18:23:36</t>
+          <t>18:31:11</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -2183,9 +2215,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606788244819215122', 'createTime': 1771093416, 'createTimeISO': '2026-02-14T18:23:36.000Z', 'text': ' [sticker]', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7138274941577937925', 'uniqueId': 'unknown_user_g404', 'avatarThumbnail': 'htt</t>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606790208725730068', 'createTime': 1771093871, 'createTimeISO': '2026-02-14T18:31:11.000Z', 'text': 'oye alpina hay mantarraya???', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7298821580599329797', 'uniqueId': 'davidcardenas09', 'avatar</t>
         </is>
       </c>
     </row>
@@ -2211,21 +2244,21 @@
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>[sticker]</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>1771091971</v>
+        <v>1771093416</v>
       </c>
       <c r="H30" s="1" t="n">
-        <v>46067.74966435185</v>
-      </c>
-      <c r="I30" s="2" t="n">
+        <v>46067.76638888889</v>
+      </c>
+      <c r="I30" s="1" t="n">
         <v>46067</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>17:59:31</t>
+          <t>18:23:36</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -2243,9 +2276,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606782063303508737', 'createTime': 1771091971, 'createTimeISO': '2026-02-14T17:59:31.000Z', 'text': '2025', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7419337733036999685', 'uniqueId': 'saka019283', 'avatarThumbnail': 'https://p77-sign</t>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606788244819215122', 'createTime': 1771093416, 'createTimeISO': '2026-02-14T18:23:36.000Z', 'text': ' [sticker]', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7138274941577937925', 'uniqueId': 'unknown_user_g404', 'avatarThumbnail': 'htt</t>
         </is>
       </c>
     </row>
@@ -2271,21 +2305,21 @@
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>y como saben si no se puede ver?</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>1771087831</v>
+        <v>1771091971</v>
       </c>
       <c r="H31" s="1" t="n">
-        <v>46067.70174768518</v>
-      </c>
-      <c r="I31" s="2" t="n">
+        <v>46067.74966435185</v>
+      </c>
+      <c r="I31" s="1" t="n">
         <v>46067</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>16:50:31</t>
+          <t>17:59:31</t>
         </is>
       </c>
       <c r="K31" t="n">
@@ -2303,9 +2337,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606764253924967176', 'createTime': 1771087831, 'createTimeISO': '2026-02-14T16:50:31.000Z', 'text': 'y como saben si no se puede ver?', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6847655935771558917', 'uniqueId': 'hancel....la...h', 'a</t>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606782063303508737', 'createTime': 1771091971, 'createTimeISO': '2026-02-14T17:59:31.000Z', 'text': '2025', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7419337733036999685', 'uniqueId': 'saka019283', 'avatarThumbnail': 'https://p77-sign</t>
         </is>
       </c>
     </row>
@@ -2331,25 +2366,25 @@
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>ellos están sobre explotando porque la primera vez que hicieron eso le salió re bien</t>
+          <t>y como saben si no se puede ver?</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>1771086393</v>
+        <v>1771087831</v>
       </c>
       <c r="H32" s="1" t="n">
-        <v>46067.68510416667</v>
-      </c>
-      <c r="I32" s="2" t="n">
+        <v>46067.70174768518</v>
+      </c>
+      <c r="I32" s="1" t="n">
         <v>46067</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>16:26:33</t>
+          <t>16:50:31</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -2363,9 +2398,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606758103325426439', 'createTime': 1771086393, 'createTimeISO': '2026-02-14T16:26:33.000Z', 'text': 'ellos están sobre explotando porque la primera vez que hicieron eso le salió re bien', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7488</t>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606764253924967176', 'createTime': 1771087831, 'createTimeISO': '2026-02-14T16:50:31.000Z', 'text': 'y como saben si no se puede ver?', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6847655935771558917', 'uniqueId': 'hancel....la...h', 'a</t>
         </is>
       </c>
     </row>
@@ -2391,21 +2427,21 @@
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Quiero!!! 🥰</t>
+          <t>ellos están sobre explotando porque la primera vez que hicieron eso le salió re bien</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>1771085382</v>
+        <v>1771086393</v>
       </c>
       <c r="H33" s="1" t="n">
-        <v>46067.67340277778</v>
-      </c>
-      <c r="I33" s="2" t="n">
+        <v>46067.68510416667</v>
+      </c>
+      <c r="I33" s="1" t="n">
         <v>46067</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>16:09:42</t>
+          <t>16:26:33</t>
         </is>
       </c>
       <c r="K33" t="n">
@@ -2423,9 +2459,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606753762271019796', 'createTime': 1771085382, 'createTimeISO': '2026-02-14T16:09:42.000Z', 'text': 'Quiero!!! 🥰', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7412745403223163909', 'uniqueId': 'tdboreas', 'avatarThumbnail': 'https://p16</t>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606758103325426439', 'createTime': 1771086393, 'createTimeISO': '2026-02-14T16:26:33.000Z', 'text': 'ellos están sobre explotando porque la primera vez que hicieron eso le salió re bien', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7488</t>
         </is>
       </c>
     </row>
@@ -2451,25 +2488,25 @@
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>amor</t>
+          <t>Quiero!!! 🥰</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>1771084215</v>
+        <v>1771085382</v>
       </c>
       <c r="H34" s="1" t="n">
-        <v>46067.65989583333</v>
-      </c>
-      <c r="I34" s="2" t="n">
+        <v>46067.67340277778</v>
+      </c>
+      <c r="I34" s="1" t="n">
         <v>46067</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>15:50:15</t>
+          <t>16:09:42</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -2483,9 +2520,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606748746374120212', 'createTime': 1771084215, 'createTimeISO': '2026-02-14T15:50:15.000Z', 'text': 'amor', 'diggCount': 2, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7024651547277100037', 'uniqueId': 'maicolcepaa0520', 'avatarThumbnail': 'https://p16</t>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606753762271019796', 'createTime': 1771085382, 'createTimeISO': '2026-02-14T16:09:42.000Z', 'text': 'Quiero!!! 🥰', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7412745403223163909', 'uniqueId': 'tdboreas', 'avatarThumbnail': 'https://p16</t>
         </is>
       </c>
     </row>
@@ -2511,21 +2549,21 @@
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Una pregunta cuántas focas hay en la nueva colección de aquamochis?</t>
+          <t>amor</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>1771079367</v>
+        <v>1771084215</v>
       </c>
       <c r="H35" s="1" t="n">
-        <v>46067.60378472223</v>
-      </c>
-      <c r="I35" s="2" t="n">
+        <v>46067.65989583333</v>
+      </c>
+      <c r="I35" s="1" t="n">
         <v>46067</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>14:29:27</t>
+          <t>15:50:15</t>
         </is>
       </c>
       <c r="K35" t="n">
@@ -2543,9 +2581,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606727932404417298', 'createTime': 1771079367, 'createTimeISO': '2026-02-14T14:29:27.000Z', 'text': 'Una pregunta cuántas focas hay en la nueva colección de aquamochis?', 'diggCount': 2, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7443532287475598391',</t>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606748746374120212', 'createTime': 1771084215, 'createTimeISO': '2026-02-14T15:50:15.000Z', 'text': 'amor', 'diggCount': 2, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7024651547277100037', 'uniqueId': 'maicolcepaa0520', 'avatarThumbnail': 'https://p16</t>
         </is>
       </c>
     </row>
@@ -2571,25 +2610,25 @@
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>juguetes que terminaran en lo más profundo del océano...</t>
+          <t>Una pregunta cuántas focas hay en la nueva colección de aquamochis?</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>1771079356</v>
+        <v>1771079367</v>
       </c>
       <c r="H36" s="1" t="n">
-        <v>46067.60365740741</v>
-      </c>
-      <c r="I36" s="2" t="n">
+        <v>46067.60378472223</v>
+      </c>
+      <c r="I36" s="1" t="n">
         <v>46067</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>14:29:16</t>
+          <t>14:29:27</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -2603,9 +2642,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606727884686476050', 'createTime': 1771079356, 'createTimeISO': '2026-02-14T14:29:16.000Z', 'text': 'juguetes que terminaran en lo más profundo del océano...', 'diggCount': 8, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6786307716072866822', 'uniqueId'</t>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606727932404417298', 'createTime': 1771079367, 'createTimeISO': '2026-02-14T14:29:27.000Z', 'text': 'Una pregunta cuántas focas hay en la nueva colección de aquamochis?', 'diggCount': 2, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7443532287475598391',</t>
         </is>
       </c>
     </row>
@@ -2631,25 +2671,25 @@
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>∞</t>
+          <t>juguetes que terminaran en lo más profundo del océano...</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>1771066510</v>
+        <v>1771079356</v>
       </c>
       <c r="H37" s="1" t="n">
-        <v>46067.45497685186</v>
-      </c>
-      <c r="I37" s="2" t="n">
+        <v>46067.60365740741</v>
+      </c>
+      <c r="I37" s="1" t="n">
         <v>46067</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>10:55:10</t>
+          <t>14:29:16</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -2663,9 +2703,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606672707526771464', 'createTime': 1771066510, 'createTimeISO': '2026-02-14T10:55:10.000Z', 'text': '∞', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7545226599298352144', 'uniqueId': 'antocc13', 'avatarThumbnail': 'https://p77-sign-sg.t</t>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606727884686476050', 'createTime': 1771079356, 'createTimeISO': '2026-02-14T14:29:16.000Z', 'text': 'juguetes que terminaran en lo más profundo del océano...', 'diggCount': 8, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6786307716072866822', 'uniqueId'</t>
         </is>
       </c>
     </row>
@@ -2691,25 +2732,25 @@
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>tengo 143</t>
+          <t>∞</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>1771049239</v>
+        <v>1771066510</v>
       </c>
       <c r="H38" s="1" t="n">
-        <v>46067.25508101852</v>
-      </c>
-      <c r="I38" s="2" t="n">
+        <v>46067.45497685186</v>
+      </c>
+      <c r="I38" s="1" t="n">
         <v>46067</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>06:07:19</t>
+          <t>10:55:10</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
@@ -2723,9 +2764,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606598502535774994', 'createTime': 1771049239, 'createTimeISO': '2026-02-14T06:07:19.000Z', 'text': 'tengo 143', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7569266375668794386', 'uniqueId': 'cata.rojas743', 'avatarThumbnail': 'https://</t>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606672707526771464', 'createTime': 1771066510, 'createTimeISO': '2026-02-14T10:55:10.000Z', 'text': '∞', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7545226599298352144', 'uniqueId': 'antocc13', 'avatarThumbnail': 'https://p77-sign-sg.t</t>
         </is>
       </c>
     </row>
@@ -2751,25 +2793,25 @@
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>@Alpina 🐮 que vuelvan los muñequitos de antes de series o algo así como los guerreros</t>
+          <t>tengo 143</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>1771043890</v>
+        <v>1771049239</v>
       </c>
       <c r="H39" s="1" t="n">
-        <v>46067.1931712963</v>
-      </c>
-      <c r="I39" s="2" t="n">
+        <v>46067.25508101852</v>
+      </c>
+      <c r="I39" s="1" t="n">
         <v>46067</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>04:38:10</t>
+          <t>06:07:19</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
@@ -2783,9 +2825,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606575506917638913', 'createTime': 1771043890, 'createTimeISO': '2026-02-14T04:38:10.000Z', 'text': '@Alpina 🐮 que vuelvan los muñequitos de antes de series o algo así como los guerreros', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '665</t>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606598502535774994', 'createTime': 1771049239, 'createTimeISO': '2026-02-14T06:07:19.000Z', 'text': 'tengo 143', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7569266375668794386', 'uniqueId': 'cata.rojas743', 'avatarThumbnail': 'https://</t>
         </is>
       </c>
     </row>
@@ -2811,25 +2854,25 @@
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>yo tengo 5.😁</t>
+          <t>@Alpina 🐮 que vuelvan los muñequitos de antes de series o algo así como los guerreros</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>1771031816</v>
+        <v>1771043890</v>
       </c>
       <c r="H40" s="1" t="n">
-        <v>46067.05342592593</v>
-      </c>
-      <c r="I40" s="2" t="n">
+        <v>46067.1931712963</v>
+      </c>
+      <c r="I40" s="1" t="n">
         <v>46067</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>01:16:56</t>
+          <t>04:38:10</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -2843,9 +2886,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606523638166913812', 'createTime': 1771031816, 'createTimeISO': '2026-02-14T01:16:56.000Z', 'text': 'yo tengo 5.😁', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7427283654273844229', 'uniqueId': 'pedro.nemoga6', 'avatarThumbnail': 'https</t>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606575506917638913', 'createTime': 1771043890, 'createTimeISO': '2026-02-14T04:38:10.000Z', 'text': '@Alpina 🐮 que vuelvan los muñequitos de antes de series o algo así como los guerreros', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '665</t>
         </is>
       </c>
     </row>
@@ -2871,25 +2915,25 @@
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ya tengo todos</t>
+          <t>yo tengo 5.😁</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>1771012282</v>
+        <v>1771031816</v>
       </c>
       <c r="H41" s="1" t="n">
-        <v>46066.82733796296</v>
-      </c>
-      <c r="I41" s="2" t="n">
-        <v>46066</v>
+        <v>46067.05342592593</v>
+      </c>
+      <c r="I41" s="1" t="n">
+        <v>46067</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>19:51:22</t>
+          <t>01:16:56</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -2903,9 +2947,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606439786600989461', 'createTime': 1771012282, 'createTimeISO': '2026-02-13T19:51:22.000Z', 'text': 'Ya tengo todos', 'diggCount': 3, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7131053865117533190', 'uniqueId': 'maria.teresa.card87', 'avatarThumbnail'</t>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606523638166913812', 'createTime': 1771031816, 'createTimeISO': '2026-02-14T01:16:56.000Z', 'text': 'yo tengo 5.😁', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7427283654273844229', 'uniqueId': 'pedro.nemoga6', 'avatarThumbnail': 'https</t>
         </is>
       </c>
     </row>
@@ -2931,25 +2976,25 @@
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>hola regalame todos plis🙏</t>
+          <t>Ya tengo todos</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>1771012205</v>
+        <v>1771012282</v>
       </c>
       <c r="H42" s="1" t="n">
-        <v>46066.82644675926</v>
-      </c>
-      <c r="I42" s="2" t="n">
+        <v>46066.82733796296</v>
+      </c>
+      <c r="I42" s="1" t="n">
         <v>46066</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>19:50:05</t>
+          <t>19:51:22</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
@@ -2963,9 +3008,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606439434900865813', 'createTime': 1771012205, 'createTimeISO': '2026-02-13T19:50:05.000Z', 'text': 'hola regalame todos plis🙏', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7576484586520216584', 'uniqueId': 'osita1941', 'avatarThumbnail</t>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606439786600989461', 'createTime': 1771012282, 'createTimeISO': '2026-02-13T19:51:22.000Z', 'text': 'Ya tengo todos', 'diggCount': 3, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7131053865117533190', 'uniqueId': 'maria.teresa.card87', 'avatarThumbnail'</t>
         </is>
       </c>
     </row>
@@ -2991,25 +3037,25 @@
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Isaporahi eres tu ? el.que entendió entendió</t>
+          <t>hola regalame todos plis🙏</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>1771004406</v>
+        <v>1771012205</v>
       </c>
       <c r="H43" s="1" t="n">
-        <v>46066.73618055556</v>
-      </c>
-      <c r="I43" s="2" t="n">
+        <v>46066.82644675926</v>
+      </c>
+      <c r="I43" s="1" t="n">
         <v>46066</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>17:40:06</t>
+          <t>19:50:05</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -3023,9 +3069,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606405974844293908', 'createTime': 1771004406, 'createTimeISO': '2026-02-13T17:40:06.000Z', 'text': 'Isaporahi eres tu ? el.que entendió entendió', 'diggCount': 2, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6843103869150741509', 'uniqueId': 'provocavi</t>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606439434900865813', 'createTime': 1771012205, 'createTimeISO': '2026-02-13T19:50:05.000Z', 'text': 'hola regalame todos plis🙏', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7576484586520216584', 'uniqueId': 'osita1941', 'avatarThumbnail</t>
         </is>
       </c>
     </row>
@@ -3051,28 +3098,28 @@
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>saque los ya yo esperé el de navidad y no llego [sticker]</t>
+          <t>Isaporahi eres tu ? el.que entendió entendió</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>1771000219</v>
+        <v>1771004406</v>
       </c>
       <c r="H44" s="1" t="n">
-        <v>46066.68771990741</v>
-      </c>
-      <c r="I44" s="2" t="n">
+        <v>46066.73618055556</v>
+      </c>
+      <c r="I44" s="1" t="n">
         <v>46066</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>16:30:19</t>
+          <t>17:40:06</t>
         </is>
       </c>
       <c r="K44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M44" t="b">
         <v>0</v>
@@ -3083,9 +3130,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606387993427985170', 'createTime': 1771000219, 'createTimeISO': '2026-02-13T16:30:19.000Z', 'text': 'saque los ya yo esperé el de navidad y no llego [sticker]', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '7582376729450349588', 'uniqueId</t>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606405974844293908', 'createTime': 1771004406, 'createTimeISO': '2026-02-13T17:40:06.000Z', 'text': 'Isaporahi eres tu ? el.que entendió entendió', 'diggCount': 2, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6843103869150741509', 'uniqueId': 'provocavi</t>
         </is>
       </c>
     </row>
@@ -3111,28 +3159,28 @@
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>no esta la foca a mi hijo le dalio la foco es preciosa 🥺 le compro solo porque a mi tambien me gusta el las olvida y yo las colecciono pero🤫</t>
+          <t>saque los ya yo esperé el de navidad y no llego [sticker]</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>1770991689</v>
+        <v>1771000219</v>
       </c>
       <c r="H45" s="1" t="n">
-        <v>46066.58899305556</v>
-      </c>
-      <c r="I45" s="2" t="n">
+        <v>46066.68771990741</v>
+      </c>
+      <c r="I45" s="1" t="n">
         <v>46066</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>14:08:09</t>
+          <t>16:30:19</t>
         </is>
       </c>
       <c r="K45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M45" t="b">
         <v>0</v>
@@ -3143,9 +3191,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606351356999615240', 'createTime': 1770991689, 'createTimeISO': '2026-02-13T14:08:09.000Z', 'text': 'no esta la foca a mi hijo le dalio la foco es preciosa 🥺 le compro solo porque a mi tambien me gusta el las olvida y yo las colecciono pero🤫', 'diggCount': 2, 'likedByAuthor': False, 'pinnedByAuthor': False, '</t>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606387993427985170', 'createTime': 1771000219, 'createTimeISO': '2026-02-13T16:30:19.000Z', 'text': 'saque los ya yo esperé el de navidad y no llego [sticker]', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '7582376729450349588', 'uniqueId</t>
         </is>
       </c>
     </row>
@@ -3171,25 +3220,25 @@
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>😏😏😏</t>
+          <t>no esta la foca a mi hijo le dalio la foco es preciosa 🥺 le compro solo porque a mi tambien me gusta el las olvida y yo las colecciono pero🤫</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>1770986962</v>
+        <v>1770991689</v>
       </c>
       <c r="H46" s="1" t="n">
-        <v>46066.53428240741</v>
-      </c>
-      <c r="I46" s="2" t="n">
+        <v>46066.58899305556</v>
+      </c>
+      <c r="I46" s="1" t="n">
         <v>46066</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>12:49:22</t>
+          <t>14:08:09</t>
         </is>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
@@ -3203,9 +3252,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606331029511602965', 'createTime': 1770986962, 'createTimeISO': '2026-02-13T12:49:22.000Z', 'text': '😏😏😏', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6856804310517842950', 'uniqueId': 'sanpaparu75', 'avatarThumbnail': 'https://p19-comm</t>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606351356999615240', 'createTime': 1770991689, 'createTimeISO': '2026-02-13T14:08:09.000Z', 'text': 'no esta la foca a mi hijo le dalio la foco es preciosa 🥺 le compro solo porque a mi tambien me gusta el las olvida y yo las colecciono pero🤫', 'diggCount': 2, 'likedByAuthor': False, 'pinnedByAuthor': False, '</t>
         </is>
       </c>
     </row>
@@ -3231,25 +3281,25 @@
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Hola alpina tengo un pequeño negocio en crecimiento gracias a Dios donde puedo comprar los productos de alpina para venderlos?</t>
+          <t>😏😏😏</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>1770984390</v>
+        <v>1770986962</v>
       </c>
       <c r="H47" s="1" t="n">
-        <v>46066.50451388889</v>
-      </c>
-      <c r="I47" s="2" t="n">
+        <v>46066.53428240741</v>
+      </c>
+      <c r="I47" s="1" t="n">
         <v>46066</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>12:06:30</t>
+          <t>12:49:22</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
@@ -3263,9 +3313,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606319986450678546', 'createTime': 1770984390, 'createTimeISO': '2026-02-13T12:06:30.000Z', 'text': 'Hola alpina tengo un pequeño negocio en crecimiento gracias a Dios donde puedo comprar los productos de alpina para venderlos?', 'diggCount': 5, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': </t>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606331029511602965', 'createTime': 1770986962, 'createTimeISO': '2026-02-13T12:49:22.000Z', 'text': '😏😏😏', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6856804310517842950', 'uniqueId': 'sanpaparu75', 'avatarThumbnail': 'https://p19-comm</t>
         </is>
       </c>
     </row>
@@ -3291,25 +3342,25 @@
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>🙄🫪</t>
+          <t>Hola alpina tengo un pequeño negocio en crecimiento gracias a Dios donde puedo comprar los productos de alpina para venderlos?</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>1770964423</v>
+        <v>1770984390</v>
       </c>
       <c r="H48" s="1" t="n">
-        <v>46066.27341435185</v>
-      </c>
-      <c r="I48" s="2" t="n">
+        <v>46066.50451388889</v>
+      </c>
+      <c r="I48" s="1" t="n">
         <v>46066</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>06:33:43</t>
+          <t>12:06:30</t>
         </is>
       </c>
       <c r="K48" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
@@ -3323,9 +3374,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606234181786485521', 'createTime': 1770964423, 'createTimeISO': '2026-02-13T06:33:43.000Z', 'text': '🙄\U0001faea', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7577226738905596946', 'uniqueId': 'tingui913', 'avatarThumbnail': 'https://p1</t>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606319986450678546', 'createTime': 1770984390, 'createTimeISO': '2026-02-13T12:06:30.000Z', 'text': 'Hola alpina tengo un pequeño negocio en crecimiento gracias a Dios donde puedo comprar los productos de alpina para venderlos?', 'diggCount': 5, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': </t>
         </is>
       </c>
     </row>
@@ -3351,25 +3403,25 @@
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>De lo mejor</t>
+          <t>🙄🫪</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>1770951402</v>
+        <v>1770964423</v>
       </c>
       <c r="H49" s="1" t="n">
-        <v>46066.12270833334</v>
-      </c>
-      <c r="I49" s="2" t="n">
+        <v>46066.27341435185</v>
+      </c>
+      <c r="I49" s="1" t="n">
         <v>46066</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>02:56:42</t>
+          <t>06:33:43</t>
         </is>
       </c>
       <c r="K49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
@@ -3383,9 +3435,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606178321075831560', 'createTime': 1770951402, 'createTimeISO': '2026-02-13T02:56:42.000Z', 'text': 'De lo mejor', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7238758478402094086', 'uniqueId': 'user1622760006000', 'avatarThumbnail': 'ht</t>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606234181786485521', 'createTime': 1770964423, 'createTimeISO': '2026-02-13T06:33:43.000Z', 'text': '🙄\U0001faea', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7577226738905596946', 'uniqueId': 'tingui913', 'avatarThumbnail': 'https://p1</t>
         </is>
       </c>
     </row>
@@ -3411,25 +3464,25 @@
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Extraño a mi ex</t>
+          <t>De lo mejor</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>1770948712</v>
+        <v>1770951402</v>
       </c>
       <c r="H50" s="1" t="n">
-        <v>46066.09157407407</v>
-      </c>
-      <c r="I50" s="2" t="n">
+        <v>46066.12270833334</v>
+      </c>
+      <c r="I50" s="1" t="n">
         <v>46066</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>02:11:52</t>
+          <t>02:56:42</t>
         </is>
       </c>
       <c r="K50" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
@@ -3443,9 +3496,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606166729261990664', 'createTime': 1770948712, 'createTimeISO': '2026-02-13T02:11:52.000Z', 'text': 'Extraño a mi ex', 'diggCount': 5, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7512221394000872456', 'uniqueId': 'papas.con.arroz35', 'avatarThumbnail':</t>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606178321075831560', 'createTime': 1770951402, 'createTimeISO': '2026-02-13T02:56:42.000Z', 'text': 'De lo mejor', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7238758478402094086', 'uniqueId': 'user1622760006000', 'avatarThumbnail': 'ht</t>
         </is>
       </c>
     </row>
@@ -3471,25 +3525,25 @@
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Yo escuché al principio Elon musk.</t>
+          <t>Extraño a mi ex</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>1770945870</v>
+        <v>1770948712</v>
       </c>
       <c r="H51" s="1" t="n">
-        <v>46066.05868055556</v>
-      </c>
-      <c r="I51" s="2" t="n">
+        <v>46066.09157407407</v>
+      </c>
+      <c r="I51" s="1" t="n">
         <v>46066</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>01:24:30</t>
+          <t>02:11:52</t>
         </is>
       </c>
       <c r="K51" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
@@ -3503,9 +3557,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606154497101988624', 'createTime': 1770945870, 'createTimeISO': '2026-02-13T01:24:30.000Z', 'text': 'Yo escuché al principio Elon musk.', 'diggCount': 2, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7531452720693675014', 'uniqueId': 'jamifyapp', 'avatar</t>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606166729261990664', 'createTime': 1770948712, 'createTimeISO': '2026-02-13T02:11:52.000Z', 'text': 'Extraño a mi ex', 'diggCount': 5, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7512221394000872456', 'uniqueId': 'papas.con.arroz35', 'avatarThumbnail':</t>
         </is>
       </c>
     </row>
@@ -3531,25 +3586,25 @@
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>lo más hermoso que he visto hoy</t>
+          <t>Yo escuché al principio Elon musk.</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>1770942820</v>
+        <v>1770945870</v>
       </c>
       <c r="H52" s="1" t="n">
-        <v>46066.02337962963</v>
-      </c>
-      <c r="I52" s="2" t="n">
+        <v>46066.05868055556</v>
+      </c>
+      <c r="I52" s="1" t="n">
         <v>46066</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>00:33:40</t>
+          <t>01:24:30</t>
         </is>
       </c>
       <c r="K52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
@@ -3563,9 +3618,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606141431102784277', 'createTime': 1770942820, 'createTimeISO': '2026-02-13T00:33:40.000Z', 'text': 'lo más hermoso que he visto hoy', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7242097318991037445', 'uniqueId': 'noreidismaria', 'avata</t>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606154497101988624', 'createTime': 1770945870, 'createTimeISO': '2026-02-13T01:24:30.000Z', 'text': 'Yo escuché al principio Elon musk.', 'diggCount': 2, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7531452720693675014', 'uniqueId': 'jamifyapp', 'avatar</t>
         </is>
       </c>
     </row>
@@ -3591,25 +3647,25 @@
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>@Espinosa @Andres Alzate</t>
+          <t>lo más hermoso que he visto hoy</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>1770939724</v>
+        <v>1770942820</v>
       </c>
       <c r="H53" s="1" t="n">
-        <v>46065.9875462963</v>
-      </c>
-      <c r="I53" s="2" t="n">
-        <v>46065</v>
+        <v>46066.02337962963</v>
+      </c>
+      <c r="I53" s="1" t="n">
+        <v>46066</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>23:42:04</t>
+          <t>00:33:40</t>
         </is>
       </c>
       <c r="K53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
@@ -3623,9 +3679,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606128082316460808', 'createTime': 1770939724, 'createTimeISO': '2026-02-12T23:42:04.000Z', 'text': '@𝐸𝑠𝑝𝑖𝑛𝑜𝑠𝑎 @Andres Alzate', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7183578757004854277', 'uniqueId': 'castro_01010', 'avatarThumbna</t>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606141431102784277', 'createTime': 1770942820, 'createTimeISO': '2026-02-13T00:33:40.000Z', 'text': 'lo más hermoso que he visto hoy', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7242097318991037445', 'uniqueId': 'noreidismaria', 'avata</t>
         </is>
       </c>
     </row>
@@ -3651,21 +3708,21 @@
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>🥰🥰🥰🥰</t>
+          <t>@Espinosa @Andres Alzate</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>1770937571</v>
+        <v>1770939724</v>
       </c>
       <c r="H54" s="1" t="n">
-        <v>46065.96262731482</v>
-      </c>
-      <c r="I54" s="2" t="n">
+        <v>46065.9875462963</v>
+      </c>
+      <c r="I54" s="1" t="n">
         <v>46065</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>23:06:11</t>
+          <t>23:42:04</t>
         </is>
       </c>
       <c r="K54" t="n">
@@ -3683,9 +3740,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606118835406340885', 'createTime': 1770937571, 'createTimeISO': '2026-02-12T23:06:11.000Z', 'text': '🥰🥰🥰🥰', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7511416596604437522', 'uniqueId': 'jeronimosanmiguel4', 'avatarThumbnail': 'https://</t>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606128082316460808', 'createTime': 1770939724, 'createTimeISO': '2026-02-12T23:42:04.000Z', 'text': '@𝐸𝑠𝑝𝑖𝑛𝑜𝑠𝑎 @Andres Alzate', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7183578757004854277', 'uniqueId': 'castro_01010', 'avatarThumbna</t>
         </is>
       </c>
     </row>
@@ -3711,21 +3769,21 @@
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>quiero el noctopi w</t>
+          <t>🥰🥰🥰🥰</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>1770933583</v>
+        <v>1770937571</v>
       </c>
       <c r="H55" s="1" t="n">
-        <v>46065.91646990741</v>
-      </c>
-      <c r="I55" s="2" t="n">
+        <v>46065.96262731482</v>
+      </c>
+      <c r="I55" s="1" t="n">
         <v>46065</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>21:59:43</t>
+          <t>23:06:11</t>
         </is>
       </c>
       <c r="K55" t="n">
@@ -3743,9 +3801,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606101748613169928', 'createTime': 1770933583, 'createTimeISO': '2026-02-12T21:59:43.000Z', 'text': 'quiero el noctopi w', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7449448478445814790', 'uniqueId': 'daren.calderon3', 'avatarThumbnail</t>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606118835406340885', 'createTime': 1770937571, 'createTimeISO': '2026-02-12T23:06:11.000Z', 'text': '🥰🥰🥰🥰', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7511416596604437522', 'uniqueId': 'jeronimosanmiguel4', 'avatarThumbnail': 'https://</t>
         </is>
       </c>
     </row>
@@ -3771,21 +3830,21 @@
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>pov mochis se quedan sin ideas o ya se un mochi de agua</t>
+          <t>quiero el noctopi w</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>1770930491</v>
+        <v>1770933583</v>
       </c>
       <c r="H56" s="1" t="n">
-        <v>46065.88068287037</v>
-      </c>
-      <c r="I56" s="2" t="n">
+        <v>46065.91646990741</v>
+      </c>
+      <c r="I56" s="1" t="n">
         <v>46065</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>21:08:11</t>
+          <t>21:59:43</t>
         </is>
       </c>
       <c r="K56" t="n">
@@ -3803,9 +3862,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606088482087600904', 'createTime': 1770930491, 'createTimeISO': '2026-02-12T21:08:11.000Z', 'text': 'pov mochis se quedan sin ideas o ya se un mochi de agua', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7554069625988105223', 'uniqueId':</t>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606101748613169928', 'createTime': 1770933583, 'createTimeISO': '2026-02-12T21:59:43.000Z', 'text': 'quiero el noctopi w', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7449448478445814790', 'uniqueId': 'daren.calderon3', 'avatarThumbnail</t>
         </is>
       </c>
     </row>
@@ -3831,25 +3891,25 @@
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>noooooo otra vez son 40 😭</t>
+          <t>pov mochis se quedan sin ideas o ya se un mochi de agua</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>1770928296</v>
+        <v>1770930491</v>
       </c>
       <c r="H57" s="1" t="n">
-        <v>46065.85527777778</v>
-      </c>
-      <c r="I57" s="2" t="n">
+        <v>46065.88068287037</v>
+      </c>
+      <c r="I57" s="1" t="n">
         <v>46065</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>20:31:36</t>
+          <t>21:08:11</t>
         </is>
       </c>
       <c r="K57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
@@ -3863,9 +3923,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606079011882943250', 'createTime': 1770928296, 'createTimeISO': '2026-02-12T20:31:36.000Z', 'text': 'noooooo otra vez son 40 😭', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7578335295364924434', 'uniqueId': 'santiagodiaz3487', 'avatarTh</t>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606088482087600904', 'createTime': 1770930491, 'createTimeISO': '2026-02-12T21:08:11.000Z', 'text': 'pov mochis se quedan sin ideas o ya se un mochi de agua', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7554069625988105223', 'uniqueId':</t>
         </is>
       </c>
     </row>
@@ -3891,28 +3952,28 @@
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>YA PAREEEEEN</t>
+          <t>noooooo otra vez son 40 😭</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>1770924722</v>
+        <v>1770928296</v>
       </c>
       <c r="H58" s="1" t="n">
-        <v>46065.81391203704</v>
-      </c>
-      <c r="I58" s="2" t="n">
+        <v>46065.85527777778</v>
+      </c>
+      <c r="I58" s="1" t="n">
         <v>46065</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>19:32:02</t>
+          <t>20:31:36</t>
         </is>
       </c>
       <c r="K58" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="L58" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M58" t="b">
         <v>0</v>
@@ -3923,9 +3984,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606063681915749141', 'createTime': 1770924722, 'createTimeISO': '2026-02-12T19:32:02.000Z', 'text': 'YA PAREEEEEN', 'diggCount': 24, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 4, 'uid': '7483155009288733717', 'uniqueId': 'limoncito3333', 'avatarThumbnail': 'http</t>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606079011882943250', 'createTime': 1770928296, 'createTimeISO': '2026-02-12T20:31:36.000Z', 'text': 'noooooo otra vez son 40 😭', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7578335295364924434', 'uniqueId': 'santiagodiaz3487', 'avatarTh</t>
         </is>
       </c>
     </row>
@@ -3951,28 +4013,28 @@
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Alpina ayuda yo estoy emocionada por que estoy acá desde los Mochis , ilumi Mochis, mini Mochis, los Mochis para la maleta, dino Mochis, jojo Mochis, y ahora los aqua Mochis no te miento no los pude conseguir todos no tengo ni 1 colección completa y lo quiero intentar con los aqua Mochis plis Alpina yo quiero una caja de aqua Mochis estoy en todo pero no en los oxxos no han llegado para los 4 logos ni los yoyo yoyo por favor pido ayuda para la lavadora</t>
+          <t>YA PAREEEEEN</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>1770921388</v>
+        <v>1770924722</v>
       </c>
       <c r="H59" s="1" t="n">
-        <v>46065.77532407407</v>
-      </c>
-      <c r="I59" s="2" t="n">
+        <v>46065.81391203704</v>
+      </c>
+      <c r="I59" s="1" t="n">
         <v>46065</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>18:36:28</t>
+          <t>19:32:02</t>
         </is>
       </c>
       <c r="K59" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M59" t="b">
         <v>0</v>
@@ -3983,9 +4045,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606049388909953810', 'createTime': 1770921388, 'createTimeISO': '2026-02-12T18:36:28.000Z', 'text': 'Alpina ayuda yo estoy emocionada por que estoy acá desde los Mochis , ilumi Mochis, mini Mochis, los Mochis para la maleta, dino Mochis, jojo Mochis, y ahora los aqua Mochis no te miento no los pude conseguir </t>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606063681915749141', 'createTime': 1770924722, 'createTimeISO': '2026-02-12T19:32:02.000Z', 'text': 'YA PAREEEEEN', 'diggCount': 24, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 4, 'uid': '7483155009288733717', 'uniqueId': 'limoncito3333', 'avatarThumbnail': 'http</t>
         </is>
       </c>
     </row>
@@ -4011,25 +4074,25 @@
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Yo tengo 6🫧</t>
+          <t>Alpina ayuda yo estoy emocionada por que estoy acá desde los Mochis , ilumi Mochis, mini Mochis, los Mochis para la maleta, dino Mochis, jojo Mochis, y ahora los aqua Mochis no te miento no los pude conseguir todos no tengo ni 1 colección completa y lo quiero intentar con los aqua Mochis plis Alpina yo quiero una caja de aqua Mochis estoy en todo pero no en los oxxos no han llegado para los 4 logos ni los yoyo yoyo por favor pido ayuda para la lavadora</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>1770920196</v>
+        <v>1770921388</v>
       </c>
       <c r="H60" s="1" t="n">
-        <v>46065.76152777778</v>
-      </c>
-      <c r="I60" s="2" t="n">
+        <v>46065.77532407407</v>
+      </c>
+      <c r="I60" s="1" t="n">
         <v>46065</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>18:16:36</t>
+          <t>18:36:28</t>
         </is>
       </c>
       <c r="K60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
@@ -4043,9 +4106,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606044275377652501', 'createTime': 1770920196, 'createTimeISO': '2026-02-12T18:16:36.000Z', 'text': 'Yo tengo 6🫧', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7321136002860008454', 'uniqueId': 'gatobias.y.titosaurio', 'avatarThumbnail':</t>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606049388909953810', 'createTime': 1770921388, 'createTimeISO': '2026-02-12T18:36:28.000Z', 'text': 'Alpina ayuda yo estoy emocionada por que estoy acá desde los Mochis , ilumi Mochis, mini Mochis, los Mochis para la maleta, dino Mochis, jojo Mochis, y ahora los aqua Mochis no te miento no los pude conseguir </t>
         </is>
       </c>
     </row>
@@ -4071,21 +4135,21 @@
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
-          <t>SOLO ALQUERIA🤪🤪🤪</t>
+          <t>Yo tengo 6🫧</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>1770917296</v>
+        <v>1770920196</v>
       </c>
       <c r="H61" s="1" t="n">
-        <v>46065.72796296296</v>
-      </c>
-      <c r="I61" s="2" t="n">
+        <v>46065.76152777778</v>
+      </c>
+      <c r="I61" s="1" t="n">
         <v>46065</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>17:28:16</t>
+          <t>18:16:36</t>
         </is>
       </c>
       <c r="K61" t="n">
@@ -4103,9 +4167,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606031806882939669', 'createTime': 1770917296, 'createTimeISO': '2026-02-12T17:28:16.000Z', 'text': 'SOLO ALQUERIA🤪🤪🤪', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7590083135682200597', 'uniqueId': 'andresito0777', 'avatarThumbnail': 'h</t>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606044275377652501', 'createTime': 1770920196, 'createTimeISO': '2026-02-12T18:16:36.000Z', 'text': 'Yo tengo 6🫧', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7321136002860008454', 'uniqueId': 'gatobias.y.titosaurio', 'avatarThumbnail':</t>
         </is>
       </c>
     </row>
@@ -4131,21 +4196,21 @@
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>hermosa mil bendiciones</t>
+          <t>SOLO ALQUERIA🤪🤪🤪</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>1770914825</v>
+        <v>1770917296</v>
       </c>
       <c r="H62" s="1" t="n">
-        <v>46065.69936342593</v>
-      </c>
-      <c r="I62" s="2" t="n">
+        <v>46065.72796296296</v>
+      </c>
+      <c r="I62" s="1" t="n">
         <v>46065</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>16:47:05</t>
+          <t>17:28:16</t>
         </is>
       </c>
       <c r="K62" t="n">
@@ -4163,9 +4228,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P62" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606021231103673105', 'createTime': 1770914825, 'createTimeISO': '2026-02-12T16:47:05.000Z', 'text': 'hermosa mil bendiciones', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6964522060413436933', 'uniqueId': 'antoniocarlosdomi3', 'avatarTh</t>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606031806882939669', 'createTime': 1770917296, 'createTimeISO': '2026-02-12T17:28:16.000Z', 'text': 'SOLO ALQUERIA🤪🤪🤪', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7590083135682200597', 'uniqueId': 'andresito0777', 'avatarThumbnail': 'h</t>
         </is>
       </c>
     </row>
@@ -4191,25 +4257,25 @@
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>sii que hermoso ya los quiero</t>
+          <t>hermosa mil bendiciones</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>1770914092</v>
+        <v>1770914825</v>
       </c>
       <c r="H63" s="1" t="n">
-        <v>46065.69087962963</v>
-      </c>
-      <c r="I63" s="2" t="n">
+        <v>46065.69936342593</v>
+      </c>
+      <c r="I63" s="1" t="n">
         <v>46065</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>16:34:52</t>
+          <t>16:47:05</t>
         </is>
       </c>
       <c r="K63" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
@@ -4223,9 +4289,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606018071988634369', 'createTime': 1770914092, 'createTimeISO': '2026-02-12T16:34:52.000Z', 'text': 'sii que hermoso ya los quiero', 'diggCount': 4, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7139507407827567621', 'uniqueId': 'xux400', 'avatarThumbnai</t>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606021231103673105', 'createTime': 1770914825, 'createTimeISO': '2026-02-12T16:47:05.000Z', 'text': 'hermosa mil bendiciones', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6964522060413436933', 'uniqueId': 'antoniocarlosdomi3', 'avatarTh</t>
         </is>
       </c>
     </row>
@@ -4251,25 +4318,25 @@
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
-          <t>jajaja ya tienen muy quemados los mochos</t>
+          <t>sii que hermoso ya los quiero</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>1770912313</v>
+        <v>1770914092</v>
       </c>
       <c r="H64" s="1" t="n">
-        <v>46065.67028935185</v>
-      </c>
-      <c r="I64" s="2" t="n">
+        <v>46065.69087962963</v>
+      </c>
+      <c r="I64" s="1" t="n">
         <v>46065</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>16:05:13</t>
+          <t>16:34:52</t>
         </is>
       </c>
       <c r="K64" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
@@ -4283,9 +4350,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P64" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606010431609963285', 'createTime': 1770912313, 'createTimeISO': '2026-02-12T16:05:13.000Z', 'text': 'jajaja ya tienen muy quemados los mochos', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6517432558840452111', 'uniqueId': '223345fabio',</t>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606018071988634369', 'createTime': 1770914092, 'createTimeISO': '2026-02-12T16:34:52.000Z', 'text': 'sii que hermoso ya los quiero', 'diggCount': 4, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7139507407827567621', 'uniqueId': 'xux400', 'avatarThumbnai</t>
         </is>
       </c>
     </row>
@@ -4311,28 +4379,28 @@
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
-          <t>dioss mio mi hija tiene todos los dinosaurios, los de navidad jajajaa y ahora salen estos jajajaj</t>
+          <t>jajaja ya tienen muy quemados los mochos</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>1770911933</v>
+        <v>1770912313</v>
       </c>
       <c r="H65" s="1" t="n">
-        <v>46065.6658912037</v>
-      </c>
-      <c r="I65" s="2" t="n">
+        <v>46065.67028935185</v>
+      </c>
+      <c r="I65" s="1" t="n">
         <v>46065</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>15:58:53</t>
+          <t>16:05:13</t>
         </is>
       </c>
       <c r="K65" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L65" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M65" t="b">
         <v>0</v>
@@ -4343,9 +4411,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606008795130921748', 'createTime': 1770911933, 'createTimeISO': '2026-02-12T15:58:53.000Z', 'text': 'dioss mio mi hija tiene todos los dinosaurios, los de navidad jajajaa y ahora salen estos jajajaj', 'diggCount': 10, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 2</t>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606010431609963285', 'createTime': 1770912313, 'createTimeISO': '2026-02-12T16:05:13.000Z', 'text': 'jajaja ya tienen muy quemados los mochos', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6517432558840452111', 'uniqueId': '223345fabio',</t>
         </is>
       </c>
     </row>
@@ -4371,28 +4440,28 @@
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>a Mochis amo los Mochis</t>
+          <t>dioss mio mi hija tiene todos los dinosaurios, los de navidad jajajaa y ahora salen estos jajajaj</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>1770891501</v>
+        <v>1770911933</v>
       </c>
       <c r="H66" s="1" t="n">
-        <v>46065.42940972222</v>
-      </c>
-      <c r="I66" s="2" t="n">
+        <v>46065.6658912037</v>
+      </c>
+      <c r="I66" s="1" t="n">
         <v>46065</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>10:18:21</t>
+          <t>15:58:53</t>
         </is>
       </c>
       <c r="K66" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M66" t="b">
         <v>0</v>
@@ -4403,9 +4472,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P66" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7605921005799211797', 'createTime': 1770891501, 'createTimeISO': '2026-02-12T10:18:21.000Z', 'text': 'a Mochis amo los Mochis', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7577169276382807048', 'uniqueId': 'sofia18597', 'avatarThumbnail'</t>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606008795130921748', 'createTime': 1770911933, 'createTimeISO': '2026-02-12T15:58:53.000Z', 'text': 'dioss mio mi hija tiene todos los dinosaurios, los de navidad jajajaa y ahora salen estos jajajaj', 'diggCount': 10, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 2</t>
         </is>
       </c>
     </row>
@@ -4431,28 +4501,28 @@
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo</t>
+          <t>a Mochis amo los Mochis</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>1770891189</v>
+        <v>1770891501</v>
       </c>
       <c r="H67" s="1" t="n">
-        <v>46065.42579861111</v>
-      </c>
-      <c r="I67" s="2" t="n">
+        <v>46065.42940972222</v>
+      </c>
+      <c r="I67" s="1" t="n">
         <v>46065</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>10:13:09</t>
+          <t>10:18:21</t>
         </is>
       </c>
       <c r="K67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M67" t="b">
         <v>0</v>
@@ -4463,9 +4533,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7605919710110106388', 'createTime': 1770891189, 'createTimeISO': '2026-02-12T10:13:09.000Z', 'text': 'yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo</t>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7605921005799211797', 'createTime': 1770891501, 'createTimeISO': '2026-02-12T10:18:21.000Z', 'text': 'a Mochis amo los Mochis', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7577169276382807048', 'uniqueId': 'sofia18597', 'avatarThumbnail'</t>
         </is>
       </c>
     </row>
@@ -4491,25 +4562,25 @@
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>mi hija me hizo comprar todos los de dinosaurios, navidad ,y ahora sacan sus favoritos 🥴🥴 animales marinos 🥴🤣🤣🤣</t>
+          <t>yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>1770890495</v>
+        <v>1770891189</v>
       </c>
       <c r="H68" s="1" t="n">
-        <v>46065.4177662037</v>
-      </c>
-      <c r="I68" s="2" t="n">
+        <v>46065.42579861111</v>
+      </c>
+      <c r="I68" s="1" t="n">
         <v>46065</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>10:01:35</t>
+          <t>10:13:09</t>
         </is>
       </c>
       <c r="K68" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="L68" t="n">
         <v>1</v>
@@ -4523,9 +4594,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P68" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7605916734050026248', 'createTime': 1770890495, 'createTimeISO': '2026-02-12T10:01:35.000Z', 'text': 'mi hija me hizo comprar todos los de dinosaurios, navidad ,y ahora sacan sus favoritos 🥴🥴 animales marinos 🥴🤣🤣🤣', 'diggCount': 14, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCo</t>
+      <c r="P68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7605919710110106388', 'createTime': 1770891189, 'createTimeISO': '2026-02-12T10:13:09.000Z', 'text': 'yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo</t>
         </is>
       </c>
     </row>
@@ -4551,28 +4623,28 @@
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
-          <t>yo quiero</t>
+          <t>mi hija me hizo comprar todos los de dinosaurios, navidad ,y ahora sacan sus favoritos 🥴🥴 animales marinos 🥴🤣🤣🤣</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>1770889565</v>
+        <v>1770890495</v>
       </c>
       <c r="H69" s="1" t="n">
-        <v>46065.40700231482</v>
-      </c>
-      <c r="I69" s="2" t="n">
+        <v>46065.4177662037</v>
+      </c>
+      <c r="I69" s="1" t="n">
         <v>46065</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>09:46:05</t>
+          <t>10:01:35</t>
         </is>
       </c>
       <c r="K69" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M69" t="b">
         <v>0</v>
@@ -4583,9 +4655,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P69" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7605912711730856705', 'createTime': 1770889565, 'createTimeISO': '2026-02-12T09:46:05.000Z', 'text': 'yo quiero', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7336195362929787910', 'uniqueId': 'melany.noriega30', 'avatarThumbnail': 'https</t>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7605916734050026248', 'createTime': 1770890495, 'createTimeISO': '2026-02-12T10:01:35.000Z', 'text': 'mi hija me hizo comprar todos los de dinosaurios, navidad ,y ahora sacan sus favoritos 🥴🥴 animales marinos 🥴🤣🤣🤣', 'diggCount': 14, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCo</t>
         </is>
       </c>
     </row>
@@ -4611,25 +4684,25 @@
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Yo quirooooo 🥺</t>
+          <t>yo quiero</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>1770884424</v>
+        <v>1770889565</v>
       </c>
       <c r="H70" s="1" t="n">
-        <v>46065.3475</v>
-      </c>
-      <c r="I70" s="2" t="n">
+        <v>46065.40700231482</v>
+      </c>
+      <c r="I70" s="1" t="n">
         <v>46065</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>08:20:24</t>
+          <t>09:46:05</t>
         </is>
       </c>
       <c r="K70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
@@ -4643,59 +4716,54 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7605890624642024212', 'createTime': 1770884424, 'createTimeISO': '2026-02-12T08:20:24.000Z', 'text': 'Yo quirooooo 🥺', 'diggCount': 2, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6573387218701811717', 'uniqueId': 'papita_0401', 'avatarThumbnail': 'https</t>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7605912711730856705', 'createTime': 1770889565, 'createTimeISO': '2026-02-12T09:46:05.000Z', 'text': 'yo quiero', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7336195362929787910', 'uniqueId': 'melany.noriega30', 'avatarThumbnail': 'https</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
+        <v>1</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>https://vt.tiktok.com/ZSmCS4nn2/</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>https://vt.tiktok.com/ZSmCS4nn2/</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Yo quirooooo 🥺</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
+        <v>1770884424</v>
+      </c>
+      <c r="H71" s="1" t="n">
+        <v>46065.3475</v>
+      </c>
+      <c r="I71" s="1" t="n">
+        <v>46065</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>08:20:24</t>
+        </is>
+      </c>
+      <c r="K71" t="n">
         <v>2</v>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DQZl34lDDef/</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DQZl34lDDef/</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>mm.____.3x</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Y esa cosa negra en la pared🤨🤨🤨</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>2025-11-20T01:56:08.000Z</t>
-        </is>
-      </c>
-      <c r="H71" s="1" t="n">
-        <v>45981.08064814815</v>
-      </c>
-      <c r="I71" s="2" t="n">
-        <v>45981</v>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>01:56:08</t>
-        </is>
-      </c>
-      <c r="K71" t="n">
-        <v>1</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
@@ -4706,12 +4774,13 @@
       <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr">
         <is>
-          <t>https://instagram.com/mm.____.3x</t>
-        </is>
-      </c>
-      <c r="P71" t="inlineStr">
-        <is>
-          <t>{'postUrl': 'https://www.instagram.com/p/DQZl34lDDef/', 'commentUrl': 'https://www.instagram.com/p/DQZl34lDDef/c/17878999155332166', 'id': '17878999155332166', 'text': 'Y esa cosa negra en la pared🤨🤨🤨', 'ownerUsername': 'mm.____.3x', 'ownerProfilePicUrl': 'https://scontent-prg1-1.cdninstagram.com/v/t51.89012-19/573323465_1219825463302212_7278921664109726296_n.png?stp=dst-webp_s150x150&amp;_nc_cat=1&amp;ig_cache_key=YW5vbnltb3VzX3Byb2ZpbGVfcGlj.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InBy</t>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr"/>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7605890624642024212', 'createTime': 1770884424, 'createTimeISO': '2026-02-12T08:20:24.000Z', 'text': 'Yo quirooooo 🥺', 'diggCount': 2, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6573387218701811717', 'uniqueId': 'papita_0401', 'avatarThumbnail': 'https</t>
         </is>
       </c>
     </row>
@@ -4736,28 +4805,28 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>luis_dacop</t>
+          <t>mm.____.3x</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dejame negociar el riñón que me sobra 🙄</t>
+          <t>Y esa cosa negra en la pared🤨🤨🤨</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2025-11-20T00:44:24.000Z</t>
+          <t>2025-11-20T01:56:08.000Z</t>
         </is>
       </c>
       <c r="H72" s="1" t="n">
-        <v>45981.03083333333</v>
-      </c>
-      <c r="I72" s="2" t="n">
+        <v>45981.08064814815</v>
+      </c>
+      <c r="I72" s="1" t="n">
         <v>45981</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>00:44:24</t>
+          <t>01:56:08</t>
         </is>
       </c>
       <c r="K72" t="n">
@@ -4772,12 +4841,13 @@
       <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr">
         <is>
-          <t>https://instagram.com/luis_dacop</t>
-        </is>
-      </c>
-      <c r="P72" t="inlineStr">
-        <is>
-          <t>{'postUrl': 'https://www.instagram.com/p/DQZl34lDDef/', 'commentUrl': 'https://www.instagram.com/p/DQZl34lDDef/c/17980855841926100', 'id': '17980855841926100', 'text': 'Dejame negociar el riñón que me sobra 🙄', 'ownerUsername': 'luis_dacop', 'ownerProfilePicUrl': 'https://scontent-prg1-1.cdninstagram.com/v/t51.82787-19/625230176_18095921168313175_2177686544448637796_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=107&amp;ig_cache_key=GGBBRCVX6x75JEpAAGRLAtJfsjgebmNDAQAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=6694</t>
+          <t>https://instagram.com/mm.____.3x</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr"/>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>{'postUrl': 'https://www.instagram.com/p/DQZl34lDDef/', 'commentUrl': 'https://www.instagram.com/p/DQZl34lDDef/c/17878999155332166', 'id': '17878999155332166', 'text': 'Y esa cosa negra en la pared🤨🤨🤨', 'ownerUsername': 'mm.____.3x', 'ownerProfilePicUrl': 'https://scontent-prg1-1.cdninstagram.com/v/t51.89012-19/573323465_1219825463302212_7278921664109726296_n.png?stp=dst-webp_s150x150&amp;_nc_cat=1&amp;ig_cache_key=YW5vbnltb3VzX3Byb2ZpbGVfcGlj.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InBy</t>
         </is>
       </c>
     </row>
@@ -4802,32 +4872,32 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>solo.roberto</t>
+          <t>luis_dacop</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>No gracias alpina está muy cara !</t>
+          <t>Dejame negociar el riñón que me sobra 🙄</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>2025-11-19T00:17:09.000Z</t>
+          <t>2025-11-20T00:44:24.000Z</t>
         </is>
       </c>
       <c r="H73" s="1" t="n">
-        <v>45980.01190972222</v>
-      </c>
-      <c r="I73" s="2" t="n">
-        <v>45980</v>
+        <v>45981.03083333333</v>
+      </c>
+      <c r="I73" s="1" t="n">
+        <v>45981</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>00:17:09</t>
+          <t>00:44:24</t>
         </is>
       </c>
       <c r="K73" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L73" t="n">
         <v>0</v>
@@ -4838,12 +4908,13 @@
       <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr">
         <is>
-          <t>https://instagram.com/solo.roberto</t>
-        </is>
-      </c>
-      <c r="P73" t="inlineStr">
-        <is>
-          <t>{'postUrl': 'https://www.instagram.com/p/DQZl34lDDef/', 'commentUrl': 'https://www.instagram.com/p/DQZl34lDDef/c/17869377699399109', 'id': '17869377699399109', 'text': 'No gracias alpina está muy cara !', 'ownerUsername': 'solo.roberto', 'ownerProfilePicUrl': 'https://scontent-prg1-1.cdninstagram.com/v/t51.75761-19/497451179_18462727648079276_6370863006333456058_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=104&amp;ig_cache_key=GKuAph2sbQzDwJdBALrOLmUm2mlYbvEnAQAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;e</t>
+          <t>https://instagram.com/luis_dacop</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr"/>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>{'postUrl': 'https://www.instagram.com/p/DQZl34lDDef/', 'commentUrl': 'https://www.instagram.com/p/DQZl34lDDef/c/17980855841926100', 'id': '17980855841926100', 'text': 'Dejame negociar el riñón que me sobra 🙄', 'ownerUsername': 'luis_dacop', 'ownerProfilePicUrl': 'https://scontent-prg1-1.cdninstagram.com/v/t51.82787-19/625230176_18095921168313175_2177686544448637796_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=107&amp;ig_cache_key=GGBBRCVX6x75JEpAAGRLAtJfsjgebmNDAQAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=6694</t>
         </is>
       </c>
     </row>
@@ -4868,32 +4939,32 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>jeanb_555</t>
+          <t>solo.roberto</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>HaaaaAAA!</t>
+          <t>No gracias alpina está muy cara !</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2025-11-17T01:13:39.000Z</t>
+          <t>2025-11-19T00:17:09.000Z</t>
         </is>
       </c>
       <c r="H74" s="1" t="n">
-        <v>45978.05114583333</v>
-      </c>
-      <c r="I74" s="2" t="n">
-        <v>45978</v>
+        <v>45980.01190972222</v>
+      </c>
+      <c r="I74" s="1" t="n">
+        <v>45980</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>01:13:39</t>
+          <t>00:17:09</t>
         </is>
       </c>
       <c r="K74" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L74" t="n">
         <v>0</v>
@@ -4904,60 +4975,63 @@
       <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr">
         <is>
-          <t>https://instagram.com/jeanb_555</t>
-        </is>
-      </c>
-      <c r="P74" t="inlineStr">
-        <is>
-          <t>{'postUrl': 'https://www.instagram.com/p/DQZl34lDDef/', 'commentUrl': 'https://www.instagram.com/p/DQZl34lDDef/c/18327825274240575', 'id': '18327825274240575', 'text': 'HaaaaAAA!', 'ownerUsername': 'jeanb_555', 'ownerProfilePicUrl': 'https://scontent-prg1-1.cdninstagram.com/v/t51.82787-19/619082747_17977100765977609_5485987972083477950_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=108&amp;ig_cache_key=GPtz5iQJXD-xE94-AL7tGZ7_JCJMbmNDAQAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InBy</t>
+          <t>https://instagram.com/solo.roberto</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>{'postUrl': 'https://www.instagram.com/p/DQZl34lDDef/', 'commentUrl': 'https://www.instagram.com/p/DQZl34lDDef/c/17869377699399109', 'id': '17869377699399109', 'text': 'No gracias alpina está muy cara !', 'ownerUsername': 'solo.roberto', 'ownerProfilePicUrl': 'https://scontent-prg1-1.cdninstagram.com/v/t51.75761-19/497451179_18462727648079276_6370863006333456058_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=104&amp;ig_cache_key=GKuAph2sbQzDwJdBALrOLmUm2mlYbvEnAQAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;e</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Facebook</t>
+          <t>Instagram</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/1318637550308481/</t>
+          <t>https://www.instagram.com/p/DQZl34lDDef/</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/1318637550308481/</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr"/>
+          <t>https://www.instagram.com/p/DQZl34lDDef/</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>jeanb_555</t>
+        </is>
+      </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Holavivianapaternia</t>
+          <t>HaaaaAAA!</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>2026-01-18T21:45:53.000Z</t>
+          <t>2025-11-17T01:13:39.000Z</t>
         </is>
       </c>
       <c r="H75" s="1" t="n">
-        <v>46040.90686342592</v>
-      </c>
-      <c r="I75" s="2" t="n">
-        <v>46040</v>
+        <v>45978.05114583333</v>
+      </c>
+      <c r="I75" s="1" t="n">
+        <v>45978</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>21:45:53</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>01:13:39</t>
+        </is>
+      </c>
+      <c r="K75" t="n">
+        <v>1</v>
       </c>
       <c r="L75" t="n">
         <v>0</v>
@@ -4966,10 +5040,15 @@
         <v>0</v>
       </c>
       <c r="N75" t="inlineStr"/>
-      <c r="O75" t="inlineStr"/>
-      <c r="P75" t="inlineStr">
-        <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/1318637550308481/', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid072YTvFDdhBStdWviNCQHm1ThEo1PHvi7Jvw7c2frsgXCsQQSvkofKqJYy1F6npfLl?comment_id=1123930883027156', 'commentId': '1123930883027156', 'id': 'Y29tbWVudDoxMzE4NjM4MDUwMzA4NDMxXzExMjM5MzA4ODMwMjcxNTY=', 'feedbackId': 'ZmVlZGJhY2s6MTMxODYzODA1MDMwODQzMV8xMTIzOTMwODgzMDI3MTU2', 'date': '2026-01-18T21:45:53.000Z', 'text': 'Holavivianapaternia', 'profileUrl': 'https:</t>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>https://instagram.com/jeanb_555</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr"/>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>{'postUrl': 'https://www.instagram.com/p/DQZl34lDDef/', 'commentUrl': 'https://www.instagram.com/p/DQZl34lDDef/c/18327825274240575', 'id': '18327825274240575', 'text': 'HaaaaAAA!', 'ownerUsername': 'jeanb_555', 'ownerProfilePicUrl': 'https://scontent-prg1-1.cdninstagram.com/v/t51.82787-19/619082747_17977100765977609_5485987972083477950_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=108&amp;ig_cache_key=GPtz5iQJXD-xE94-AL7tGZ7_JCJMbmNDAQAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InBy</t>
         </is>
       </c>
     </row>
@@ -4995,29 +5074,27 @@
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Salome</t>
+          <t>Holavivianapaternia</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-01-14T23:51:57.000Z</t>
+          <t>2026-01-18T21:45:53.000Z</t>
         </is>
       </c>
       <c r="H76" s="1" t="n">
-        <v>46036.99440972223</v>
-      </c>
-      <c r="I76" s="2" t="n">
-        <v>46036</v>
+        <v>46040.90686342592</v>
+      </c>
+      <c r="I76" s="1" t="n">
+        <v>46040</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>23:51:57</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>21:45:53</t>
+        </is>
+      </c>
+      <c r="K76" t="n">
+        <v>0</v>
       </c>
       <c r="L76" t="n">
         <v>0</v>
@@ -5027,9 +5104,10 @@
       </c>
       <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr"/>
-      <c r="P76" t="inlineStr">
-        <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/1318637550308481/', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid072YTvFDdhBStdWviNCQHm1ThEo1PHvi7Jvw7c2frsgXCsQQSvkofKqJYy1F6npfLl?comment_id=1412783150373933', 'commentId': '1412783150373933', 'id': 'Y29tbWVudDoxMzE4NjM4MDUwMzA4NDMxXzE0MTI3ODMxNTAzNzM5MzM=', 'feedbackId': 'ZmVlZGJhY2s6MTMxODYzODA1MDMwODQzMV8xNDEyNzgzMTUwMzczOTMz', 'date': '2026-01-14T23:51:57.000Z', 'text': 'Salome', 'profileUrl': 'https://www.faceboo</t>
+      <c r="P76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/1318637550308481/', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid072YTvFDdhBStdWviNCQHm1ThEo1PHvi7Jvw7c2frsgXCsQQSvkofKqJYy1F6npfLl?comment_id=1123930883027156', 'commentId': '1123930883027156', 'id': 'Y29tbWVudDoxMzE4NjM4MDUwMzA4NDMxXzExMjM5MzA4ODMwMjcxNTY=', 'feedbackId': 'ZmVlZGJhY2s6MTMxODYzODA1MDMwODQzMV8xMTIzOTMwODgzMDI3MTU2', 'date': '2026-01-18T21:45:53.000Z', 'text': 'Holavivianapaternia', 'profileUrl': 'https:</t>
         </is>
       </c>
     </row>
@@ -5055,30 +5133,27 @@
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ñ
-Ññ</t>
+          <t>Salome</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>2026-01-11T20:48:42.000Z</t>
+          <t>2026-01-14T23:51:57.000Z</t>
         </is>
       </c>
       <c r="H77" s="1" t="n">
-        <v>46033.86715277778</v>
-      </c>
-      <c r="I77" s="2" t="n">
-        <v>46033</v>
+        <v>46036.99440972223</v>
+      </c>
+      <c r="I77" s="1" t="n">
+        <v>46036</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>20:48:42</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t>23:51:57</t>
+        </is>
+      </c>
+      <c r="K77" t="n">
+        <v>0</v>
       </c>
       <c r="L77" t="n">
         <v>0</v>
@@ -5088,9 +5163,10 @@
       </c>
       <c r="N77" t="inlineStr"/>
       <c r="O77" t="inlineStr"/>
-      <c r="P77" t="inlineStr">
-        <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/1318637550308481/', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid072YTvFDdhBStdWviNCQHm1ThEo1PHvi7Jvw7c2frsgXCsQQSvkofKqJYy1F6npfLl?comment_id=1185407276613695', 'commentId': '1185407276613695', 'id': 'Y29tbWVudDoxMzE4NjM4MDUwMzA4NDMxXzExODU0MDcyNzY2MTM2OTU=', 'feedbackId': 'ZmVlZGJhY2s6MTMxODYzODA1MDMwODQzMV8xMTg1NDA3Mjc2NjEzNjk1', 'date': '2026-01-11T20:48:42.000Z', 'text': 'Ñ\nÑñ', 'profileUrl': 'https://www.facebook</t>
+      <c r="P77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/1318637550308481/', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid072YTvFDdhBStdWviNCQHm1ThEo1PHvi7Jvw7c2frsgXCsQQSvkofKqJYy1F6npfLl?comment_id=1412783150373933', 'commentId': '1412783150373933', 'id': 'Y29tbWVudDoxMzE4NjM4MDUwMzA4NDMxXzE0MTI3ODMxNTAzNzM5MzM=', 'feedbackId': 'ZmVlZGJhY2s6MTMxODYzODA1MDMwODQzMV8xNDEyNzgzMTUwMzczOTMz', 'date': '2026-01-14T23:51:57.000Z', 'text': 'Salome', 'profileUrl': 'https://www.faceboo</t>
         </is>
       </c>
     </row>
@@ -5116,29 +5192,28 @@
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Bueno</t>
+          <t>Ñ
+Ññ</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>2026-01-10T22:35:04.000Z</t>
+          <t>2026-01-11T20:48:42.000Z</t>
         </is>
       </c>
       <c r="H78" s="1" t="n">
-        <v>46032.94101851852</v>
-      </c>
-      <c r="I78" s="2" t="n">
-        <v>46032</v>
+        <v>46033.86715277778</v>
+      </c>
+      <c r="I78" s="1" t="n">
+        <v>46033</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>22:35:04</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>20:48:42</t>
+        </is>
+      </c>
+      <c r="K78" t="n">
+        <v>1</v>
       </c>
       <c r="L78" t="n">
         <v>0</v>
@@ -5148,9 +5223,10 @@
       </c>
       <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr"/>
-      <c r="P78" t="inlineStr">
-        <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/1318637550308481/', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid072YTvFDdhBStdWviNCQHm1ThEo1PHvi7Jvw7c2frsgXCsQQSvkofKqJYy1F6npfLl?comment_id=893455673202688', 'commentId': '893455673202688', 'id': 'Y29tbWVudDoxMzE4NjM4MDUwMzA4NDMxXzg5MzQ1NTY3MzIwMjY4OA==', 'feedbackId': 'ZmVlZGJhY2s6MTMxODYzODA1MDMwODQzMV84OTM0NTU2NzMyMDI2ODg=', 'date': '2026-01-10T22:35:04.000Z', 'text': 'Bueno', 'profileUrl': 'https://www.facebook.c</t>
+      <c r="P78" t="inlineStr"/>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/1318637550308481/', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid072YTvFDdhBStdWviNCQHm1ThEo1PHvi7Jvw7c2frsgXCsQQSvkofKqJYy1F6npfLl?comment_id=1185407276613695', 'commentId': '1185407276613695', 'id': 'Y29tbWVudDoxMzE4NjM4MDUwMzA4NDMxXzExODU0MDcyNzY2MTM2OTU=', 'feedbackId': 'ZmVlZGJhY2s6MTMxODYzODA1MDMwODQzMV8xMTg1NDA3Mjc2NjEzNjk1', 'date': '2026-01-11T20:48:42.000Z', 'text': 'Ñ\nÑñ', 'profileUrl': 'https://www.facebook</t>
         </is>
       </c>
     </row>
@@ -5176,29 +5252,27 @@
       <c r="E79" t="inlineStr"/>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Soy onerto</t>
+          <t>Bueno</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>2026-01-10T00:41:55.000Z</t>
+          <t>2026-01-10T22:35:04.000Z</t>
         </is>
       </c>
       <c r="H79" s="1" t="n">
-        <v>46032.0291087963</v>
-      </c>
-      <c r="I79" s="2" t="n">
+        <v>46032.94101851852</v>
+      </c>
+      <c r="I79" s="1" t="n">
         <v>46032</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>00:41:55</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>22:35:04</t>
+        </is>
+      </c>
+      <c r="K79" t="n">
+        <v>0</v>
       </c>
       <c r="L79" t="n">
         <v>0</v>
@@ -5208,9 +5282,10 @@
       </c>
       <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr"/>
-      <c r="P79" t="inlineStr">
-        <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/1318637550308481/', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid072YTvFDdhBStdWviNCQHm1ThEo1PHvi7Jvw7c2frsgXCsQQSvkofKqJYy1F6npfLl?comment_id=754375667135961', 'commentId': '754375667135961', 'id': 'Y29tbWVudDoxMzE4NjM4MDUwMzA4NDMxXzc1NDM3NTY2NzEzNTk2MQ==', 'feedbackId': 'ZmVlZGJhY2s6MTMxODYzODA1MDMwODQzMV83NTQzNzU2NjcxMzU5NjE=', 'date': '2026-01-10T00:41:55.000Z', 'text': 'Soy onerto', 'profileUrl': 'https://www.faceb</t>
+      <c r="P79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/1318637550308481/', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid072YTvFDdhBStdWviNCQHm1ThEo1PHvi7Jvw7c2frsgXCsQQSvkofKqJYy1F6npfLl?comment_id=893455673202688', 'commentId': '893455673202688', 'id': 'Y29tbWVudDoxMzE4NjM4MDUwMzA4NDMxXzg5MzQ1NTY3MzIwMjY4OA==', 'feedbackId': 'ZmVlZGJhY2s6MTMxODYzODA1MDMwODQzMV84OTM0NTU2NzMyMDI2ODg=', 'date': '2026-01-10T22:35:04.000Z', 'text': 'Bueno', 'profileUrl': 'https://www.facebook.c</t>
         </is>
       </c>
     </row>
@@ -5236,29 +5311,27 @@
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Muy cierto. Lo recomiendo x experiencia propia.</t>
+          <t>Soy onerto</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>2026-01-09T22:09:01.000Z</t>
+          <t>2026-01-10T00:41:55.000Z</t>
         </is>
       </c>
       <c r="H80" s="1" t="n">
-        <v>46031.92292824074</v>
-      </c>
-      <c r="I80" s="2" t="n">
-        <v>46031</v>
+        <v>46032.0291087963</v>
+      </c>
+      <c r="I80" s="1" t="n">
+        <v>46032</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>22:09:01</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+          <t>00:41:55</t>
+        </is>
+      </c>
+      <c r="K80" t="n">
+        <v>0</v>
       </c>
       <c r="L80" t="n">
         <v>0</v>
@@ -5268,9 +5341,10 @@
       </c>
       <c r="N80" t="inlineStr"/>
       <c r="O80" t="inlineStr"/>
-      <c r="P80" t="inlineStr">
-        <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/1318637550308481/', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid072YTvFDdhBStdWviNCQHm1ThEo1PHvi7Jvw7c2frsgXCsQQSvkofKqJYy1F6npfLl?comment_id=1689542495353193', 'commentId': '1689542495353193', 'id': 'Y29tbWVudDoxMzE4NjM4MDUwMzA4NDMxXzE2ODk1NDI0OTUzNTMxOTM=', 'feedbackId': 'ZmVlZGJhY2s6MTMxODYzODA1MDMwODQzMV8xNjg5NTQyNDk1MzUzMTkz', 'date': '2026-01-09T22:09:01.000Z', 'text': 'Muy cierto. Lo recomiendo x experiencia pro</t>
+      <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/1318637550308481/', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid072YTvFDdhBStdWviNCQHm1ThEo1PHvi7Jvw7c2frsgXCsQQSvkofKqJYy1F6npfLl?comment_id=754375667135961', 'commentId': '754375667135961', 'id': 'Y29tbWVudDoxMzE4NjM4MDUwMzA4NDMxXzc1NDM3NTY2NzEzNTk2MQ==', 'feedbackId': 'ZmVlZGJhY2s6MTMxODYzODA1MDMwODQzMV83NTQzNzU2NjcxMzU5NjE=', 'date': '2026-01-10T00:41:55.000Z', 'text': 'Soy onerto', 'profileUrl': 'https://www.faceb</t>
         </is>
       </c>
     </row>
@@ -5296,29 +5370,27 @@
       <c r="E81" t="inlineStr"/>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ya no venden nada deslactosado y sin azúcar.</t>
+          <t>Muy cierto. Lo recomiendo x experiencia propia.</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>2026-01-09T20:26:53.000Z</t>
+          <t>2026-01-09T22:09:01.000Z</t>
         </is>
       </c>
       <c r="H81" s="1" t="n">
-        <v>46031.85200231482</v>
-      </c>
-      <c r="I81" s="2" t="n">
+        <v>46031.92292824074</v>
+      </c>
+      <c r="I81" s="1" t="n">
         <v>46031</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>20:26:53</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>22:09:01</t>
+        </is>
+      </c>
+      <c r="K81" t="n">
+        <v>2</v>
       </c>
       <c r="L81" t="n">
         <v>0</v>
@@ -5328,9 +5400,10 @@
       </c>
       <c r="N81" t="inlineStr"/>
       <c r="O81" t="inlineStr"/>
-      <c r="P81" t="inlineStr">
-        <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/1318637550308481/', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid072YTvFDdhBStdWviNCQHm1ThEo1PHvi7Jvw7c2frsgXCsQQSvkofKqJYy1F6npfLl?comment_id=1565057301442891', 'commentId': '1565057301442891', 'id': 'Y29tbWVudDoxMzE4NjM4MDUwMzA4NDMxXzE1NjUwNTczMDE0NDI4OTE=', 'feedbackId': 'ZmVlZGJhY2s6MTMxODYzODA1MDMwODQzMV8xNTY1MDU3MzAxNDQyODkx', 'date': '2026-01-09T20:26:53.000Z', 'text': 'Ya no venden nada deslactosado y sin azúcar</t>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/1318637550308481/', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid072YTvFDdhBStdWviNCQHm1ThEo1PHvi7Jvw7c2frsgXCsQQSvkofKqJYy1F6npfLl?comment_id=1689542495353193', 'commentId': '1689542495353193', 'id': 'Y29tbWVudDoxMzE4NjM4MDUwMzA4NDMxXzE2ODk1NDI0OTUzNTMxOTM=', 'feedbackId': 'ZmVlZGJhY2s6MTMxODYzODA1MDMwODQzMV8xNjg5NTQyNDk1MzUzMTkz', 'date': '2026-01-09T22:09:01.000Z', 'text': 'Muy cierto. Lo recomiendo x experiencia pro</t>
         </is>
       </c>
     </row>
@@ -5356,29 +5429,27 @@
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Quien y donde dice q el azúcar ayuda a fortalecer el sistema inmune ?</t>
+          <t>Ya no venden nada deslactosado y sin azúcar.</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2026-01-09T01:15:23.000Z</t>
+          <t>2026-01-09T20:26:53.000Z</t>
         </is>
       </c>
       <c r="H82" s="1" t="n">
-        <v>46031.05234953704</v>
-      </c>
-      <c r="I82" s="2" t="n">
+        <v>46031.85200231482</v>
+      </c>
+      <c r="I82" s="1" t="n">
         <v>46031</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>01:15:23</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>20:26:53</t>
+        </is>
+      </c>
+      <c r="K82" t="n">
+        <v>0</v>
       </c>
       <c r="L82" t="n">
         <v>0</v>
@@ -5388,7 +5459,67 @@
       </c>
       <c r="N82" t="inlineStr"/>
       <c r="O82" t="inlineStr"/>
-      <c r="P82" t="inlineStr">
+      <c r="P82" t="inlineStr"/>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/1318637550308481/', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid072YTvFDdhBStdWviNCQHm1ThEo1PHvi7Jvw7c2frsgXCsQQSvkofKqJYy1F6npfLl?comment_id=1565057301442891', 'commentId': '1565057301442891', 'id': 'Y29tbWVudDoxMzE4NjM4MDUwMzA4NDMxXzE1NjUwNTczMDE0NDI4OTE=', 'feedbackId': 'ZmVlZGJhY2s6MTMxODYzODA1MDMwODQzMV8xNTY1MDU3MzAxNDQyODkx', 'date': '2026-01-09T20:26:53.000Z', 'text': 'Ya no venden nada deslactosado y sin azúcar</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>3</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/1318637550308481/</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/1318637550308481/</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Quien y donde dice q el azúcar ayuda a fortalecer el sistema inmune ?</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>2026-01-09T01:15:23.000Z</t>
+        </is>
+      </c>
+      <c r="H83" s="1" t="n">
+        <v>46031.05234953704</v>
+      </c>
+      <c r="I83" s="1" t="n">
+        <v>46031</v>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>01:15:23</t>
+        </is>
+      </c>
+      <c r="K83" t="n">
+        <v>0</v>
+      </c>
+      <c r="L83" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" t="b">
+        <v>0</v>
+      </c>
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" t="inlineStr"/>
+      <c r="P83" t="inlineStr"/>
+      <c r="Q83" t="inlineStr">
         <is>
           <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/1318637550308481/', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid072YTvFDdhBStdWviNCQHm1ThEo1PHvi7Jvw7c2frsgXCsQQSvkofKqJYy1F6npfLl?comment_id=1206257714984269', 'commentId': '1206257714984269', 'id': 'Y29tbWVudDoxMzE4NjM4MDUwMzA4NDMxXzEyMDYyNTc3MTQ5ODQyNjk=', 'feedbackId': 'ZmVlZGJhY2s6MTMxODYzODA1MDMwODQzMV8xMjA2MjU3NzE0OTg0MjY5', 'date': '2026-01-09T01:15:23.000Z', 'text': 'Quien y donde dice q el azúcar ayuda a fort</t>
         </is>
@@ -5460,7 +5591,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E2" t="n">
         <v>99</v>
@@ -5615,10 +5746,10 @@
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D4" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="E4" t="n">
         <v>99</v>

--- a/Comentarios Campaña.xlsx
+++ b/Comentarios Campaña.xlsx
@@ -19,11 +19,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -54,10 +52,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -910,7 +907,7 @@
       <c r="H8" s="1" t="n">
         <v>46068.73875</v>
       </c>
-      <c r="I8" s="2" t="n">
+      <c r="I8" s="1" t="n">
         <v>46068</v>
       </c>
       <c r="J8" t="inlineStr">

--- a/Comentarios Campaña.xlsx
+++ b/Comentarios Campaña.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P83"/>
+  <dimension ref="A1:Q92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -504,6 +504,11 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>extraction_status</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>created_time_raw</t>
         </is>
       </c>
@@ -539,7 +544,7 @@
       <c r="H2" s="1" t="n">
         <v>46069.04180555556</v>
       </c>
-      <c r="I2" s="2" t="n">
+      <c r="I2" s="1" t="n">
         <v>46069</v>
       </c>
       <c r="J2" t="inlineStr">
@@ -562,7 +567,8 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7607261475942220545', 'createTime': 1771203612, 'createTimeISO': '2026-02-16T01:00:12.000Z', 'text': 'yo tengo todos los q a salido pq mi mm me los tare ya q trabaja en alpina', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '695597863502037</t>
         </is>
@@ -599,7 +605,7 @@
       <c r="H3" s="1" t="n">
         <v>46068.9044212963</v>
       </c>
-      <c r="I3" s="2" t="n">
+      <c r="I3" s="1" t="n">
         <v>46068</v>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,7 +628,8 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7607210527748162311', 'createTime': 1771191742, 'createTimeISO': '2026-02-15T21:42:22.000Z', 'text': 'sos', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7593056634043204615', 'uniqueId': 'la.bubu8556', 'avatarThumbnail': 'https://p16-comm</t>
         </is>
@@ -659,7 +666,7 @@
       <c r="H4" s="1" t="n">
         <v>46068.81594907407</v>
       </c>
-      <c r="I4" s="2" t="n">
+      <c r="I4" s="1" t="n">
         <v>46068</v>
       </c>
       <c r="J4" t="inlineStr">
@@ -682,7 +689,8 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7607177720812339975', 'createTime': 1771184098, 'createTimeISO': '2026-02-15T19:34:58.000Z', 'text': 'Hola alpina te amo', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7587775700880606225', 'uniqueId': 'christopher.castr002', 'avatarThumb</t>
         </is>
@@ -719,7 +727,7 @@
       <c r="H5" s="1" t="n">
         <v>46068.80881944444</v>
       </c>
-      <c r="I5" s="2" t="n">
+      <c r="I5" s="1" t="n">
         <v>46068</v>
       </c>
       <c r="J5" t="inlineStr">
@@ -742,7 +750,8 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7607175055629435665', 'createTime': 1771183482, 'createTimeISO': '2026-02-15T19:24:42.000Z', 'text': 'una pío pío rojo agua Mochis 🥳🥳🥳', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7597509511503299601', 'uniqueId': 'familiapeluches2026',</t>
         </is>
@@ -779,7 +788,7 @@
       <c r="H6" s="1" t="n">
         <v>46068.80244212963</v>
       </c>
-      <c r="I6" s="2" t="n">
+      <c r="I6" s="1" t="n">
         <v>46068</v>
       </c>
       <c r="J6" t="inlineStr">
@@ -802,7 +811,8 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7607172648293171969', 'createTime': 1771182931, 'createTimeISO': '2026-02-15T19:15:31.000Z', 'text': ' [sticker]', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7498893686404875319', 'uniqueId': 'amypalacioserrera', 'avatarThumbnail': 'htt</t>
         </is>
@@ -839,7 +849,7 @@
       <c r="H7" s="1" t="n">
         <v>46068.76951388889</v>
       </c>
-      <c r="I7" s="2" t="n">
+      <c r="I7" s="1" t="n">
         <v>46068</v>
       </c>
       <c r="J7" t="inlineStr">
@@ -862,7 +872,8 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7607160512694174482', 'createTime': 1771180086, 'createTimeISO': '2026-02-15T18:28:06.000Z', 'text': 'tengo dos dinosaurios, tres de Navidad y dos del mar. ya estoy obsesionada', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '73319522321483</t>
         </is>
@@ -899,7 +910,7 @@
       <c r="H8" s="1" t="n">
         <v>46068.73875</v>
       </c>
-      <c r="I8" s="2" t="n">
+      <c r="I8" s="1" t="n">
         <v>46068</v>
       </c>
       <c r="J8" t="inlineStr">
@@ -922,7 +933,8 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7607149095819445012', 'createTime': 1771177428, 'createTimeISO': '2026-02-15T17:43:48.000Z', 'text': 'Pueden ver la lista oficial en mi perfil 🥰', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6942672037790041094', 'uniqueId': 'hola.soy.an</t>
         </is>
@@ -959,7 +971,7 @@
       <c r="H9" s="1" t="n">
         <v>46068.73170138889</v>
       </c>
-      <c r="I9" s="2" t="n">
+      <c r="I9" s="1" t="n">
         <v>46068</v>
       </c>
       <c r="J9" t="inlineStr">
@@ -982,7 +994,8 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7607146486328984338', 'createTime': 1771176819, 'createTimeISO': '2026-02-15T17:33:39.000Z', 'text': 'Muy caro', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6957546666179200005', 'uniqueId': 'amarillo987', 'avatarThumbnail': 'https://p16</t>
         </is>
@@ -1020,7 +1033,7 @@
       <c r="H10" s="1" t="n">
         <v>46068.72800925926</v>
       </c>
-      <c r="I10" s="2" t="n">
+      <c r="I10" s="1" t="n">
         <v>46068</v>
       </c>
       <c r="J10" t="inlineStr">
@@ -1043,7 +1056,8 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr">
         <is>
           <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7607145092734976776', 'createTime': 1771176500, 'createTimeISO': '2026-02-15T17:28:20.000Z', 'text': 'Ami seme derritieron todos 😭💔\n(nose por que)', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7471458807811327031', 'uniqueId': 'robloxia</t>
         </is>
@@ -1071,21 +1085,23 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>porque ahora solo asen Mochis</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>1771173370</v>
+          <t>Uju o ok okoviigugyu</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2026-02-15T17:02:50.000Z</t>
+        </is>
       </c>
       <c r="H11" s="1" t="n">
-        <v>46068.6917824074</v>
+        <v>46068.71030092592</v>
       </c>
       <c r="I11" s="2" t="n">
         <v>46068</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>16:36:10</t>
+          <t>17:02:50</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1095,7 +1111,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
@@ -1103,9 +1119,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7607131662543192852', 'createTime': 1771173370, 'createTimeISO': '2026-02-15T16:36:10.000Z', 'text': 'porque ahora solo asen Mochis', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7582793117721527304', 'uniqueId': 'joangamer19904', 'avatar</t>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>{'commentId': '7607138509371949845', 'text': 'Uju o ok okoviigugyu', 'createTime': '2026-02-15T17:02:50.000Z', 'likeCount': 0, 'replyCount': 0, 'isPinned': False, 'isAuthorLiked': False, 'userId': '7077319095574922246', 'username': 'lindav_20', 'nickname': '️', 'avatarUrl': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/d4fd57c34f43a24c1a8c79e828ac2856~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=667b60f4&amp;x-expires=1772902800&amp;x-signature=jRB81J65mLHM5%2F2%2FzVTG8c10eKQ</t>
         </is>
       </c>
     </row>
@@ -1131,21 +1148,21 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nooo otra vez nooo</t>
+          <t>porque ahora solo asen Mochis</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1771173239</v>
+        <v>1771173370</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>46068.6902662037</v>
-      </c>
-      <c r="I12" s="2" t="n">
+        <v>46068.6917824074</v>
+      </c>
+      <c r="I12" s="1" t="n">
         <v>46068</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>16:33:59</t>
+          <t>16:36:10</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1163,9 +1180,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7607131081683649300', 'createTime': 1771173239, 'createTimeISO': '2026-02-15T16:33:59.000Z', 'text': 'Nooo otra vez nooo', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6806838285697106950', 'uniqueId': 'monicacifuentes4', 'avatarThumbnail</t>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7607131662543192852', 'createTime': 1771173370, 'createTimeISO': '2026-02-15T16:36:10.000Z', 'text': 'porque ahora solo asen Mochis', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7582793117721527304', 'uniqueId': 'joangamer19904', 'avatar</t>
         </is>
       </c>
     </row>
@@ -1191,21 +1209,21 @@
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>alpina hay mantarraya???</t>
+          <t>Nooo otra vez nooo</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1771171536</v>
+        <v>1771173239</v>
       </c>
       <c r="H13" s="1" t="n">
-        <v>46068.67055555555</v>
-      </c>
-      <c r="I13" s="2" t="n">
+        <v>46068.6902662037</v>
+      </c>
+      <c r="I13" s="1" t="n">
         <v>46068</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>16:05:36</t>
+          <t>16:33:59</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1223,9 +1241,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7607123785518777109', 'createTime': 1771171536, 'createTimeISO': '2026-02-15T16:05:36.000Z', 'text': 'alpina hay mantarraya???', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7298821580599329797', 'uniqueId': 'davidcardenas09', 'avatarThum</t>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7607131081683649300', 'createTime': 1771173239, 'createTimeISO': '2026-02-15T16:33:59.000Z', 'text': 'Nooo otra vez nooo', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6806838285697106950', 'uniqueId': 'monicacifuentes4', 'avatarThumbnail</t>
         </is>
       </c>
     </row>
@@ -1251,21 +1270,21 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>perfecto para mi pecera 😁</t>
+          <t>alpina hay mantarraya???</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1771169516</v>
+        <v>1771171536</v>
       </c>
       <c r="H14" s="1" t="n">
-        <v>46068.64717592593</v>
-      </c>
-      <c r="I14" s="2" t="n">
+        <v>46068.67055555555</v>
+      </c>
+      <c r="I14" s="1" t="n">
         <v>46068</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>15:31:56</t>
+          <t>16:05:36</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1283,9 +1302,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7607115112029930248', 'createTime': 1771169516, 'createTimeISO': '2026-02-15T15:31:56.000Z', 'text': 'perfecto para mi pecera 😁', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7398844929906623493', 'uniqueId': 'danilo.alvarez_', 'avatarThu</t>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7607123785518777109', 'createTime': 1771171536, 'createTimeISO': '2026-02-15T16:05:36.000Z', 'text': 'alpina hay mantarraya???', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7298821580599329797', 'uniqueId': 'davidcardenas09', 'avatarThum</t>
         </is>
       </c>
     </row>
@@ -1311,21 +1331,23 @@
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>alpina regaleme los mochis</t>
-        </is>
-      </c>
-      <c r="G15" t="n">
-        <v>1771168333</v>
+          <t>X2 la ruina jajaja</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2026-02-15T15:44:21.000Z</t>
+        </is>
       </c>
       <c r="H15" s="1" t="n">
-        <v>46068.63348379629</v>
+        <v>46068.65579861111</v>
       </c>
       <c r="I15" s="2" t="n">
         <v>46068</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>15:12:13</t>
+          <t>15:44:21</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1335,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
@@ -1343,9 +1365,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7607110027069768455', 'createTime': 1771168333, 'createTimeISO': '2026-02-15T15:12:13.000Z', 'text': 'alpina regaleme los mochis', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7449505731574760453', 'uniqueId': 'bassielol10', 'avatarThumbn</t>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>{'commentId': '7607118315177837330', 'text': 'X2 la ruina jajaja', 'createTime': '2026-02-15T15:44:21.000Z', 'likeCount': 1, 'replyCount': 0, 'isPinned': False, 'isAuthorLiked': False, 'userId': '6887365764200317958', 'username': 'htdc2016', 'nickname': 'HtD', 'avatarUrl': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/3ccffb9e73988e3e507bb37edf1cbf60~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=8410edde&amp;x-expires=1772902800&amp;x-signature=aLtLnAXDFQT8zeuUCBS3TUsxM8k%3D&amp;t</t>
         </is>
       </c>
     </row>
@@ -1371,21 +1394,21 @@
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>se pueden meter en el agua o se dañan?</t>
+          <t>perfecto para mi pecera 😁</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1771166591</v>
+        <v>1771169516</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>46068.61332175926</v>
-      </c>
-      <c r="I16" s="2" t="n">
+        <v>46068.64717592593</v>
+      </c>
+      <c r="I16" s="1" t="n">
         <v>46068</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>14:43:11</t>
+          <t>15:31:56</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1403,9 +1426,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7607102555449737991', 'createTime': 1771166591, 'createTimeISO': '2026-02-15T14:43:11.000Z', 'text': 'se pueden meter en el agua o se dañan?', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6843576266509108229', 'uniqueId': 'edwinperilla', </t>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7607115112029930248', 'createTime': 1771169516, 'createTimeISO': '2026-02-15T15:31:56.000Z', 'text': 'perfecto para mi pecera 😁', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7398844929906623493', 'uniqueId': 'danilo.alvarez_', 'avatarThu</t>
         </is>
       </c>
     </row>
@@ -1431,21 +1455,21 @@
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>amo los Mochis [sticker]</t>
+          <t>alpina regaleme los mochis</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1771135495</v>
+        <v>1771168333</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>46068.25341435185</v>
-      </c>
-      <c r="I17" s="2" t="n">
+        <v>46068.63348379629</v>
+      </c>
+      <c r="I17" s="1" t="n">
         <v>46068</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>06:04:55</t>
+          <t>15:12:13</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1463,9 +1487,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606968952678417159', 'createTime': 1771135495, 'createTimeISO': '2026-02-15T06:04:55.000Z', 'text': 'amo los Mochis [sticker]', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7358029087606588422', 'uniqueId': 'gabis_ortis', 'avatarThumbnai</t>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7607110027069768455', 'createTime': 1771168333, 'createTimeISO': '2026-02-15T15:12:13.000Z', 'text': 'alpina regaleme los mochis', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7449505731574760453', 'uniqueId': 'bassielol10', 'avatarThumbn</t>
         </is>
       </c>
     </row>
@@ -1491,21 +1516,21 @@
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Metan lo muñequitos que hacían antes [sticker]</t>
+          <t>se pueden meter en el agua o se dañan?</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1771130506</v>
+        <v>1771166591</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>46068.19567129629</v>
-      </c>
-      <c r="I18" s="2" t="n">
+        <v>46068.61332175926</v>
+      </c>
+      <c r="I18" s="1" t="n">
         <v>46068</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>04:41:46</t>
+          <t>14:43:11</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1523,9 +1548,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606947532074091271', 'createTime': 1771130506, 'createTimeISO': '2026-02-15T04:41:46.000Z', 'text': 'Metan lo muñequitos que hacían antes [sticker]', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7452207058546181126', 'uniqueId': 'miguela</t>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7607102555449737991', 'createTime': 1771166591, 'createTimeISO': '2026-02-15T14:43:11.000Z', 'text': 'se pueden meter en el agua o se dañan?', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6843576266509108229', 'uniqueId': 'edwinperilla', </t>
         </is>
       </c>
     </row>
@@ -1551,25 +1577,25 @@
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>yo ya tengo uno👺 [sticker]</t>
+          <t>amo los Mochis [sticker]</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>1771123668</v>
+        <v>1771135495</v>
       </c>
       <c r="H19" s="1" t="n">
-        <v>46068.11652777778</v>
-      </c>
-      <c r="I19" s="2" t="n">
+        <v>46068.25341435185</v>
+      </c>
+      <c r="I19" s="1" t="n">
         <v>46068</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>02:47:48</t>
+          <t>06:04:55</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -1583,9 +1609,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606918182959694613', 'createTime': 1771123668, 'createTimeISO': '2026-02-15T02:47:48.000Z', 'text': 'yo ya tengo uno👺 [sticker]', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7578869395050775570', 'uniqueId': 'sharik_rodriguez2', 'avatar</t>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606968952678417159', 'createTime': 1771135495, 'createTimeISO': '2026-02-15T06:04:55.000Z', 'text': 'amo los Mochis [sticker]', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7358029087606588422', 'uniqueId': 'gabis_ortis', 'avatarThumbnai</t>
         </is>
       </c>
     </row>
@@ -1611,21 +1638,21 @@
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>y muchas piedras</t>
+          <t>Metan lo muñequitos que hacían antes [sticker]</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1771119916</v>
+        <v>1771130506</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>46068.07310185185</v>
-      </c>
-      <c r="I20" s="2" t="n">
+        <v>46068.19567129629</v>
+      </c>
+      <c r="I20" s="1" t="n">
         <v>46068</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>01:45:16</t>
+          <t>04:41:46</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1643,9 +1670,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606902021753586452', 'createTime': 1771119916, 'createTimeISO': '2026-02-15T01:45:16.000Z', 'text': 'y muchas piedras', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7219811811126117382', 'uniqueId': 'maricel.1921', 'avatarThumbnail': 'ht</t>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606947532074091271', 'createTime': 1771130506, 'createTimeISO': '2026-02-15T04:41:46.000Z', 'text': 'Metan lo muñequitos que hacían antes [sticker]', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7452207058546181126', 'uniqueId': 'miguela</t>
         </is>
       </c>
     </row>
@@ -1671,21 +1699,21 @@
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>@skibidisof mochis del aguaaaaaaaaaaaaa</t>
+          <t>yo ya tengo uno👺 [sticker]</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>1771118528</v>
+        <v>1771123668</v>
       </c>
       <c r="H21" s="1" t="n">
-        <v>46068.05703703704</v>
-      </c>
-      <c r="I21" s="2" t="n">
+        <v>46068.11652777778</v>
+      </c>
+      <c r="I21" s="1" t="n">
         <v>46068</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>01:22:08</t>
+          <t>02:47:48</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -1703,9 +1731,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606896084937540373', 'createTime': 1771118528, 'createTimeISO': '2026-02-15T01:22:08.000Z', 'text': '@𝘀𝗸𝗶𝗯𝗶𝗱𝗶𝘀𝗼𝗳 mochis del aguaaaaaaaaaaaaa', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7319063244818859014', 'uniqueId': 'zapynushin', '</t>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606918182959694613', 'createTime': 1771123668, 'createTimeISO': '2026-02-15T02:47:48.000Z', 'text': 'yo ya tengo uno👺 [sticker]', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7578869395050775570', 'uniqueId': 'sharik_rodriguez2', 'avatar</t>
         </is>
       </c>
     </row>
@@ -1731,21 +1760,21 @@
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>TODOS A LAS CALLES 17 DE FEBRERO POR UNA VIDA DIGNA, NO A LA BAJA DEL SALARIO MINIMO VITAL</t>
+          <t>y muchas piedras</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>1771110301</v>
+        <v>1771119916</v>
       </c>
       <c r="H22" s="1" t="n">
-        <v>46067.96181712963</v>
-      </c>
-      <c r="I22" s="2" t="n">
-        <v>46067</v>
+        <v>46068.07310185185</v>
+      </c>
+      <c r="I22" s="1" t="n">
+        <v>46068</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>23:05:01</t>
+          <t>01:45:16</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -1763,9 +1792,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606860679941702421', 'createTime': 1771110301, 'createTimeISO': '2026-02-14T23:05:01.000Z', 'text': 'TODOS A LAS CALLES 17 DE FEBRERO POR UNA VIDA DIGNA, NO A LA BAJA DEL SALARIO MINIMO VITAL', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid':</t>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606902021753586452', 'createTime': 1771119916, 'createTimeISO': '2026-02-15T01:45:16.000Z', 'text': 'y muchas piedras', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7219811811126117382', 'uniqueId': 'maricel.1921', 'avatarThumbnail': 'ht</t>
         </is>
       </c>
     </row>
@@ -1791,25 +1821,25 @@
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>los amoooo, déjenlo mucho tiempo por favor 🥰🥰</t>
+          <t>@skibidisof mochis del aguaaaaaaaaaaaaa</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>1771106038</v>
+        <v>1771118528</v>
       </c>
       <c r="H23" s="1" t="n">
-        <v>46067.91247685185</v>
-      </c>
-      <c r="I23" s="2" t="n">
-        <v>46067</v>
+        <v>46068.05703703704</v>
+      </c>
+      <c r="I23" s="1" t="n">
+        <v>46068</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>21:53:58</t>
+          <t>01:22:08</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -1823,9 +1853,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606842411357422354', 'createTime': 1771106038, 'createTimeISO': '2026-02-14T21:53:58.000Z', 'text': 'los amoooo, déjenlo mucho tiempo por favor 🥰🥰', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7151105819618362374', 'uniqueId': 'pau15838</t>
+      <c r="P23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606896084937540373', 'createTime': 1771118528, 'createTimeISO': '2026-02-15T01:22:08.000Z', 'text': '@𝘀𝗸𝗶𝗯𝗶𝗱𝗶𝘀𝗼𝗳 mochis del aguaaaaaaaaaaaaa', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7319063244818859014', 'uniqueId': 'zapynushin', '</t>
         </is>
       </c>
     </row>
@@ -1851,21 +1882,21 @@
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Alpina te ama🌟 y te piensa mucho</t>
+          <t>TODOS A LAS CALLES 17 DE FEBRERO POR UNA VIDA DIGNA, NO A LA BAJA DEL SALARIO MINIMO VITAL</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>1771103349</v>
+        <v>1771110301</v>
       </c>
       <c r="H24" s="1" t="n">
-        <v>46067.88135416667</v>
-      </c>
-      <c r="I24" s="2" t="n">
+        <v>46067.96181712963</v>
+      </c>
+      <c r="I24" s="1" t="n">
         <v>46067</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>21:09:09</t>
+          <t>23:05:01</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -1883,9 +1914,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606830870297330453', 'createTime': 1771103349, 'createTimeISO': '2026-02-14T21:09:09.000Z', 'text': 'Alpina te ama🌟 y te piensa mucho', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7090696448391873542', 'uniqueId': 'twice_tofu', 'avatarT</t>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606860679941702421', 'createTime': 1771110301, 'createTimeISO': '2026-02-14T23:05:01.000Z', 'text': 'TODOS A LAS CALLES 17 DE FEBRERO POR UNA VIDA DIGNA, NO A LA BAJA DEL SALARIO MINIMO VITAL', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid':</t>
         </is>
       </c>
     </row>
@@ -1911,21 +1943,21 @@
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>esto es arteeee</t>
+          <t>los amoooo, déjenlo mucho tiempo por favor 🥰🥰</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>1771103337</v>
+        <v>1771106038</v>
       </c>
       <c r="H25" s="1" t="n">
-        <v>46067.88121527778</v>
-      </c>
-      <c r="I25" s="2" t="n">
+        <v>46067.91247685185</v>
+      </c>
+      <c r="I25" s="1" t="n">
         <v>46067</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>21:08:57</t>
+          <t>21:53:58</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -1943,9 +1975,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606830782704157460', 'createTime': 1771103337, 'createTimeISO': '2026-02-14T21:08:57.000Z', 'text': 'esto es arteeee', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7090696448391873542', 'uniqueId': 'twice_tofu', 'avatarThumbnail': 'https</t>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606842411357422354', 'createTime': 1771106038, 'createTimeISO': '2026-02-14T21:53:58.000Z', 'text': 'los amoooo, déjenlo mucho tiempo por favor 🥰🥰', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7151105819618362374', 'uniqueId': 'pau15838</t>
         </is>
       </c>
     </row>
@@ -1971,21 +2004,21 @@
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>arteeee</t>
+          <t>Alpina te ama🌟 y te piensa mucho</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>1771103331</v>
+        <v>1771103349</v>
       </c>
       <c r="H26" s="1" t="n">
-        <v>46067.88114583334</v>
-      </c>
-      <c r="I26" s="2" t="n">
+        <v>46067.88135416667</v>
+      </c>
+      <c r="I26" s="1" t="n">
         <v>46067</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>21:08:51</t>
+          <t>21:09:09</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -2003,9 +2036,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606830779751138069', 'createTime': 1771103331, 'createTimeISO': '2026-02-14T21:08:51.000Z', 'text': 'arteeee', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7090696448391873542', 'uniqueId': 'twice_tofu', 'avatarThumbnail': 'https://p16-c</t>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606830870297330453', 'createTime': 1771103349, 'createTimeISO': '2026-02-14T21:09:09.000Z', 'text': 'Alpina te ama🌟 y te piensa mucho', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7090696448391873542', 'uniqueId': 'twice_tofu', 'avatarT</t>
         </is>
       </c>
     </row>
@@ -2031,25 +2065,25 @@
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>hay en el ara?</t>
+          <t>esto es arteeee</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>1771100040</v>
+        <v>1771103337</v>
       </c>
       <c r="H27" s="1" t="n">
-        <v>46067.84305555555</v>
-      </c>
-      <c r="I27" s="2" t="n">
+        <v>46067.88121527778</v>
+      </c>
+      <c r="I27" s="1" t="n">
         <v>46067</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>20:14:00</t>
+          <t>21:08:57</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -2063,9 +2097,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606816669142385424', 'createTime': 1771100040, 'createTimeISO': '2026-02-14T20:14:00.000Z', 'text': 'hay en el ara?', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6888066902696018950', 'uniqueId': 'alguienramdon78', 'avatarThumbnail': 'h</t>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606830782704157460', 'createTime': 1771103337, 'createTimeISO': '2026-02-14T21:08:57.000Z', 'text': 'esto es arteeee', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7090696448391873542', 'uniqueId': 'twice_tofu', 'avatarThumbnail': 'https</t>
         </is>
       </c>
     </row>
@@ -2091,21 +2126,21 @@
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>oye alpina hay mantarraya??</t>
+          <t>arteeee</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>1771093895</v>
+        <v>1771103331</v>
       </c>
       <c r="H28" s="1" t="n">
-        <v>46067.77193287037</v>
-      </c>
-      <c r="I28" s="2" t="n">
+        <v>46067.88114583334</v>
+      </c>
+      <c r="I28" s="1" t="n">
         <v>46067</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>18:31:35</t>
+          <t>21:08:51</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -2123,9 +2158,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606790296471421716', 'createTime': 1771093895, 'createTimeISO': '2026-02-14T18:31:35.000Z', 'text': 'oye alpina hay mantarraya??', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7298821580599329797', 'uniqueId': 'davidcardenas09', 'avatarT</t>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606830779751138069', 'createTime': 1771103331, 'createTimeISO': '2026-02-14T21:08:51.000Z', 'text': 'arteeee', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7090696448391873542', 'uniqueId': 'twice_tofu', 'avatarThumbnail': 'https://p16-c</t>
         </is>
       </c>
     </row>
@@ -2151,25 +2187,25 @@
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>oye alpina hay mantarraya???</t>
+          <t>hay en el ara?</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>1771093871</v>
+        <v>1771100040</v>
       </c>
       <c r="H29" s="1" t="n">
-        <v>46067.77165509259</v>
-      </c>
-      <c r="I29" s="2" t="n">
+        <v>46067.84305555555</v>
+      </c>
+      <c r="I29" s="1" t="n">
         <v>46067</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>18:31:11</t>
+          <t>20:14:00</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -2183,9 +2219,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606790208725730068', 'createTime': 1771093871, 'createTimeISO': '2026-02-14T18:31:11.000Z', 'text': 'oye alpina hay mantarraya???', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7298821580599329797', 'uniqueId': 'davidcardenas09', 'avatar</t>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606816669142385424', 'createTime': 1771100040, 'createTimeISO': '2026-02-14T20:14:00.000Z', 'text': 'hay en el ara?', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6888066902696018950', 'uniqueId': 'alguienramdon78', 'avatarThumbnail': 'h</t>
         </is>
       </c>
     </row>
@@ -2211,21 +2248,21 @@
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>[sticker]</t>
+          <t>oye alpina hay mantarraya??</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>1771093416</v>
+        <v>1771093895</v>
       </c>
       <c r="H30" s="1" t="n">
-        <v>46067.76638888889</v>
-      </c>
-      <c r="I30" s="2" t="n">
+        <v>46067.77193287037</v>
+      </c>
+      <c r="I30" s="1" t="n">
         <v>46067</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>18:23:36</t>
+          <t>18:31:35</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -2243,9 +2280,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606788244819215122', 'createTime': 1771093416, 'createTimeISO': '2026-02-14T18:23:36.000Z', 'text': ' [sticker]', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7138274941577937925', 'uniqueId': 'unknown_user_g404', 'avatarThumbnail': 'htt</t>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606790296471421716', 'createTime': 1771093895, 'createTimeISO': '2026-02-14T18:31:35.000Z', 'text': 'oye alpina hay mantarraya??', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7298821580599329797', 'uniqueId': 'davidcardenas09', 'avatarT</t>
         </is>
       </c>
     </row>
@@ -2271,21 +2309,21 @@
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>oye alpina hay mantarraya???</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>1771091971</v>
+        <v>1771093871</v>
       </c>
       <c r="H31" s="1" t="n">
-        <v>46067.74966435185</v>
-      </c>
-      <c r="I31" s="2" t="n">
+        <v>46067.77165509259</v>
+      </c>
+      <c r="I31" s="1" t="n">
         <v>46067</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>17:59:31</t>
+          <t>18:31:11</t>
         </is>
       </c>
       <c r="K31" t="n">
@@ -2303,9 +2341,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606782063303508737', 'createTime': 1771091971, 'createTimeISO': '2026-02-14T17:59:31.000Z', 'text': '2025', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7419337733036999685', 'uniqueId': 'saka019283', 'avatarThumbnail': 'https://p16-comm</t>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606790208725730068', 'createTime': 1771093871, 'createTimeISO': '2026-02-14T18:31:11.000Z', 'text': 'oye alpina hay mantarraya???', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7298821580599329797', 'uniqueId': 'davidcardenas09', 'avatar</t>
         </is>
       </c>
     </row>
@@ -2331,21 +2370,21 @@
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>y como saben si no se puede ver?</t>
+          <t>[sticker]</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>1771087831</v>
+        <v>1771093416</v>
       </c>
       <c r="H32" s="1" t="n">
-        <v>46067.70174768518</v>
-      </c>
-      <c r="I32" s="2" t="n">
+        <v>46067.76638888889</v>
+      </c>
+      <c r="I32" s="1" t="n">
         <v>46067</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>16:50:31</t>
+          <t>18:23:36</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -2363,9 +2402,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606764253924967176', 'createTime': 1771087831, 'createTimeISO': '2026-02-14T16:50:31.000Z', 'text': 'y como saben si no se puede ver?', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6847655935771558917', 'uniqueId': 'hancel....la...h', 'a</t>
+      <c r="P32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606788244819215122', 'createTime': 1771093416, 'createTimeISO': '2026-02-14T18:23:36.000Z', 'text': ' [sticker]', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7138274941577937925', 'uniqueId': 'unknown_user_g404', 'avatarThumbnail': 'htt</t>
         </is>
       </c>
     </row>
@@ -2391,25 +2431,25 @@
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>ellos están sobre explotando porque la primera vez que hicieron eso le salió re bien</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>1771086393</v>
+        <v>1771091971</v>
       </c>
       <c r="H33" s="1" t="n">
-        <v>46067.68510416667</v>
-      </c>
-      <c r="I33" s="2" t="n">
+        <v>46067.74966435185</v>
+      </c>
+      <c r="I33" s="1" t="n">
         <v>46067</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>16:26:33</t>
+          <t>17:59:31</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -2423,9 +2463,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606758103325426439', 'createTime': 1771086393, 'createTimeISO': '2026-02-14T16:26:33.000Z', 'text': 'ellos están sobre explotando porque la primera vez que hicieron eso le salió re bien', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7488</t>
+      <c r="P33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606782063303508737', 'createTime': 1771091971, 'createTimeISO': '2026-02-14T17:59:31.000Z', 'text': '2025', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7419337733036999685', 'uniqueId': 'saka019283', 'avatarThumbnail': 'https://p16-comm</t>
         </is>
       </c>
     </row>
@@ -2451,25 +2492,25 @@
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Quiero!!! 🥰</t>
+          <t>y como saben si no se puede ver?</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>1771085382</v>
+        <v>1771087831</v>
       </c>
       <c r="H34" s="1" t="n">
-        <v>46067.67340277778</v>
-      </c>
-      <c r="I34" s="2" t="n">
+        <v>46067.70174768518</v>
+      </c>
+      <c r="I34" s="1" t="n">
         <v>46067</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>16:09:42</t>
+          <t>16:50:31</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -2483,9 +2524,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606753762271019796', 'createTime': 1771085382, 'createTimeISO': '2026-02-14T16:09:42.000Z', 'text': 'Quiero!!! 🥰', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7412745403223163909', 'uniqueId': 'tdboreas', 'avatarThumbnail': 'https://p16</t>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606764253924967176', 'createTime': 1771087831, 'createTimeISO': '2026-02-14T16:50:31.000Z', 'text': 'y como saben si no se puede ver?', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6847655935771558917', 'uniqueId': 'hancel....la...h', 'a</t>
         </is>
       </c>
     </row>
@@ -2511,25 +2553,25 @@
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>amor</t>
+          <t>ellos están sobre explotando porque la primera vez que hicieron eso le salió re bien</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>1771084215</v>
+        <v>1771086393</v>
       </c>
       <c r="H35" s="1" t="n">
-        <v>46067.65989583333</v>
-      </c>
-      <c r="I35" s="2" t="n">
+        <v>46067.68510416667</v>
+      </c>
+      <c r="I35" s="1" t="n">
         <v>46067</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>15:50:15</t>
+          <t>16:26:33</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -2543,9 +2585,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606748746374120212', 'createTime': 1771084215, 'createTimeISO': '2026-02-14T15:50:15.000Z', 'text': 'amor', 'diggCount': 2, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7024651547277100037', 'uniqueId': 'maicolcepaa0520', 'avatarThumbnail': 'https://p16</t>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606758103325426439', 'createTime': 1771086393, 'createTimeISO': '2026-02-14T16:26:33.000Z', 'text': 'ellos están sobre explotando porque la primera vez que hicieron eso le salió re bien', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7488</t>
         </is>
       </c>
     </row>
@@ -2571,25 +2614,25 @@
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Una pregunta cuántas focas hay en la nueva colección de aquamochis?</t>
+          <t>Quiero!!! 🥰</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>1771079367</v>
+        <v>1771085382</v>
       </c>
       <c r="H36" s="1" t="n">
-        <v>46067.60378472223</v>
-      </c>
-      <c r="I36" s="2" t="n">
+        <v>46067.67340277778</v>
+      </c>
+      <c r="I36" s="1" t="n">
         <v>46067</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>14:29:27</t>
+          <t>16:09:42</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -2603,9 +2646,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606727932404417298', 'createTime': 1771079367, 'createTimeISO': '2026-02-14T14:29:27.000Z', 'text': 'Una pregunta cuántas focas hay en la nueva colección de aquamochis?', 'diggCount': 2, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7443532287475598391',</t>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606753762271019796', 'createTime': 1771085382, 'createTimeISO': '2026-02-14T16:09:42.000Z', 'text': 'Quiero!!! 🥰', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7412745403223163909', 'uniqueId': 'tdboreas', 'avatarThumbnail': 'https://p16</t>
         </is>
       </c>
     </row>
@@ -2631,25 +2675,25 @@
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>juguetes que terminaran en lo más profundo del océano...</t>
+          <t>amor</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>1771079356</v>
+        <v>1771084215</v>
       </c>
       <c r="H37" s="1" t="n">
-        <v>46067.60365740741</v>
-      </c>
-      <c r="I37" s="2" t="n">
+        <v>46067.65989583333</v>
+      </c>
+      <c r="I37" s="1" t="n">
         <v>46067</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>14:29:16</t>
+          <t>15:50:15</t>
         </is>
       </c>
       <c r="K37" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -2663,9 +2707,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606727884686476050', 'createTime': 1771079356, 'createTimeISO': '2026-02-14T14:29:16.000Z', 'text': 'juguetes que terminaran en lo más profundo del océano...', 'diggCount': 9, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6786307716072866822', 'uniqueId'</t>
+      <c r="P37" t="inlineStr"/>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606748746374120212', 'createTime': 1771084215, 'createTimeISO': '2026-02-14T15:50:15.000Z', 'text': 'amor', 'diggCount': 2, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7024651547277100037', 'uniqueId': 'maicolcepaa0520', 'avatarThumbnail': 'https://p16</t>
         </is>
       </c>
     </row>
@@ -2691,25 +2736,25 @@
       <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>∞</t>
+          <t>Una pregunta cuántas focas hay en la nueva colección de aquamochis?</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>1771066510</v>
+        <v>1771079367</v>
       </c>
       <c r="H38" s="1" t="n">
-        <v>46067.45497685186</v>
-      </c>
-      <c r="I38" s="2" t="n">
+        <v>46067.60378472223</v>
+      </c>
+      <c r="I38" s="1" t="n">
         <v>46067</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>10:55:10</t>
+          <t>14:29:27</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
@@ -2723,9 +2768,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606672707526771464', 'createTime': 1771066510, 'createTimeISO': '2026-02-14T10:55:10.000Z', 'text': '∞', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7545226599298352144', 'uniqueId': 'antocc13', 'avatarThumbnail': 'https://p16-common-si</t>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606727932404417298', 'createTime': 1771079367, 'createTimeISO': '2026-02-14T14:29:27.000Z', 'text': 'Una pregunta cuántas focas hay en la nueva colección de aquamochis?', 'diggCount': 2, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7443532287475598391',</t>
         </is>
       </c>
     </row>
@@ -2751,25 +2797,25 @@
       <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>tengo 143</t>
+          <t>juguetes que terminaran en lo más profundo del océano...</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>1771049239</v>
+        <v>1771079356</v>
       </c>
       <c r="H39" s="1" t="n">
-        <v>46067.25508101852</v>
-      </c>
-      <c r="I39" s="2" t="n">
+        <v>46067.60365740741</v>
+      </c>
+      <c r="I39" s="1" t="n">
         <v>46067</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>06:07:19</t>
+          <t>14:29:16</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="L39" t="n">
         <v>0</v>
@@ -2783,9 +2829,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606598502535774994', 'createTime': 1771049239, 'createTimeISO': '2026-02-14T06:07:19.000Z', 'text': 'tengo 143', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7569266375668794386', 'uniqueId': 'cata.rojas743', 'avatarThumbnail': 'https://</t>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606727884686476050', 'createTime': 1771079356, 'createTimeISO': '2026-02-14T14:29:16.000Z', 'text': 'juguetes que terminaran en lo más profundo del océano...', 'diggCount': 9, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6786307716072866822', 'uniqueId'</t>
         </is>
       </c>
     </row>
@@ -2811,21 +2858,21 @@
       <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>@Alpina 🐮 que vuelvan los muñequitos de antes de series o algo así como los guerreros</t>
+          <t>∞</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>1771043890</v>
+        <v>1771066510</v>
       </c>
       <c r="H40" s="1" t="n">
-        <v>46067.1931712963</v>
-      </c>
-      <c r="I40" s="2" t="n">
+        <v>46067.45497685186</v>
+      </c>
+      <c r="I40" s="1" t="n">
         <v>46067</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>04:38:10</t>
+          <t>10:55:10</t>
         </is>
       </c>
       <c r="K40" t="n">
@@ -2843,9 +2890,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606575506917638913', 'createTime': 1771043890, 'createTimeISO': '2026-02-14T04:38:10.000Z', 'text': '@Alpina 🐮 que vuelvan los muñequitos de antes de series o algo así como los guerreros', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '665</t>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606672707526771464', 'createTime': 1771066510, 'createTimeISO': '2026-02-14T10:55:10.000Z', 'text': '∞', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7545226599298352144', 'uniqueId': 'antocc13', 'avatarThumbnail': 'https://p16-common-si</t>
         </is>
       </c>
     </row>
@@ -2871,21 +2919,21 @@
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>yo tengo 5.😁</t>
+          <t>tengo 143</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>1771031816</v>
+        <v>1771049239</v>
       </c>
       <c r="H41" s="1" t="n">
-        <v>46067.05342592593</v>
-      </c>
-      <c r="I41" s="2" t="n">
+        <v>46067.25508101852</v>
+      </c>
+      <c r="I41" s="1" t="n">
         <v>46067</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>01:16:56</t>
+          <t>06:07:19</t>
         </is>
       </c>
       <c r="K41" t="n">
@@ -2903,9 +2951,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606523638166913812', 'createTime': 1771031816, 'createTimeISO': '2026-02-14T01:16:56.000Z', 'text': 'yo tengo 5.😁', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7427283654273844229', 'uniqueId': 'pedro.nemoga6', 'avatarThumbnail': 'https</t>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606598502535774994', 'createTime': 1771049239, 'createTimeISO': '2026-02-14T06:07:19.000Z', 'text': 'tengo 143', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7569266375668794386', 'uniqueId': 'cata.rojas743', 'avatarThumbnail': 'https://</t>
         </is>
       </c>
     </row>
@@ -2931,25 +2980,25 @@
       <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ya tengo todos</t>
+          <t>@Alpina 🐮 que vuelvan los muñequitos de antes de series o algo así como los guerreros</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>1771012282</v>
+        <v>1771043890</v>
       </c>
       <c r="H42" s="1" t="n">
-        <v>46066.82733796296</v>
-      </c>
-      <c r="I42" s="2" t="n">
-        <v>46066</v>
+        <v>46067.1931712963</v>
+      </c>
+      <c r="I42" s="1" t="n">
+        <v>46067</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>19:51:22</t>
+          <t>04:38:10</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
@@ -2963,9 +3012,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606439786600989461', 'createTime': 1771012282, 'createTimeISO': '2026-02-13T19:51:22.000Z', 'text': 'Ya tengo todos', 'diggCount': 3, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7131053865117533190', 'uniqueId': 'maria.teresa.card87', 'avatarThumbnail'</t>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606575506917638913', 'createTime': 1771043890, 'createTimeISO': '2026-02-14T04:38:10.000Z', 'text': '@Alpina 🐮 que vuelvan los muñequitos de antes de series o algo así como los guerreros', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '665</t>
         </is>
       </c>
     </row>
@@ -2991,31 +3041,33 @@
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>hola regalame todos plis🙏</t>
-        </is>
-      </c>
-      <c r="G43" t="n">
-        <v>1771012205</v>
+          <t>😏</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2026-02-14T02:08:26.000Z</t>
+        </is>
       </c>
       <c r="H43" s="1" t="n">
-        <v>46066.82644675926</v>
+        <v>46067.08918981482</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>19:50:05</t>
+          <t>02:08:26</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
       <c r="M43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr">
@@ -3023,9 +3075,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P43" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606439434900865813', 'createTime': 1771012205, 'createTimeISO': '2026-02-13T19:50:05.000Z', 'text': 'hola regalame todos plis🙏', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7576484586520216584', 'uniqueId': 'osita1941', 'avatarThumbnail</t>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>{'commentId': '7606536903240745729', 'text': '😏', 'createTime': '2026-02-14T02:08:26.000Z', 'likeCount': 0, 'replyCount': 0, 'isPinned': False, 'isAuthorLiked': False, 'userId': '7599737831011877904', 'username': 'isabellaalfonsopinzon', 'nickname': 'los tres loquitos', 'avatarUrl': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/2f2013059caaa99f2917db48b8fcf187~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=3db79554&amp;x-expires=1772902800&amp;x-signature=XeZpD%2FfnG8BiSlSCyciG</t>
         </is>
       </c>
     </row>
@@ -3051,25 +3104,25 @@
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Isaporahi eres tu ? el.que entendió entendió</t>
+          <t>yo tengo 5.😁</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>1771004406</v>
+        <v>1771031816</v>
       </c>
       <c r="H44" s="1" t="n">
-        <v>46066.73618055556</v>
-      </c>
-      <c r="I44" s="2" t="n">
-        <v>46066</v>
+        <v>46067.05342592593</v>
+      </c>
+      <c r="I44" s="1" t="n">
+        <v>46067</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>17:40:06</t>
+          <t>01:16:56</t>
         </is>
       </c>
       <c r="K44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
@@ -3083,9 +3136,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606405974844293908', 'createTime': 1771004406, 'createTimeISO': '2026-02-13T17:40:06.000Z', 'text': 'Isaporahi eres tu ? el.que entendió entendió', 'diggCount': 2, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6843103869150741509', 'uniqueId': 'provocavi</t>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606523638166913812', 'createTime': 1771031816, 'createTimeISO': '2026-02-14T01:16:56.000Z', 'text': 'yo tengo 5.😁', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7427283654273844229', 'uniqueId': 'pedro.nemoga6', 'avatarThumbnail': 'https</t>
         </is>
       </c>
     </row>
@@ -3111,31 +3165,33 @@
       <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>saque los ya yo esperé el de navidad y no llego [sticker]</t>
-        </is>
-      </c>
-      <c r="G45" t="n">
-        <v>1771000219</v>
+          <t>Ñññqqq</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2026-02-13T23:36:41.000Z</t>
+        </is>
       </c>
       <c r="H45" s="1" t="n">
-        <v>46066.68771990741</v>
+        <v>46066.98380787037</v>
       </c>
       <c r="I45" s="2" t="n">
         <v>46066</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>16:30:19</t>
+          <t>23:36:41</t>
         </is>
       </c>
       <c r="K45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr">
@@ -3143,9 +3199,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606387993427985170', 'createTime': 1771000219, 'createTimeISO': '2026-02-13T16:30:19.000Z', 'text': 'saque los ya yo esperé el de navidad y no llego [sticker]', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '7582376729450349588', 'uniqueId</t>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>{'commentId': '7606497822305174280', 'text': 'Ñññqqq', 'createTime': '2026-02-13T23:36:41.000Z', 'likeCount': 0, 'replyCount': 0, 'isPinned': False, 'isAuthorLiked': False, 'userId': '6868039799083828230', 'username': 'yarladis', 'nickname': 'Yarladis Córdoba Cór', 'avatarUrl': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/b254cf1b122ffebe4342088c9b0fe48d~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=5acb7eb7&amp;x-expires=1772902800&amp;x-signature=h3ZTou6T7iRg5DNRPs7oD3B3xiM</t>
         </is>
       </c>
     </row>
@@ -3171,31 +3228,33 @@
       <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>no esta la foca a mi hijo le dalio la foco es preciosa 🥺 le compro solo porque a mi tambien me gusta el las olvida y yo las colecciono pero🤫</t>
-        </is>
-      </c>
-      <c r="G46" t="n">
-        <v>1770991689</v>
+          <t>si 🤑🤑</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2026-02-13T22:52:37.000Z</t>
+        </is>
       </c>
       <c r="H46" s="1" t="n">
-        <v>46066.58899305556</v>
+        <v>46066.95320601852</v>
       </c>
       <c r="I46" s="2" t="n">
         <v>46066</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>14:08:09</t>
+          <t>22:52:37</t>
         </is>
       </c>
       <c r="K46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L46" t="n">
         <v>0</v>
       </c>
       <c r="M46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr">
@@ -3203,9 +3262,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P46" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606351356999615240', 'createTime': 1770991689, 'createTimeISO': '2026-02-13T14:08:09.000Z', 'text': 'no esta la foca a mi hijo le dalio la foco es preciosa 🥺 le compro solo porque a mi tambien me gusta el las olvida y yo las colecciono pero🤫', 'diggCount': 2, 'likedByAuthor': False, 'pinnedByAuthor': False, '</t>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>{'commentId': '7606486459705738002', 'text': 'si 🤑🤑', 'createTime': '2026-02-13T22:52:37.000Z', 'likeCount': 0, 'replyCount': 0, 'isPinned': False, 'isAuthorLiked': False, 'userId': '7525254651593032712', 'username': 'mr.bachecket', 'nickname': 'Mr.Bachecket', 'avatarUrl': 'https://p19-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/bbe705c134381f1a440232957cd50fa3~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=13914574&amp;x-expires=1772902800&amp;x-signature=Dh0z%2F8ZSSJdV6eZEmSDISxx1dbY%3D</t>
         </is>
       </c>
     </row>
@@ -3231,25 +3291,25 @@
       <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>😏😏😏</t>
+          <t>Ya tengo todos</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>1770986962</v>
+        <v>1771012282</v>
       </c>
       <c r="H47" s="1" t="n">
-        <v>46066.53428240741</v>
-      </c>
-      <c r="I47" s="2" t="n">
+        <v>46066.82733796296</v>
+      </c>
+      <c r="I47" s="1" t="n">
         <v>46066</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>12:49:22</t>
+          <t>19:51:22</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
@@ -3263,9 +3323,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606331029511602965', 'createTime': 1770986962, 'createTimeISO': '2026-02-13T12:49:22.000Z', 'text': '😏😏😏', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6856804310517842950', 'uniqueId': 'sanpaparu75', 'avatarThumbnail': 'https://p16-comm</t>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606439786600989461', 'createTime': 1771012282, 'createTimeISO': '2026-02-13T19:51:22.000Z', 'text': 'Ya tengo todos', 'diggCount': 3, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7131053865117533190', 'uniqueId': 'maria.teresa.card87', 'avatarThumbnail'</t>
         </is>
       </c>
     </row>
@@ -3291,25 +3352,25 @@
       <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Hola alpina tengo un pequeño negocio en crecimiento gracias a Dios donde puedo comprar los productos de alpina para venderlos?</t>
+          <t>hola regalame todos plis🙏</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>1770984390</v>
+        <v>1771012205</v>
       </c>
       <c r="H48" s="1" t="n">
-        <v>46066.50451388889</v>
-      </c>
-      <c r="I48" s="2" t="n">
+        <v>46066.82644675926</v>
+      </c>
+      <c r="I48" s="1" t="n">
         <v>46066</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>12:06:30</t>
+          <t>19:50:05</t>
         </is>
       </c>
       <c r="K48" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
@@ -3323,9 +3384,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606319986450678546', 'createTime': 1770984390, 'createTimeISO': '2026-02-13T12:06:30.000Z', 'text': 'Hola alpina tengo un pequeño negocio en crecimiento gracias a Dios donde puedo comprar los productos de alpina para venderlos?', 'diggCount': 5, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': </t>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606439434900865813', 'createTime': 1771012205, 'createTimeISO': '2026-02-13T19:50:05.000Z', 'text': 'hola regalame todos plis🙏', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7576484586520216584', 'uniqueId': 'osita1941', 'avatarThumbnail</t>
         </is>
       </c>
     </row>
@@ -3351,25 +3413,25 @@
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>🙄🫪</t>
+          <t>Isaporahi eres tu ? el.que entendió entendió</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>1770964423</v>
+        <v>1771004406</v>
       </c>
       <c r="H49" s="1" t="n">
-        <v>46066.27341435185</v>
-      </c>
-      <c r="I49" s="2" t="n">
+        <v>46066.73618055556</v>
+      </c>
+      <c r="I49" s="1" t="n">
         <v>46066</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>06:33:43</t>
+          <t>17:40:06</t>
         </is>
       </c>
       <c r="K49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L49" t="n">
         <v>0</v>
@@ -3383,9 +3445,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606234181786485521', 'createTime': 1770964423, 'createTimeISO': '2026-02-13T06:33:43.000Z', 'text': '🙄\U0001faea', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7577226738905596946', 'uniqueId': 'tingui913', 'avatarThumbnail': 'https://p1</t>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606405974844293908', 'createTime': 1771004406, 'createTimeISO': '2026-02-13T17:40:06.000Z', 'text': 'Isaporahi eres tu ? el.que entendió entendió', 'diggCount': 2, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6843103869150741509', 'uniqueId': 'provocavi</t>
         </is>
       </c>
     </row>
@@ -3411,28 +3474,28 @@
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>De lo mejor</t>
+          <t>saque los ya yo esperé el de navidad y no llego [sticker]</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>1770951402</v>
+        <v>1771000219</v>
       </c>
       <c r="H50" s="1" t="n">
-        <v>46066.12270833334</v>
-      </c>
-      <c r="I50" s="2" t="n">
+        <v>46066.68771990741</v>
+      </c>
+      <c r="I50" s="1" t="n">
         <v>46066</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>02:56:42</t>
+          <t>16:30:19</t>
         </is>
       </c>
       <c r="K50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M50" t="b">
         <v>0</v>
@@ -3443,9 +3506,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606178321075831560', 'createTime': 1770951402, 'createTimeISO': '2026-02-13T02:56:42.000Z', 'text': 'De lo mejor', 'diggCount': 3, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7238758478402094086', 'uniqueId': 'user1622760006000', 'avatarThumbnail': 'ht</t>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606387993427985170', 'createTime': 1771000219, 'createTimeISO': '2026-02-13T16:30:19.000Z', 'text': 'saque los ya yo esperé el de navidad y no llego [sticker]', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 1, 'uid': '7582376729450349588', 'uniqueId</t>
         </is>
       </c>
     </row>
@@ -3471,25 +3535,25 @@
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Extraño a mi ex</t>
+          <t>no esta la foca a mi hijo le dalio la foco es preciosa 🥺 le compro solo porque a mi tambien me gusta el las olvida y yo las colecciono pero🤫</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>1770948712</v>
+        <v>1770991689</v>
       </c>
       <c r="H51" s="1" t="n">
-        <v>46066.09157407407</v>
-      </c>
-      <c r="I51" s="2" t="n">
+        <v>46066.58899305556</v>
+      </c>
+      <c r="I51" s="1" t="n">
         <v>46066</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>02:11:52</t>
+          <t>14:08:09</t>
         </is>
       </c>
       <c r="K51" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
@@ -3503,9 +3567,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606166729261990664', 'createTime': 1770948712, 'createTimeISO': '2026-02-13T02:11:52.000Z', 'text': 'Extraño a mi ex', 'diggCount': 6, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7512221394000872456', 'uniqueId': 'papas.con.arroz35', 'avatarThumbnail':</t>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606351356999615240', 'createTime': 1770991689, 'createTimeISO': '2026-02-13T14:08:09.000Z', 'text': 'no esta la foca a mi hijo le dalio la foco es preciosa 🥺 le compro solo porque a mi tambien me gusta el las olvida y yo las colecciono pero🤫', 'diggCount': 2, 'likedByAuthor': False, 'pinnedByAuthor': False, '</t>
         </is>
       </c>
     </row>
@@ -3531,25 +3596,25 @@
       <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Yo escuché al principio Elon musk.</t>
+          <t>😏😏😏</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>1770945870</v>
+        <v>1770986962</v>
       </c>
       <c r="H52" s="1" t="n">
-        <v>46066.05868055556</v>
-      </c>
-      <c r="I52" s="2" t="n">
+        <v>46066.53428240741</v>
+      </c>
+      <c r="I52" s="1" t="n">
         <v>46066</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>01:24:30</t>
+          <t>12:49:22</t>
         </is>
       </c>
       <c r="K52" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L52" t="n">
         <v>0</v>
@@ -3563,9 +3628,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606154497101988624', 'createTime': 1770945870, 'createTimeISO': '2026-02-13T01:24:30.000Z', 'text': 'Yo escuché al principio Elon musk.', 'diggCount': 2, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7531452720693675014', 'uniqueId': 'jamifyapp', 'avatar</t>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606331029511602965', 'createTime': 1770986962, 'createTimeISO': '2026-02-13T12:49:22.000Z', 'text': '😏😏😏', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6856804310517842950', 'uniqueId': 'sanpaparu75', 'avatarThumbnail': 'https://p16-comm</t>
         </is>
       </c>
     </row>
@@ -3591,25 +3657,25 @@
       <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>lo más hermoso que he visto hoy</t>
+          <t>Hola alpina tengo un pequeño negocio en crecimiento gracias a Dios donde puedo comprar los productos de alpina para venderlos?</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>1770942820</v>
+        <v>1770984390</v>
       </c>
       <c r="H53" s="1" t="n">
-        <v>46066.02337962963</v>
-      </c>
-      <c r="I53" s="2" t="n">
+        <v>46066.50451388889</v>
+      </c>
+      <c r="I53" s="1" t="n">
         <v>46066</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>00:33:40</t>
+          <t>12:06:30</t>
         </is>
       </c>
       <c r="K53" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L53" t="n">
         <v>0</v>
@@ -3623,9 +3689,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606141431102784277', 'createTime': 1770942820, 'createTimeISO': '2026-02-13T00:33:40.000Z', 'text': 'lo más hermoso que he visto hoy', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7242097318991037445', 'uniqueId': 'noreidismaria', 'avata</t>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606319986450678546', 'createTime': 1770984390, 'createTimeISO': '2026-02-13T12:06:30.000Z', 'text': 'Hola alpina tengo un pequeño negocio en crecimiento gracias a Dios donde puedo comprar los productos de alpina para venderlos?', 'diggCount': 5, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': </t>
         </is>
       </c>
     </row>
@@ -3651,21 +3718,21 @@
       <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>@Espinosa @Andres Alzate</t>
+          <t>🙄🫪</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>1770939724</v>
+        <v>1770964423</v>
       </c>
       <c r="H54" s="1" t="n">
-        <v>46065.9875462963</v>
-      </c>
-      <c r="I54" s="2" t="n">
-        <v>46065</v>
+        <v>46066.27341435185</v>
+      </c>
+      <c r="I54" s="1" t="n">
+        <v>46066</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>23:42:04</t>
+          <t>06:33:43</t>
         </is>
       </c>
       <c r="K54" t="n">
@@ -3683,9 +3750,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606128082316460808', 'createTime': 1770939724, 'createTimeISO': '2026-02-12T23:42:04.000Z', 'text': '@𝐸𝑠𝑝𝑖𝑛𝑜𝑠𝑎 @Andres Alzate', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7183578757004854277', 'uniqueId': 'castro_01010', 'avatarThumbna</t>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606234181786485521', 'createTime': 1770964423, 'createTimeISO': '2026-02-13T06:33:43.000Z', 'text': '🙄\U0001faea', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7577226738905596946', 'uniqueId': 'tingui913', 'avatarThumbnail': 'https://p1</t>
         </is>
       </c>
     </row>
@@ -3711,25 +3779,25 @@
       <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>🥰🥰🥰🥰</t>
+          <t>De lo mejor</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>1770937571</v>
+        <v>1770951402</v>
       </c>
       <c r="H55" s="1" t="n">
-        <v>46065.96262731482</v>
-      </c>
-      <c r="I55" s="2" t="n">
-        <v>46065</v>
+        <v>46066.12270833334</v>
+      </c>
+      <c r="I55" s="1" t="n">
+        <v>46066</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>23:06:11</t>
+          <t>02:56:42</t>
         </is>
       </c>
       <c r="K55" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
@@ -3743,9 +3811,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606118835406340885', 'createTime': 1770937571, 'createTimeISO': '2026-02-12T23:06:11.000Z', 'text': '🥰🥰🥰🥰', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7511416596604437522', 'uniqueId': 'jeronimosanmiguel4', 'avatarThumbnail': 'https://</t>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606178321075831560', 'createTime': 1770951402, 'createTimeISO': '2026-02-13T02:56:42.000Z', 'text': 'De lo mejor', 'diggCount': 3, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7238758478402094086', 'uniqueId': 'user1622760006000', 'avatarThumbnail': 'ht</t>
         </is>
       </c>
     </row>
@@ -3771,25 +3840,25 @@
       <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>quiero el noctopi w</t>
+          <t>Extraño a mi ex</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>1770933583</v>
+        <v>1770948712</v>
       </c>
       <c r="H56" s="1" t="n">
-        <v>46065.91646990741</v>
-      </c>
-      <c r="I56" s="2" t="n">
-        <v>46065</v>
+        <v>46066.09157407407</v>
+      </c>
+      <c r="I56" s="1" t="n">
+        <v>46066</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>21:59:43</t>
+          <t>02:11:52</t>
         </is>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
@@ -3803,9 +3872,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606101748613169928', 'createTime': 1770933583, 'createTimeISO': '2026-02-12T21:59:43.000Z', 'text': 'quiero el noctopi w', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7449448478445814790', 'uniqueId': 'daren.calderon3', 'avatarThumbnail</t>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606166729261990664', 'createTime': 1770948712, 'createTimeISO': '2026-02-13T02:11:52.000Z', 'text': 'Extraño a mi ex', 'diggCount': 6, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7512221394000872456', 'uniqueId': 'papas.con.arroz35', 'avatarThumbnail':</t>
         </is>
       </c>
     </row>
@@ -3831,25 +3901,25 @@
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>pov mochis se quedan sin ideas o ya se un mochi de agua</t>
+          <t>Yo escuché al principio Elon musk.</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>1770930491</v>
+        <v>1770945870</v>
       </c>
       <c r="H57" s="1" t="n">
-        <v>46065.88068287037</v>
-      </c>
-      <c r="I57" s="2" t="n">
-        <v>46065</v>
+        <v>46066.05868055556</v>
+      </c>
+      <c r="I57" s="1" t="n">
+        <v>46066</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>21:08:11</t>
+          <t>01:24:30</t>
         </is>
       </c>
       <c r="K57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
@@ -3863,9 +3933,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606088482087600904', 'createTime': 1770930491, 'createTimeISO': '2026-02-12T21:08:11.000Z', 'text': 'pov mochis se quedan sin ideas o ya se un mochi de agua', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7554069625988105223', 'uniqueId':</t>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606154497101988624', 'createTime': 1770945870, 'createTimeISO': '2026-02-13T01:24:30.000Z', 'text': 'Yo escuché al principio Elon musk.', 'diggCount': 2, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7531452720693675014', 'uniqueId': 'jamifyapp', 'avatar</t>
         </is>
       </c>
     </row>
@@ -3891,21 +3962,21 @@
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>noooooo otra vez son 40 😭</t>
+          <t>lo más hermoso que he visto hoy</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>1770928296</v>
+        <v>1770942820</v>
       </c>
       <c r="H58" s="1" t="n">
-        <v>46065.85527777778</v>
-      </c>
-      <c r="I58" s="2" t="n">
-        <v>46065</v>
+        <v>46066.02337962963</v>
+      </c>
+      <c r="I58" s="1" t="n">
+        <v>46066</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>20:31:36</t>
+          <t>00:33:40</t>
         </is>
       </c>
       <c r="K58" t="n">
@@ -3923,9 +3994,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606079011882943250', 'createTime': 1770928296, 'createTimeISO': '2026-02-12T20:31:36.000Z', 'text': 'noooooo otra vez son 40 😭', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7578335295364924434', 'uniqueId': 'santiagodiaz3487', 'avatarTh</t>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606141431102784277', 'createTime': 1770942820, 'createTimeISO': '2026-02-13T00:33:40.000Z', 'text': 'lo más hermoso que he visto hoy', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7242097318991037445', 'uniqueId': 'noreidismaria', 'avata</t>
         </is>
       </c>
     </row>
@@ -3951,28 +4023,28 @@
       <c r="E59" t="inlineStr"/>
       <c r="F59" t="inlineStr">
         <is>
-          <t>YA PAREEEEEN</t>
+          <t>@Espinosa @Andres Alzate</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>1770924722</v>
+        <v>1770939724</v>
       </c>
       <c r="H59" s="1" t="n">
-        <v>46065.81391203704</v>
-      </c>
-      <c r="I59" s="2" t="n">
+        <v>46065.9875462963</v>
+      </c>
+      <c r="I59" s="1" t="n">
         <v>46065</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>19:32:02</t>
+          <t>23:42:04</t>
         </is>
       </c>
       <c r="K59" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="L59" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M59" t="b">
         <v>0</v>
@@ -3983,9 +4055,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606063681915749141', 'createTime': 1770924722, 'createTimeISO': '2026-02-12T19:32:02.000Z', 'text': 'YA PAREEEEEN', 'diggCount': 34, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 4, 'uid': '7483155009288733717', 'uniqueId': 'limoncito3212', 'avatarThumbnail': 'http</t>
+      <c r="P59" t="inlineStr"/>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606128082316460808', 'createTime': 1770939724, 'createTimeISO': '2026-02-12T23:42:04.000Z', 'text': '@𝐸𝑠𝑝𝑖𝑛𝑜𝑠𝑎 @Andres Alzate', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7183578757004854277', 'uniqueId': 'castro_01010', 'avatarThumbna</t>
         </is>
       </c>
     </row>
@@ -4011,31 +4084,33 @@
       <c r="E60" t="inlineStr"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Alpina ayuda yo estoy emocionada por que estoy acá desde los Mochis , ilumi Mochis, mini Mochis, los Mochis para la maleta, dino Mochis, jojo Mochis, y ahora los aqua Mochis no te miento no los pude conseguir todos no tengo ni 1 colección completa y lo quiero intentar con los aqua Mochis plis Alpina yo quiero una caja de aqua Mochis estoy en todo pero no en los oxxos no han llegado para los 4 logos ni los yoyo yoyo por favor pido ayuda para la lavadora</t>
-        </is>
-      </c>
-      <c r="G60" t="n">
-        <v>1770921388</v>
+          <t>los Mochis son eternos</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2026-02-12T23:35:51.000Z</t>
+        </is>
       </c>
       <c r="H60" s="1" t="n">
-        <v>46065.77532407407</v>
+        <v>46065.98322916667</v>
       </c>
       <c r="I60" s="2" t="n">
         <v>46065</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>18:36:28</t>
+          <t>23:35:51</t>
         </is>
       </c>
       <c r="K60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L60" t="n">
         <v>0</v>
       </c>
       <c r="M60" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr">
@@ -4043,9 +4118,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606049388909953810', 'createTime': 1770921388, 'createTimeISO': '2026-02-12T18:36:28.000Z', 'text': 'Alpina ayuda yo estoy emocionada por que estoy acá desde los Mochis , ilumi Mochis, mini Mochis, los Mochis para la maleta, dino Mochis, jojo Mochis, y ahora los aqua Mochis no te miento no los pude conseguir </t>
+      <c r="P60" t="inlineStr"/>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>{'commentId': '7606126465424540436', 'text': 'los Mochis son eternos', 'createTime': '2026-02-12T23:35:51.000Z', 'likeCount': 3, 'replyCount': 0, 'isPinned': False, 'isAuthorLiked': False, 'userId': '7446423531677582342', 'username': 'jorgito_0x', 'nickname': 'Jorgito_0x', 'avatarUrl': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/01e8819ff0a3fd58d3e392dee94c41bb~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=ce375298&amp;x-expires=1772902800&amp;x-signature=PLUsYdtJnPWiFFqpUH6</t>
         </is>
       </c>
     </row>
@@ -4071,21 +4147,21 @@
       <c r="E61" t="inlineStr"/>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Yo tengo 6🫧</t>
+          <t>🥰🥰🥰🥰</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>1770920196</v>
+        <v>1770937571</v>
       </c>
       <c r="H61" s="1" t="n">
-        <v>46065.76152777778</v>
-      </c>
-      <c r="I61" s="2" t="n">
+        <v>46065.96262731482</v>
+      </c>
+      <c r="I61" s="1" t="n">
         <v>46065</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>18:16:36</t>
+          <t>23:06:11</t>
         </is>
       </c>
       <c r="K61" t="n">
@@ -4103,9 +4179,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606044275377652501', 'createTime': 1770920196, 'createTimeISO': '2026-02-12T18:16:36.000Z', 'text': 'Yo tengo 6🫧', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7321136002860008454', 'uniqueId': 'gatobias.y.titosaurio', 'avatarThumbnail':</t>
+      <c r="P61" t="inlineStr"/>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606118835406340885', 'createTime': 1770937571, 'createTimeISO': '2026-02-12T23:06:11.000Z', 'text': '🥰🥰🥰🥰', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7511416596604437522', 'uniqueId': 'jeronimosanmiguel4', 'avatarThumbnail': 'https://</t>
         </is>
       </c>
     </row>
@@ -4131,21 +4208,21 @@
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr">
         <is>
-          <t>SOLO ALQUERIA🤪🤪🤪</t>
+          <t>quiero el noctopi w</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>1770917296</v>
+        <v>1770933583</v>
       </c>
       <c r="H62" s="1" t="n">
-        <v>46065.72796296296</v>
-      </c>
-      <c r="I62" s="2" t="n">
+        <v>46065.91646990741</v>
+      </c>
+      <c r="I62" s="1" t="n">
         <v>46065</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>17:28:16</t>
+          <t>21:59:43</t>
         </is>
       </c>
       <c r="K62" t="n">
@@ -4163,9 +4240,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P62" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606031806882939669', 'createTime': 1770917296, 'createTimeISO': '2026-02-12T17:28:16.000Z', 'text': 'SOLO ALQUERIA🤪🤪🤪', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7590083135682200597', 'uniqueId': 'andresito0777', 'avatarThumbnail': 'h</t>
+      <c r="P62" t="inlineStr"/>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606101748613169928', 'createTime': 1770933583, 'createTimeISO': '2026-02-12T21:59:43.000Z', 'text': 'quiero el noctopi w', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7449448478445814790', 'uniqueId': 'daren.calderon3', 'avatarThumbnail</t>
         </is>
       </c>
     </row>
@@ -4191,21 +4269,23 @@
       <c r="E63" t="inlineStr"/>
       <c r="F63" t="inlineStr">
         <is>
-          <t>hermosa mil bendiciones</t>
-        </is>
-      </c>
-      <c r="G63" t="n">
-        <v>1770914825</v>
+          <t>???</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>2026-02-12T21:23:57.000Z</t>
+        </is>
       </c>
       <c r="H63" s="1" t="n">
-        <v>46065.69936342593</v>
+        <v>46065.89163194445</v>
       </c>
       <c r="I63" s="2" t="n">
         <v>46065</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>16:47:05</t>
+          <t>21:23:57</t>
         </is>
       </c>
       <c r="K63" t="n">
@@ -4215,7 +4295,7 @@
         <v>0</v>
       </c>
       <c r="M63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N63" t="inlineStr"/>
       <c r="O63" t="inlineStr">
@@ -4223,9 +4303,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606021231103673105', 'createTime': 1770914825, 'createTimeISO': '2026-02-12T16:47:05.000Z', 'text': 'hermosa mil bendiciones', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6964522060413436933', 'uniqueId': 'antoniocarlosdomi3', 'avatarTh</t>
+      <c r="P63" t="inlineStr"/>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>{'commentId': '7606092519969866514', 'text': '???', 'createTime': '2026-02-12T21:23:57.000Z', 'likeCount': 0, 'replyCount': 0, 'isPinned': False, 'isAuthorLiked': False, 'userId': '7525254651593032712', 'username': 'mr.bachecket', 'nickname': 'Mr.Bachecket', 'avatarUrl': 'https://p19-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/bbe705c134381f1a440232957cd50fa3~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=13914574&amp;x-expires=1772902800&amp;x-signature=Dh0z%2F8ZSSJdV6eZEmSDISxx1dbY%3D&amp;t</t>
         </is>
       </c>
     </row>
@@ -4251,25 +4332,25 @@
       <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr">
         <is>
-          <t>sii que hermoso ya los quiero</t>
+          <t>pov mochis se quedan sin ideas o ya se un mochi de agua</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>1770914092</v>
+        <v>1770930491</v>
       </c>
       <c r="H64" s="1" t="n">
-        <v>46065.69087962963</v>
-      </c>
-      <c r="I64" s="2" t="n">
+        <v>46065.88068287037</v>
+      </c>
+      <c r="I64" s="1" t="n">
         <v>46065</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>16:34:52</t>
+          <t>21:08:11</t>
         </is>
       </c>
       <c r="K64" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
@@ -4283,9 +4364,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P64" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606018071988634369', 'createTime': 1770914092, 'createTimeISO': '2026-02-12T16:34:52.000Z', 'text': 'sii que hermoso ya los quiero', 'diggCount': 4, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7139507407827567621', 'uniqueId': 'xux400', 'avatarThumbnai</t>
+      <c r="P64" t="inlineStr"/>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606088482087600904', 'createTime': 1770930491, 'createTimeISO': '2026-02-12T21:08:11.000Z', 'text': 'pov mochis se quedan sin ideas o ya se un mochi de agua', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7554069625988105223', 'uniqueId':</t>
         </is>
       </c>
     </row>
@@ -4311,25 +4393,25 @@
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="inlineStr">
         <is>
-          <t>jajaja ya tienen muy quemados los mochos</t>
+          <t>noooooo otra vez son 40 😭</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>1770912313</v>
+        <v>1770928296</v>
       </c>
       <c r="H65" s="1" t="n">
-        <v>46065.67028935185</v>
-      </c>
-      <c r="I65" s="2" t="n">
+        <v>46065.85527777778</v>
+      </c>
+      <c r="I65" s="1" t="n">
         <v>46065</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>16:05:13</t>
+          <t>20:31:36</t>
         </is>
       </c>
       <c r="K65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
@@ -4343,9 +4425,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606010431609963285', 'createTime': 1770912313, 'createTimeISO': '2026-02-12T16:05:13.000Z', 'text': 'jajaja ya tienen muy quemados los mochos', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6517432558840452111', 'uniqueId': '223345fabio',</t>
+      <c r="P65" t="inlineStr"/>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606079011882943250', 'createTime': 1770928296, 'createTimeISO': '2026-02-12T20:31:36.000Z', 'text': 'noooooo otra vez son 40 😭', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7578335295364924434', 'uniqueId': 'santiagodiaz3487', 'avatarTh</t>
         </is>
       </c>
     </row>
@@ -4371,28 +4454,28 @@
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>dioss mio mi hija tiene todos los dinosaurios, los de navidad jajajaa y ahora salen estos jajajaj</t>
+          <t>YA PAREEEEEN</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>1770911933</v>
+        <v>1770924722</v>
       </c>
       <c r="H66" s="1" t="n">
-        <v>46065.6658912037</v>
-      </c>
-      <c r="I66" s="2" t="n">
+        <v>46065.81391203704</v>
+      </c>
+      <c r="I66" s="1" t="n">
         <v>46065</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>15:58:53</t>
+          <t>19:32:02</t>
         </is>
       </c>
       <c r="K66" t="n">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="L66" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M66" t="b">
         <v>0</v>
@@ -4403,9 +4486,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P66" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606008795130921748', 'createTime': 1770911933, 'createTimeISO': '2026-02-12T15:58:53.000Z', 'text': 'dioss mio mi hija tiene todos los dinosaurios, los de navidad jajajaa y ahora salen estos jajajaj', 'diggCount': 10, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 2</t>
+      <c r="P66" t="inlineStr"/>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606063681915749141', 'createTime': 1770924722, 'createTimeISO': '2026-02-12T19:32:02.000Z', 'text': 'YA PAREEEEEN', 'diggCount': 34, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 4, 'uid': '7483155009288733717', 'uniqueId': 'limoncito3212', 'avatarThumbnail': 'http</t>
         </is>
       </c>
     </row>
@@ -4431,21 +4515,21 @@
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>a Mochis amo los Mochis</t>
+          <t>Alpina ayuda yo estoy emocionada por que estoy acá desde los Mochis , ilumi Mochis, mini Mochis, los Mochis para la maleta, dino Mochis, jojo Mochis, y ahora los aqua Mochis no te miento no los pude conseguir todos no tengo ni 1 colección completa y lo quiero intentar con los aqua Mochis plis Alpina yo quiero una caja de aqua Mochis estoy en todo pero no en los oxxos no han llegado para los 4 logos ni los yoyo yoyo por favor pido ayuda para la lavadora</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>1770891501</v>
+        <v>1770921388</v>
       </c>
       <c r="H67" s="1" t="n">
-        <v>46065.42940972222</v>
-      </c>
-      <c r="I67" s="2" t="n">
+        <v>46065.77532407407</v>
+      </c>
+      <c r="I67" s="1" t="n">
         <v>46065</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>10:18:21</t>
+          <t>18:36:28</t>
         </is>
       </c>
       <c r="K67" t="n">
@@ -4463,9 +4547,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7605921005799211797', 'createTime': 1770891501, 'createTimeISO': '2026-02-12T10:18:21.000Z', 'text': 'a Mochis amo los Mochis', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7577169276382807048', 'uniqueId': 'sofia18597', 'avatarThumbnail'</t>
+      <c r="P67" t="inlineStr"/>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606049388909953810', 'createTime': 1770921388, 'createTimeISO': '2026-02-12T18:36:28.000Z', 'text': 'Alpina ayuda yo estoy emocionada por que estoy acá desde los Mochis , ilumi Mochis, mini Mochis, los Mochis para la maleta, dino Mochis, jojo Mochis, y ahora los aqua Mochis no te miento no los pude conseguir </t>
         </is>
       </c>
     </row>
@@ -4491,28 +4576,28 @@
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo</t>
+          <t>Yo tengo 6🫧</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>1770891189</v>
+        <v>1770920196</v>
       </c>
       <c r="H68" s="1" t="n">
-        <v>46065.42579861111</v>
-      </c>
-      <c r="I68" s="2" t="n">
+        <v>46065.76152777778</v>
+      </c>
+      <c r="I68" s="1" t="n">
         <v>46065</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>10:13:09</t>
+          <t>18:16:36</t>
         </is>
       </c>
       <c r="K68" t="n">
         <v>0</v>
       </c>
       <c r="L68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M68" t="b">
         <v>0</v>
@@ -4523,9 +4608,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P68" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7605919710110106388', 'createTime': 1770891189, 'createTimeISO': '2026-02-12T10:13:09.000Z', 'text': 'yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo</t>
+      <c r="P68" t="inlineStr"/>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606044275377652501', 'createTime': 1770920196, 'createTimeISO': '2026-02-12T18:16:36.000Z', 'text': 'Yo tengo 6🫧', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7321136002860008454', 'uniqueId': 'gatobias.y.titosaurio', 'avatarThumbnail':</t>
         </is>
       </c>
     </row>
@@ -4551,28 +4637,28 @@
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="inlineStr">
         <is>
-          <t>mi hija me hizo comprar todos los de dinosaurios, navidad ,y ahora sacan sus favoritos 🥴🥴 animales marinos 🥴🤣🤣🤣</t>
+          <t>SOLO ALQUERIA🤪🤪🤪</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>1770890495</v>
+        <v>1770917296</v>
       </c>
       <c r="H69" s="1" t="n">
-        <v>46065.4177662037</v>
-      </c>
-      <c r="I69" s="2" t="n">
+        <v>46065.72796296296</v>
+      </c>
+      <c r="I69" s="1" t="n">
         <v>46065</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>10:01:35</t>
+          <t>17:28:16</t>
         </is>
       </c>
       <c r="K69" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="L69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M69" t="b">
         <v>0</v>
@@ -4583,9 +4669,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P69" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7605916734050026248', 'createTime': 1770890495, 'createTimeISO': '2026-02-12T10:01:35.000Z', 'text': 'mi hija me hizo comprar todos los de dinosaurios, navidad ,y ahora sacan sus favoritos 🥴🥴 animales marinos 🥴🤣🤣🤣', 'diggCount': 15, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCo</t>
+      <c r="P69" t="inlineStr"/>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606031806882939669', 'createTime': 1770917296, 'createTimeISO': '2026-02-12T17:28:16.000Z', 'text': 'SOLO ALQUERIA🤪🤪🤪', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7590083135682200597', 'uniqueId': 'andresito0777', 'avatarThumbnail': 'h</t>
         </is>
       </c>
     </row>
@@ -4611,21 +4698,21 @@
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="inlineStr">
         <is>
-          <t>yo quiero</t>
+          <t>hermosa mil bendiciones</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>1770889565</v>
+        <v>1770914825</v>
       </c>
       <c r="H70" s="1" t="n">
-        <v>46065.40700231482</v>
-      </c>
-      <c r="I70" s="2" t="n">
+        <v>46065.69936342593</v>
+      </c>
+      <c r="I70" s="1" t="n">
         <v>46065</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>09:46:05</t>
+          <t>16:47:05</t>
         </is>
       </c>
       <c r="K70" t="n">
@@ -4643,9 +4730,10 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7605912711730856705', 'createTime': 1770889565, 'createTimeISO': '2026-02-12T09:46:05.000Z', 'text': 'yo quiero', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7336195362929787910', 'uniqueId': 'melany.noriega30', 'avatarThumbnail': 'https</t>
+      <c r="P70" t="inlineStr"/>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606021231103673105', 'createTime': 1770914825, 'createTimeISO': '2026-02-12T16:47:05.000Z', 'text': 'hermosa mil bendiciones', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6964522060413436933', 'uniqueId': 'antoniocarlosdomi3', 'avatarTh</t>
         </is>
       </c>
     </row>
@@ -4671,25 +4759,25 @@
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Yo quirooooo 🥺</t>
+          <t>sii que hermoso ya los quiero</t>
         </is>
       </c>
       <c r="G71" t="n">
-        <v>1770884424</v>
+        <v>1770914092</v>
       </c>
       <c r="H71" s="1" t="n">
-        <v>46065.3475</v>
-      </c>
-      <c r="I71" s="2" t="n">
+        <v>46065.69087962963</v>
+      </c>
+      <c r="I71" s="1" t="n">
         <v>46065</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>08:20:24</t>
+          <t>16:34:52</t>
         </is>
       </c>
       <c r="K71" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L71" t="n">
         <v>0</v>
@@ -4703,59 +4791,54 @@
           <t>https://www.tiktok.com/@</t>
         </is>
       </c>
-      <c r="P71" t="inlineStr">
-        <is>
-          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7605890624642024212', 'createTime': 1770884424, 'createTimeISO': '2026-02-12T08:20:24.000Z', 'text': 'Yo quirooooo 🥺', 'diggCount': 2, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6573387218701811717', 'uniqueId': 'papita_0401', 'avatarThumbnail': 'https</t>
+      <c r="P71" t="inlineStr"/>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606018071988634369', 'createTime': 1770914092, 'createTimeISO': '2026-02-12T16:34:52.000Z', 'text': 'sii que hermoso ya los quiero', 'diggCount': 4, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7139507407827567621', 'uniqueId': 'xux400', 'avatarThumbnai</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DQZl34lDDef/</t>
+          <t>https://vt.tiktok.com/ZSmCS4nn2/</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DQZl34lDDef/</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>mm.____.3x</t>
-        </is>
-      </c>
+          <t>https://vt.tiktok.com/ZSmCS4nn2/</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Y esa cosa negra en la pared🤨🤨🤨</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>2025-11-20T01:56:08.000Z</t>
-        </is>
+          <t>jajaja ya tienen muy quemados los mochos</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>1770912313</v>
       </c>
       <c r="H72" s="1" t="n">
-        <v>45981.08064814815</v>
-      </c>
-      <c r="I72" s="2" t="n">
-        <v>45981</v>
+        <v>46065.67028935185</v>
+      </c>
+      <c r="I72" s="1" t="n">
+        <v>46065</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>01:56:08</t>
+          <t>16:05:13</t>
         </is>
       </c>
       <c r="K72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L72" t="n">
         <v>0</v>
@@ -4766,65 +4849,60 @@
       <c r="N72" t="inlineStr"/>
       <c r="O72" t="inlineStr">
         <is>
-          <t>https://instagram.com/mm.____.3x</t>
-        </is>
-      </c>
-      <c r="P72" t="inlineStr">
-        <is>
-          <t>{'postUrl': 'https://www.instagram.com/p/DQZl34lDDef/', 'commentUrl': 'https://www.instagram.com/p/DQZl34lDDef/c/17878999155332166', 'id': '17878999155332166', 'text': 'Y esa cosa negra en la pared🤨🤨🤨', 'ownerUsername': 'mm.____.3x', 'ownerProfilePicUrl': 'https://scontent-iad3-1.cdninstagram.com/v/t51.89012-19/573323465_1219825463302212_7278921664109726296_n.png?stp=dst-webp_s150x150&amp;_nc_cat=1&amp;ig_cache_key=YW5vbnltb3VzX3Byb2ZpbGVfcGlj.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InBy</t>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr"/>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606010431609963285', 'createTime': 1770912313, 'createTimeISO': '2026-02-12T16:05:13.000Z', 'text': 'jajaja ya tienen muy quemados los mochos', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6517432558840452111', 'uniqueId': '223345fabio',</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
+        <v>1</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>https://vt.tiktok.com/ZSmCS4nn2/</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>https://vt.tiktok.com/ZSmCS4nn2/</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>dioss mio mi hija tiene todos los dinosaurios, los de navidad jajajaa y ahora salen estos jajajaj</t>
+        </is>
+      </c>
+      <c r="G73" t="n">
+        <v>1770911933</v>
+      </c>
+      <c r="H73" s="1" t="n">
+        <v>46065.6658912037</v>
+      </c>
+      <c r="I73" s="1" t="n">
+        <v>46065</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>15:58:53</t>
+        </is>
+      </c>
+      <c r="K73" t="n">
+        <v>10</v>
+      </c>
+      <c r="L73" t="n">
         <v>2</v>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Instagram</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DQZl34lDDef/</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/p/DQZl34lDDef/</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>luis_dacop</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Dejame negociar el riñón que me sobra 🙄</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>2025-11-20T00:44:24.000Z</t>
-        </is>
-      </c>
-      <c r="H73" s="1" t="n">
-        <v>45981.03083333333</v>
-      </c>
-      <c r="I73" s="2" t="n">
-        <v>45981</v>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>00:44:24</t>
-        </is>
-      </c>
-      <c r="K73" t="n">
-        <v>1</v>
-      </c>
-      <c r="L73" t="n">
-        <v>0</v>
       </c>
       <c r="M73" t="b">
         <v>0</v>
@@ -4832,124 +4910,116 @@
       <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr">
         <is>
-          <t>https://instagram.com/luis_dacop</t>
-        </is>
-      </c>
-      <c r="P73" t="inlineStr">
-        <is>
-          <t>{'postUrl': 'https://www.instagram.com/p/DQZl34lDDef/', 'commentUrl': 'https://www.instagram.com/p/DQZl34lDDef/c/17980855841926100', 'id': '17980855841926100', 'text': 'Dejame negociar el riñón que me sobra 🙄', 'ownerUsername': 'luis_dacop', 'ownerProfilePicUrl': 'https://scontent-iad3-1.cdninstagram.com/v/t51.82787-19/625230176_18095921168313175_2177686544448637796_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=107&amp;ig_cache_key=GGBBRCVX6x75JEpAAGRLAtJfsjgebmNDAQAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=6694</t>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr"/>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7606008795130921748', 'createTime': 1770911933, 'createTimeISO': '2026-02-12T15:58:53.000Z', 'text': 'dioss mio mi hija tiene todos los dinosaurios, los de navidad jajajaa y ahora salen estos jajajaj', 'diggCount': 10, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 2</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DQZl34lDDef/</t>
+          <t>https://vt.tiktok.com/ZSmCS4nn2/</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DQZl34lDDef/</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>solo.roberto</t>
-        </is>
-      </c>
+          <t>https://vt.tiktok.com/ZSmCS4nn2/</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr"/>
       <c r="F74" t="inlineStr">
         <is>
-          <t>No gracias alpina está muy cara !</t>
+          <t>Igual mi hijo 🤦‍♀️🤦‍♀️</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>2025-11-19T00:17:09.000Z</t>
+          <t>2026-02-12T14:53:56.000Z</t>
         </is>
       </c>
       <c r="H74" s="1" t="n">
-        <v>45980.01190972222</v>
+        <v>46065.62078703703</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>45980</v>
+        <v>46065</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>00:17:09</t>
+          <t>14:53:56</t>
         </is>
       </c>
       <c r="K74" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L74" t="n">
         <v>0</v>
       </c>
       <c r="M74" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr">
         <is>
-          <t>https://instagram.com/solo.roberto</t>
-        </is>
-      </c>
-      <c r="P74" t="inlineStr">
-        <is>
-          <t>{'postUrl': 'https://www.instagram.com/p/DQZl34lDDef/', 'commentUrl': 'https://www.instagram.com/p/DQZl34lDDef/c/17869377699399109', 'id': '17869377699399109', 'text': 'No gracias alpina está muy cara !', 'ownerUsername': 'solo.roberto', 'ownerProfilePicUrl': 'https://scontent-iad3-1.cdninstagram.com/v/t51.75761-19/497451179_18462727648079276_6370863006333456058_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=104&amp;ig_cache_key=GKuAph2sbQzDwJdBALrOLmUm2mlYbvEnAQAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;e</t>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr"/>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>{'commentId': '7605992064228328212', 'text': 'Igual mi hijo 🤦\u200d♀️🤦\u200d♀️', 'createTime': '2026-02-12T14:53:56.000Z', 'likeCount': 0, 'replyCount': 0, 'isPinned': False, 'isAuthorLiked': False, 'userId': '7476588311118709780', 'username': 'kolimte', 'nickname': 'kolim', 'avatarUrl': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/8aa671e892280aa6117fb7a40e9db2c0~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=59330f77&amp;x-expires=1772902800&amp;x-signature=K4hyoRW9N2%2FwkVi</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Instagram</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DQZl34lDDef/</t>
+          <t>https://vt.tiktok.com/ZSmCS4nn2/</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/p/DQZl34lDDef/</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>jeanb_555</t>
-        </is>
-      </c>
+          <t>https://vt.tiktok.com/ZSmCS4nn2/</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
-          <t>HaaaaAAA!</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>2025-11-17T01:13:39.000Z</t>
-        </is>
+          <t>a Mochis amo los Mochis</t>
+        </is>
+      </c>
+      <c r="G75" t="n">
+        <v>1770891501</v>
       </c>
       <c r="H75" s="1" t="n">
-        <v>45978.05114583333</v>
-      </c>
-      <c r="I75" s="2" t="n">
-        <v>45978</v>
+        <v>46065.42940972222</v>
+      </c>
+      <c r="I75" s="1" t="n">
+        <v>46065</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>01:13:39</t>
+          <t>10:18:21</t>
         </is>
       </c>
       <c r="K75" t="n">
@@ -4964,491 +5034,1059 @@
       <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr">
         <is>
-          <t>https://instagram.com/jeanb_555</t>
-        </is>
-      </c>
-      <c r="P75" t="inlineStr">
-        <is>
-          <t>{'postUrl': 'https://www.instagram.com/p/DQZl34lDDef/', 'commentUrl': 'https://www.instagram.com/p/DQZl34lDDef/c/18327825274240575', 'id': '18327825274240575', 'text': 'HaaaaAAA!', 'ownerUsername': 'jeanb_555', 'ownerProfilePicUrl': 'https://scontent-iad3-1.cdninstagram.com/v/t51.82787-19/619082747_17977100765977609_5485987972083477950_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=108&amp;ig_cache_key=GPtz5iQJXD-xE94-AL7tGZ7_JCJMbmNDAQAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InBy</t>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr"/>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7605921005799211797', 'createTime': 1770891501, 'createTimeISO': '2026-02-12T10:18:21.000Z', 'text': 'a Mochis amo los Mochis', 'diggCount': 1, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7577169276382807048', 'uniqueId': 'sofia18597', 'avatarThumbnail'</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Facebook</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/1318637550308481/</t>
+          <t>https://vt.tiktok.com/ZSmCS4nn2/</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/1318637550308481/</t>
+          <t>https://vt.tiktok.com/ZSmCS4nn2/</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Holavivianapaternia</t>
+          <t>😁</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>2026-01-18T21:45:53.000Z</t>
+          <t>2026-02-12T10:13:14.000Z</t>
         </is>
       </c>
       <c r="H76" s="1" t="n">
-        <v>46040.90686342592</v>
+        <v>46065.42585648148</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>46040</v>
+        <v>46065</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>21:45:53</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>10:13:14</t>
+        </is>
+      </c>
+      <c r="K76" t="n">
+        <v>0</v>
       </c>
       <c r="L76" t="n">
         <v>0</v>
       </c>
       <c r="M76" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N76" t="inlineStr"/>
-      <c r="O76" t="inlineStr"/>
-      <c r="P76" t="inlineStr">
-        <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/1318637550308481/', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid07ABytcFMswuYfZXzEvApUr8Z5dWYLLCCCK83g8dRCHkNnDoLghdZYeDPwM1muMnrl?comment_id=1123930883027156', 'commentId': '1123930883027156', 'id': 'Y29tbWVudDoxMzE4NjM4MDUwMzA4NDMxXzExMjM5MzA4ODMwMjcxNTY=', 'feedbackId': 'ZmVlZGJhY2s6MTMxODYzODA1MDMwODQzMV8xMTIzOTMwODgzMDI3MTU2', 'date': '2026-01-18T21:45:53.000Z', 'text': 'Holavivianapaternia', 'profileUrl': 'https:</t>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr"/>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>{'commentId': '7605919689387459349', 'text': '😁', 'createTime': '2026-02-12T10:13:14.000Z', 'likeCount': 0, 'replyCount': 0, 'isPinned': False, 'isAuthorLiked': False, 'userId': '7535984268544869394', 'username': 'a_k10773', 'nickname': 'Mari l H v', 'avatarUrl': 'https://p16-common-sign.tiktokcdn-us.com/tos-alisg-avt-0068/95e175bb1aa9a2a8bb6408c5d36a1f3e~tplv-tiktokx-cropcenter:100:100.jpg?dr=9640&amp;refresh_token=5be9f68c&amp;x-expires=1772902800&amp;x-signature=um9xPmzpQhK7cGxXw7VZGWKpKmI%3D&amp;t=4d5b0474&amp;</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Facebook</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/1318637550308481/</t>
+          <t>https://vt.tiktok.com/ZSmCS4nn2/</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/1318637550308481/</t>
+          <t>https://vt.tiktok.com/ZSmCS4nn2/</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Salome</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>2026-01-14T23:51:57.000Z</t>
-        </is>
+          <t>yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo</t>
+        </is>
+      </c>
+      <c r="G77" t="n">
+        <v>1770891189</v>
       </c>
       <c r="H77" s="1" t="n">
-        <v>46036.99440972223</v>
-      </c>
-      <c r="I77" s="2" t="n">
-        <v>46036</v>
+        <v>46065.42579861111</v>
+      </c>
+      <c r="I77" s="1" t="n">
+        <v>46065</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>23:51:57</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>10:13:09</t>
+        </is>
+      </c>
+      <c r="K77" t="n">
+        <v>0</v>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M77" t="b">
         <v>0</v>
       </c>
       <c r="N77" t="inlineStr"/>
-      <c r="O77" t="inlineStr"/>
-      <c r="P77" t="inlineStr">
-        <is>
-          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/1318637550308481/', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid07ABytcFMswuYfZXzEvApUr8Z5dWYLLCCCK83g8dRCHkNnDoLghdZYeDPwM1muMnrl?comment_id=1412783150373933', 'commentId': '1412783150373933', 'id': 'Y29tbWVudDoxMzE4NjM4MDUwMzA4NDMxXzE0MTI3ODMxNTAzNzM5MzM=', 'feedbackId': 'ZmVlZGJhY2s6MTMxODYzODA1MDMwODQzMV8xNDEyNzgzMTUwMzczOTMz', 'date': '2026-01-14T23:51:57.000Z', 'text': 'Salome', 'profileUrl': 'https://www.faceboo</t>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr"/>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7605919710110106388', 'createTime': 1770891189, 'createTimeISO': '2026-02-12T10:13:09.000Z', 'text': 'yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo yoooooooooooo</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Facebook</t>
+          <t>TikTok</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/1318637550308481/</t>
+          <t>https://vt.tiktok.com/ZSmCS4nn2/</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/100064867445065/posts/1318637550308481/</t>
+          <t>https://vt.tiktok.com/ZSmCS4nn2/</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="inlineStr">
         <is>
+          <t>mi hija me hizo comprar todos los de dinosaurios, navidad ,y ahora sacan sus favoritos 🥴🥴 animales marinos 🥴🤣🤣🤣</t>
+        </is>
+      </c>
+      <c r="G78" t="n">
+        <v>1770890495</v>
+      </c>
+      <c r="H78" s="1" t="n">
+        <v>46065.4177662037</v>
+      </c>
+      <c r="I78" s="1" t="n">
+        <v>46065</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>10:01:35</t>
+        </is>
+      </c>
+      <c r="K78" t="n">
+        <v>15</v>
+      </c>
+      <c r="L78" t="n">
+        <v>1</v>
+      </c>
+      <c r="M78" t="b">
+        <v>0</v>
+      </c>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr"/>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7605916734050026248', 'createTime': 1770890495, 'createTimeISO': '2026-02-12T10:01:35.000Z', 'text': 'mi hija me hizo comprar todos los de dinosaurios, navidad ,y ahora sacan sus favoritos 🥴🥴 animales marinos 🥴🤣🤣🤣', 'diggCount': 15, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCo</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>1</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>https://vt.tiktok.com/ZSmCS4nn2/</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>https://vt.tiktok.com/ZSmCS4nn2/</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>yo quiero</t>
+        </is>
+      </c>
+      <c r="G79" t="n">
+        <v>1770889565</v>
+      </c>
+      <c r="H79" s="1" t="n">
+        <v>46065.40700231482</v>
+      </c>
+      <c r="I79" s="1" t="n">
+        <v>46065</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>09:46:05</t>
+        </is>
+      </c>
+      <c r="K79" t="n">
+        <v>0</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0</v>
+      </c>
+      <c r="M79" t="b">
+        <v>0</v>
+      </c>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr"/>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7605912711730856705', 'createTime': 1770889565, 'createTimeISO': '2026-02-12T09:46:05.000Z', 'text': 'yo quiero', 'diggCount': 0, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '7336195362929787910', 'uniqueId': 'melany.noriega30', 'avatarThumbnail': 'https</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>1</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>TikTok</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>https://vt.tiktok.com/ZSmCS4nn2/</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>https://vt.tiktok.com/ZSmCS4nn2/</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Yo quirooooo 🥺</t>
+        </is>
+      </c>
+      <c r="G80" t="n">
+        <v>1770884424</v>
+      </c>
+      <c r="H80" s="1" t="n">
+        <v>46065.3475</v>
+      </c>
+      <c r="I80" s="1" t="n">
+        <v>46065</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>08:20:24</t>
+        </is>
+      </c>
+      <c r="K80" t="n">
+        <v>2</v>
+      </c>
+      <c r="L80" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" t="b">
+        <v>0</v>
+      </c>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>https://www.tiktok.com/@</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr"/>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>{'videoWebUrl': 'https://www.tiktok.com/@alpinacol/video/7605370456417373452', 'submittedVideoUrl': 'https://vt.tiktok.com/ZSmCS4nn2/', 'input': 'https://vt.tiktok.com/ZSmCS4nn2/', 'cid': '7605890624642024212', 'createTime': 1770884424, 'createTimeISO': '2026-02-12T08:20:24.000Z', 'text': 'Yo quirooooo 🥺', 'diggCount': 2, 'likedByAuthor': False, 'pinnedByAuthor': False, 'repliesToId': None, 'replyCommentTotal': 0, 'uid': '6573387218701811717', 'uniqueId': 'papita_0401', 'avatarThumbnail': 'https</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>2</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DQZl34lDDef/</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DQZl34lDDef/</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>mm.____.3x</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Y esa cosa negra en la pared🤨🤨🤨</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>2025-11-20T01:56:08.000Z</t>
+        </is>
+      </c>
+      <c r="H81" s="1" t="n">
+        <v>45981.08064814815</v>
+      </c>
+      <c r="I81" s="1" t="n">
+        <v>45981</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>01:56:08</t>
+        </is>
+      </c>
+      <c r="K81" t="n">
+        <v>1</v>
+      </c>
+      <c r="L81" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" t="b">
+        <v>0</v>
+      </c>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>https://instagram.com/mm.____.3x</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr"/>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>{'postUrl': 'https://www.instagram.com/p/DQZl34lDDef/', 'commentUrl': 'https://www.instagram.com/p/DQZl34lDDef/c/17878999155332166', 'id': '17878999155332166', 'text': 'Y esa cosa negra en la pared🤨🤨🤨', 'ownerUsername': 'mm.____.3x', 'ownerProfilePicUrl': 'https://scontent-iad3-1.cdninstagram.com/v/t51.89012-19/573323465_1219825463302212_7278921664109726296_n.png?stp=dst-webp_s150x150&amp;_nc_cat=1&amp;ig_cache_key=YW5vbnltb3VzX3Byb2ZpbGVfcGlj.3-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InBy</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>2</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DQZl34lDDef/</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DQZl34lDDef/</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>luis_dacop</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Dejame negociar el riñón que me sobra 🙄</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>2025-11-20T00:44:24.000Z</t>
+        </is>
+      </c>
+      <c r="H82" s="1" t="n">
+        <v>45981.03083333333</v>
+      </c>
+      <c r="I82" s="1" t="n">
+        <v>45981</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>00:44:24</t>
+        </is>
+      </c>
+      <c r="K82" t="n">
+        <v>1</v>
+      </c>
+      <c r="L82" t="n">
+        <v>0</v>
+      </c>
+      <c r="M82" t="b">
+        <v>0</v>
+      </c>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>https://instagram.com/luis_dacop</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr"/>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>{'postUrl': 'https://www.instagram.com/p/DQZl34lDDef/', 'commentUrl': 'https://www.instagram.com/p/DQZl34lDDef/c/17980855841926100', 'id': '17980855841926100', 'text': 'Dejame negociar el riñón que me sobra 🙄', 'ownerUsername': 'luis_dacop', 'ownerProfilePicUrl': 'https://scontent-iad3-1.cdninstagram.com/v/t51.82787-19/625230176_18095921168313175_2177686544448637796_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=107&amp;ig_cache_key=GGBBRCVX6x75JEpAAGRLAtJfsjgebmNDAQAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=6694</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>2</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DQZl34lDDef/</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DQZl34lDDef/</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>solo.roberto</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>No gracias alpina está muy cara !</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>2025-11-19T00:17:09.000Z</t>
+        </is>
+      </c>
+      <c r="H83" s="1" t="n">
+        <v>45980.01190972222</v>
+      </c>
+      <c r="I83" s="1" t="n">
+        <v>45980</v>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>00:17:09</t>
+        </is>
+      </c>
+      <c r="K83" t="n">
+        <v>4</v>
+      </c>
+      <c r="L83" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" t="b">
+        <v>0</v>
+      </c>
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>https://instagram.com/solo.roberto</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr"/>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>{'postUrl': 'https://www.instagram.com/p/DQZl34lDDef/', 'commentUrl': 'https://www.instagram.com/p/DQZl34lDDef/c/17869377699399109', 'id': '17869377699399109', 'text': 'No gracias alpina está muy cara !', 'ownerUsername': 'solo.roberto', 'ownerProfilePicUrl': 'https://scontent-iad3-1.cdninstagram.com/v/t51.75761-19/497451179_18462727648079276_6370863006333456058_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=104&amp;ig_cache_key=GKuAph2sbQzDwJdBALrOLmUm2mlYbvEnAQAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;e</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>2</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Instagram</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DQZl34lDDef/</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DQZl34lDDef/</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>jeanb_555</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>HaaaaAAA!</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>2025-11-17T01:13:39.000Z</t>
+        </is>
+      </c>
+      <c r="H84" s="1" t="n">
+        <v>45978.05114583333</v>
+      </c>
+      <c r="I84" s="1" t="n">
+        <v>45978</v>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>01:13:39</t>
+        </is>
+      </c>
+      <c r="K84" t="n">
+        <v>1</v>
+      </c>
+      <c r="L84" t="n">
+        <v>0</v>
+      </c>
+      <c r="M84" t="b">
+        <v>0</v>
+      </c>
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>https://instagram.com/jeanb_555</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr"/>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>{'postUrl': 'https://www.instagram.com/p/DQZl34lDDef/', 'commentUrl': 'https://www.instagram.com/p/DQZl34lDDef/c/18327825274240575', 'id': '18327825274240575', 'text': 'HaaaaAAA!', 'ownerUsername': 'jeanb_555', 'ownerProfilePicUrl': 'https://scontent-iad3-1.cdninstagram.com/v/t51.82787-19/619082747_17977100765977609_5485987972083477950_n.jpg?stp=dst-jpg_e0_s150x150_tt6&amp;_nc_cat=108&amp;ig_cache_key=GPtz5iQJXD-xE94-AL7tGZ7_JCJMbmNDAQAB1501500j-ccb7-5&amp;ccb=7-5&amp;_nc_sid=669407&amp;efg=eyJ2ZW5jb2RlX3RhZyI6InBy</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>3</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/1318637550308481/</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/1318637550308481/</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Holavivianapaternia</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>2026-01-18T21:45:53.000Z</t>
+        </is>
+      </c>
+      <c r="H85" s="1" t="n">
+        <v>46040.90686342592</v>
+      </c>
+      <c r="I85" s="1" t="n">
+        <v>46040</v>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>21:45:53</t>
+        </is>
+      </c>
+      <c r="K85" t="n">
+        <v>0</v>
+      </c>
+      <c r="L85" t="n">
+        <v>0</v>
+      </c>
+      <c r="M85" t="b">
+        <v>0</v>
+      </c>
+      <c r="N85" t="inlineStr"/>
+      <c r="O85" t="inlineStr"/>
+      <c r="P85" t="inlineStr"/>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/1318637550308481/', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid07ABytcFMswuYfZXzEvApUr8Z5dWYLLCCCK83g8dRCHkNnDoLghdZYeDPwM1muMnrl?comment_id=1123930883027156', 'commentId': '1123930883027156', 'id': 'Y29tbWVudDoxMzE4NjM4MDUwMzA4NDMxXzExMjM5MzA4ODMwMjcxNTY=', 'feedbackId': 'ZmVlZGJhY2s6MTMxODYzODA1MDMwODQzMV8xMTIzOTMwODgzMDI3MTU2', 'date': '2026-01-18T21:45:53.000Z', 'text': 'Holavivianapaternia', 'profileUrl': 'https:</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>3</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/1318637550308481/</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/1318637550308481/</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Salome</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>2026-01-14T23:51:57.000Z</t>
+        </is>
+      </c>
+      <c r="H86" s="1" t="n">
+        <v>46036.99440972223</v>
+      </c>
+      <c r="I86" s="1" t="n">
+        <v>46036</v>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>23:51:57</t>
+        </is>
+      </c>
+      <c r="K86" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" t="b">
+        <v>0</v>
+      </c>
+      <c r="N86" t="inlineStr"/>
+      <c r="O86" t="inlineStr"/>
+      <c r="P86" t="inlineStr"/>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/1318637550308481/', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid07ABytcFMswuYfZXzEvApUr8Z5dWYLLCCCK83g8dRCHkNnDoLghdZYeDPwM1muMnrl?comment_id=1412783150373933', 'commentId': '1412783150373933', 'id': 'Y29tbWVudDoxMzE4NjM4MDUwMzA4NDMxXzE0MTI3ODMxNTAzNzM5MzM=', 'feedbackId': 'ZmVlZGJhY2s6MTMxODYzODA1MDMwODQzMV8xNDEyNzgzMTUwMzczOTMz', 'date': '2026-01-14T23:51:57.000Z', 'text': 'Salome', 'profileUrl': 'https://www.faceboo</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>3</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/1318637550308481/</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/100064867445065/posts/1318637550308481/</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr">
+        <is>
           <t>Ñ
 Ññ</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="G87" t="inlineStr">
         <is>
           <t>2026-01-11T20:48:42.000Z</t>
         </is>
       </c>
-      <c r="H78" s="1" t="n">
+      <c r="H87" s="1" t="n">
         <v>46033.86715277778</v>
       </c>
-      <c r="I78" s="2" t="n">
+      <c r="I87" s="1" t="n">
         <v>46033</v>
       </c>
-      <c r="J78" t="inlineStr">
+      <c r="J87" t="inlineStr">
         <is>
           <t>20:48:42</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L78" t="n">
-        <v>0</v>
-      </c>
-      <c r="M78" t="b">
-        <v>0</v>
-      </c>
-      <c r="N78" t="inlineStr"/>
-      <c r="O78" t="inlineStr"/>
-      <c r="P78" t="inlineStr">
+      <c r="K87" t="n">
+        <v>1</v>
+      </c>
+      <c r="L87" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" t="b">
+        <v>0</v>
+      </c>
+      <c r="N87" t="inlineStr"/>
+      <c r="O87" t="inlineStr"/>
+      <c r="P87" t="inlineStr"/>
+      <c r="Q87" t="inlineStr">
         <is>
           <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/1318637550308481/', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid07ABytcFMswuYfZXzEvApUr8Z5dWYLLCCCK83g8dRCHkNnDoLghdZYeDPwM1muMnrl?comment_id=1185407276613695', 'commentId': '1185407276613695', 'id': 'Y29tbWVudDoxMzE4NjM4MDUwMzA4NDMxXzExODU0MDcyNzY2MTM2OTU=', 'feedbackId': 'ZmVlZGJhY2s6MTMxODYzODA1MDMwODQzMV8xMTg1NDA3Mjc2NjEzNjk1', 'date': '2026-01-11T20:48:42.000Z', 'text': 'Ñ\nÑñ', 'profileUrl': 'https://www.facebook</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" t="n">
+    <row r="88">
+      <c r="A88" t="n">
         <v>3</v>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B88" t="inlineStr">
         <is>
           <t>Facebook</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="C88" t="inlineStr">
         <is>
           <t>https://www.facebook.com/100064867445065/posts/1318637550308481/</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="D88" t="inlineStr">
         <is>
           <t>https://www.facebook.com/100064867445065/posts/1318637550308481/</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr">
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr">
         <is>
           <t>Bueno</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="G88" t="inlineStr">
         <is>
           <t>2026-01-10T22:35:04.000Z</t>
         </is>
       </c>
-      <c r="H79" s="1" t="n">
+      <c r="H88" s="1" t="n">
         <v>46032.94101851852</v>
       </c>
-      <c r="I79" s="2" t="n">
+      <c r="I88" s="1" t="n">
         <v>46032</v>
       </c>
-      <c r="J79" t="inlineStr">
+      <c r="J88" t="inlineStr">
         <is>
           <t>22:35:04</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L79" t="n">
-        <v>0</v>
-      </c>
-      <c r="M79" t="b">
-        <v>0</v>
-      </c>
-      <c r="N79" t="inlineStr"/>
-      <c r="O79" t="inlineStr"/>
-      <c r="P79" t="inlineStr">
+      <c r="K88" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" t="b">
+        <v>0</v>
+      </c>
+      <c r="N88" t="inlineStr"/>
+      <c r="O88" t="inlineStr"/>
+      <c r="P88" t="inlineStr"/>
+      <c r="Q88" t="inlineStr">
         <is>
           <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/1318637550308481/', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid07ABytcFMswuYfZXzEvApUr8Z5dWYLLCCCK83g8dRCHkNnDoLghdZYeDPwM1muMnrl?comment_id=893455673202688', 'commentId': '893455673202688', 'id': 'Y29tbWVudDoxMzE4NjM4MDUwMzA4NDMxXzg5MzQ1NTY3MzIwMjY4OA==', 'feedbackId': 'ZmVlZGJhY2s6MTMxODYzODA1MDMwODQzMV84OTM0NTU2NzMyMDI2ODg=', 'date': '2026-01-10T22:35:04.000Z', 'text': 'Bueno', 'profileUrl': 'https://www.facebook.c</t>
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" t="n">
+    <row r="89">
+      <c r="A89" t="n">
         <v>3</v>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="B89" t="inlineStr">
         <is>
           <t>Facebook</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
+      <c r="C89" t="inlineStr">
         <is>
           <t>https://www.facebook.com/100064867445065/posts/1318637550308481/</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
+      <c r="D89" t="inlineStr">
         <is>
           <t>https://www.facebook.com/100064867445065/posts/1318637550308481/</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr">
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr">
         <is>
           <t>Soy onerto</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="G89" t="inlineStr">
         <is>
           <t>2026-01-10T00:41:55.000Z</t>
         </is>
       </c>
-      <c r="H80" s="1" t="n">
+      <c r="H89" s="1" t="n">
         <v>46032.0291087963</v>
       </c>
-      <c r="I80" s="2" t="n">
+      <c r="I89" s="1" t="n">
         <v>46032</v>
       </c>
-      <c r="J80" t="inlineStr">
+      <c r="J89" t="inlineStr">
         <is>
           <t>00:41:55</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L80" t="n">
-        <v>0</v>
-      </c>
-      <c r="M80" t="b">
-        <v>0</v>
-      </c>
-      <c r="N80" t="inlineStr"/>
-      <c r="O80" t="inlineStr"/>
-      <c r="P80" t="inlineStr">
+      <c r="K89" t="n">
+        <v>0</v>
+      </c>
+      <c r="L89" t="n">
+        <v>0</v>
+      </c>
+      <c r="M89" t="b">
+        <v>0</v>
+      </c>
+      <c r="N89" t="inlineStr"/>
+      <c r="O89" t="inlineStr"/>
+      <c r="P89" t="inlineStr"/>
+      <c r="Q89" t="inlineStr">
         <is>
           <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/1318637550308481/', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid07ABytcFMswuYfZXzEvApUr8Z5dWYLLCCCK83g8dRCHkNnDoLghdZYeDPwM1muMnrl?comment_id=754375667135961', 'commentId': '754375667135961', 'id': 'Y29tbWVudDoxMzE4NjM4MDUwMzA4NDMxXzc1NDM3NTY2NzEzNTk2MQ==', 'feedbackId': 'ZmVlZGJhY2s6MTMxODYzODA1MDMwODQzMV83NTQzNzU2NjcxMzU5NjE=', 'date': '2026-01-10T00:41:55.000Z', 'text': 'Soy onerto', 'profileUrl': 'https://www.faceb</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" t="n">
+    <row r="90">
+      <c r="A90" t="n">
         <v>3</v>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="B90" t="inlineStr">
         <is>
           <t>Facebook</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="C90" t="inlineStr">
         <is>
           <t>https://www.facebook.com/100064867445065/posts/1318637550308481/</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
+      <c r="D90" t="inlineStr">
         <is>
           <t>https://www.facebook.com/100064867445065/posts/1318637550308481/</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr">
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr">
         <is>
           <t>Muy cierto. Lo recomiendo x experiencia propia.</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="G90" t="inlineStr">
         <is>
           <t>2026-01-09T22:09:01.000Z</t>
         </is>
       </c>
-      <c r="H81" s="1" t="n">
+      <c r="H90" s="1" t="n">
         <v>46031.92292824074</v>
       </c>
-      <c r="I81" s="2" t="n">
+      <c r="I90" s="1" t="n">
         <v>46031</v>
       </c>
-      <c r="J81" t="inlineStr">
+      <c r="J90" t="inlineStr">
         <is>
           <t>22:09:01</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L81" t="n">
-        <v>0</v>
-      </c>
-      <c r="M81" t="b">
-        <v>0</v>
-      </c>
-      <c r="N81" t="inlineStr"/>
-      <c r="O81" t="inlineStr"/>
-      <c r="P81" t="inlineStr">
+      <c r="K90" t="n">
+        <v>2</v>
+      </c>
+      <c r="L90" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" t="b">
+        <v>0</v>
+      </c>
+      <c r="N90" t="inlineStr"/>
+      <c r="O90" t="inlineStr"/>
+      <c r="P90" t="inlineStr"/>
+      <c r="Q90" t="inlineStr">
         <is>
           <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/1318637550308481/', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid07ABytcFMswuYfZXzEvApUr8Z5dWYLLCCCK83g8dRCHkNnDoLghdZYeDPwM1muMnrl?comment_id=1689542495353193', 'commentId': '1689542495353193', 'id': 'Y29tbWVudDoxMzE4NjM4MDUwMzA4NDMxXzE2ODk1NDI0OTUzNTMxOTM=', 'feedbackId': 'ZmVlZGJhY2s6MTMxODYzODA1MDMwODQzMV8xNjg5NTQyNDk1MzUzMTkz', 'date': '2026-01-09T22:09:01.000Z', 'text': 'Muy cierto. Lo recomiendo x experiencia pro</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" t="n">
+    <row r="91">
+      <c r="A91" t="n">
         <v>3</v>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="B91" t="inlineStr">
         <is>
           <t>Facebook</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
+      <c r="C91" t="inlineStr">
         <is>
           <t>https://www.facebook.com/100064867445065/posts/1318637550308481/</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
+      <c r="D91" t="inlineStr">
         <is>
           <t>https://www.facebook.com/100064867445065/posts/1318637550308481/</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr">
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr">
         <is>
           <t>Ya no venden nada deslactosado y sin azúcar.</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="G91" t="inlineStr">
         <is>
           <t>2026-01-09T20:26:53.000Z</t>
         </is>
       </c>
-      <c r="H82" s="1" t="n">
+      <c r="H91" s="1" t="n">
         <v>46031.85200231482</v>
       </c>
-      <c r="I82" s="2" t="n">
+      <c r="I91" s="1" t="n">
         <v>46031</v>
       </c>
-      <c r="J82" t="inlineStr">
+      <c r="J91" t="inlineStr">
         <is>
           <t>20:26:53</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L82" t="n">
-        <v>0</v>
-      </c>
-      <c r="M82" t="b">
-        <v>0</v>
-      </c>
-      <c r="N82" t="inlineStr"/>
-      <c r="O82" t="inlineStr"/>
-      <c r="P82" t="inlineStr">
+      <c r="K91" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" t="b">
+        <v>0</v>
+      </c>
+      <c r="N91" t="inlineStr"/>
+      <c r="O91" t="inlineStr"/>
+      <c r="P91" t="inlineStr"/>
+      <c r="Q91" t="inlineStr">
         <is>
           <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/1318637550308481/', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid07ABytcFMswuYfZXzEvApUr8Z5dWYLLCCCK83g8dRCHkNnDoLghdZYeDPwM1muMnrl?comment_id=1565057301442891', 'commentId': '1565057301442891', 'id': 'Y29tbWVudDoxMzE4NjM4MDUwMzA4NDMxXzE1NjUwNTczMDE0NDI4OTE=', 'feedbackId': 'ZmVlZGJhY2s6MTMxODYzODA1MDMwODQzMV8xNTY1MDU3MzAxNDQyODkx', 'date': '2026-01-09T20:26:53.000Z', 'text': 'Ya no venden nada deslactosado y sin azúcar</t>
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" t="n">
+    <row r="92">
+      <c r="A92" t="n">
         <v>3</v>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="B92" t="inlineStr">
         <is>
           <t>Facebook</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
+      <c r="C92" t="inlineStr">
         <is>
           <t>https://www.facebook.com/100064867445065/posts/1318637550308481/</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
+      <c r="D92" t="inlineStr">
         <is>
           <t>https://www.facebook.com/100064867445065/posts/1318637550308481/</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr"/>
-      <c r="F83" t="inlineStr">
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr">
         <is>
           <t>Quien y donde dice q el azúcar ayuda a fortalecer el sistema inmune ?</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
+      <c r="G92" t="inlineStr">
         <is>
           <t>2026-01-09T01:15:23.000Z</t>
         </is>
       </c>
-      <c r="H83" s="1" t="n">
+      <c r="H92" s="1" t="n">
         <v>46031.05234953704</v>
       </c>
-      <c r="I83" s="2" t="n">
+      <c r="I92" s="1" t="n">
         <v>46031</v>
       </c>
-      <c r="J83" t="inlineStr">
+      <c r="J92" t="inlineStr">
         <is>
           <t>01:15:23</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L83" t="n">
-        <v>0</v>
-      </c>
-      <c r="M83" t="b">
-        <v>0</v>
-      </c>
-      <c r="N83" t="inlineStr"/>
-      <c r="O83" t="inlineStr"/>
-      <c r="P83" t="inlineStr">
+      <c r="K92" t="n">
+        <v>0</v>
+      </c>
+      <c r="L92" t="n">
+        <v>0</v>
+      </c>
+      <c r="M92" t="b">
+        <v>0</v>
+      </c>
+      <c r="N92" t="inlineStr"/>
+      <c r="O92" t="inlineStr"/>
+      <c r="P92" t="inlineStr"/>
+      <c r="Q92" t="inlineStr">
         <is>
           <t>{'facebookUrl': 'https://www.facebook.com/100064867445065/posts/1318637550308481/', 'commentUrl': 'https://www.facebook.com/alpina/posts/pfbid07ABytcFMswuYfZXzEvApUr8Z5dWYLLCCCK83g8dRCHkNnDoLghdZYeDPwM1muMnrl?comment_id=1206257714984269', 'commentId': '1206257714984269', 'id': 'Y29tbWVudDoxMzE4NjM4MDUwMzA4NDMxXzEyMDYyNTc3MTQ5ODQyNjk=', 'feedbackId': 'ZmVlZGJhY2s6MTMxODYzODA1MDMwODQzMV8xMjA2MjU3NzE0OTg0MjY5', 'date': '2026-01-09T01:15:23.000Z', 'text': 'Quien y donde dice q el azúcar ayuda a fort</t>
         </is>
@@ -5520,7 +6158,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="E2" t="n">
         <v>114</v>
@@ -5675,10 +6313,10 @@
         <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>70</v>
+        <v>79</v>
       </c>
       <c r="D4" t="n">
-        <v>1.63</v>
+        <v>1.44</v>
       </c>
       <c r="E4" t="n">
         <v>114</v>
